--- a/GearSage-client/pkgGear/data_raw/abu_rod_import.xlsx
+++ b/GearSage-client/pkgGear/data_raw/abu_rod_import.xlsx
@@ -2649,7 +2649,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AQ206"/>
+  <dimension ref="A1:AR206"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2755,30 +2755,33 @@
         <v>guide_use_hint</v>
       </c>
       <c r="AI1" t="str">
+        <v>recommended_rig_pairing</v>
+      </c>
+      <c r="AJ1" t="str">
         <v>hook_keeper_included</v>
       </c>
-      <c r="AJ1" t="str">
+      <c r="AK1" t="str">
         <v>sweet_spot_lure_weight_real</v>
       </c>
-      <c r="AK1" t="str">
+      <c r="AL1" t="str">
         <v>official_environment</v>
       </c>
-      <c r="AL1" t="str">
+      <c r="AM1" t="str">
         <v>player_environment</v>
       </c>
-      <c r="AM1" t="str">
+      <c r="AN1" t="str">
         <v>player_positioning</v>
       </c>
-      <c r="AN1" t="str">
+      <c r="AO1" t="str">
         <v>player_selling_points</v>
       </c>
-      <c r="AO1" t="str">
+      <c r="AP1" t="str">
         <v>Description</v>
       </c>
-      <c r="AP1" t="str">
+      <c r="AQ1" t="str">
         <v>Extra Spec 1</v>
       </c>
-      <c r="AQ1" t="str">
+      <c r="AR1" t="str">
         <v>Extra Spec 2</v>
       </c>
     </row>
@@ -2883,33 +2886,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH2" t="str" s="1">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用枪柄 6'6" M Fast，适合轻中量底操，Texas Rig、Free Rig、Rubber Jig 可以打岸边硬物和稀疏 cover；移动饵只是活性高时的补充。</v>
       </c>
       <c r="AI2" t="str" s="1">
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
+      </c>
+      <c r="AJ2" t="str" s="1">
         <v>1</v>
       </c>
-      <c r="AJ2" t="str" s="1">
-        <v/>
-      </c>
       <c r="AK2" t="str" s="1">
         <v/>
       </c>
       <c r="AL2" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM2" t="str" s="1">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 6'6"轻中量底操</v>
       </c>
       <c r="AN2" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>实战泛用 / 6'6" M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO2" t="str" s="1">
+        <v>实战泛用枪柄 6'6" M Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP2" t="str" s="1">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP2" t="str" s="1">
+      <c r="AQ2" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ2" t="str" s="1">
+      <c r="AR2" t="str" s="1">
         <v>UPC: 36282135567; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -3014,33 +3020,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH3" t="str" s="1">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用枪柄 6'6" MH Fast，更适合 Texas / Jig 路线，Texas Rig、Rubber Jig、Free Rig 先保证落点和读底，鱼活性高时可切移动饵提高覆盖。</v>
       </c>
       <c r="AI3" t="str" s="1">
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
+      </c>
+      <c r="AJ3" t="str" s="1">
         <v>1</v>
       </c>
-      <c r="AJ3" t="str" s="1">
-        <v/>
-      </c>
       <c r="AK3" t="str" s="1">
         <v/>
       </c>
       <c r="AL3" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM3" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 6'6"中重型底操</v>
       </c>
       <c r="AN3" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>实战泛用 / 6'6" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO3" t="str" s="1">
+        <v>实战泛用枪柄 6'6" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP3" t="str" s="1">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP3" t="str" s="1">
+      <c r="AQ3" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ3" t="str" s="1">
+      <c r="AR3" t="str" s="1">
         <v>UPC: 36282135574; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -3145,33 +3154,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH4" t="str" s="1">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用枪柄 6'6" MH Fast，用于 cover 外缘和硬结构慢拖，Texas Rig、Rubber Jig、Free Rig 的优势在刺鱼余量和软硬饵切换宽容。</v>
       </c>
       <c r="AI4" t="str" s="1">
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
+      </c>
+      <c r="AJ4" t="str" s="1">
         <v>1</v>
       </c>
-      <c r="AJ4" t="str" s="1">
-        <v/>
-      </c>
       <c r="AK4" t="str" s="1">
         <v/>
       </c>
       <c r="AL4" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM4" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 6'6"中重型底操</v>
       </c>
       <c r="AN4" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>实战泛用 / 6'6" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO4" t="str" s="1">
+        <v>实战泛用枪柄 6'6" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP4" t="str" s="1">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP4" t="str" s="1">
+      <c r="AQ4" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ4" t="str" s="1">
+      <c r="AR4" t="str" s="1">
         <v>UPC: 36282143333; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -3276,33 +3288,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH5" t="str" s="1">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用枪柄 6'9" MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI5" t="str" s="1">
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
+      </c>
+      <c r="AJ5" t="str" s="1">
         <v>1</v>
       </c>
-      <c r="AJ5" t="str" s="1">
-        <v/>
-      </c>
       <c r="AK5" t="str" s="1">
         <v/>
       </c>
       <c r="AL5" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM5" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 6'9"中重型底操</v>
       </c>
       <c r="AN5" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>实战泛用 / 6'9" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO5" t="str" s="1">
+        <v>实战泛用枪柄 6'9" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP5" t="str" s="1">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP5" t="str" s="1">
+      <c r="AQ5" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ5" t="str" s="1">
+      <c r="AR5" t="str" s="1">
         <v>UPC: 36282135581; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -3407,33 +3422,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH6" t="str" s="1">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用枪柄 7' M Fast，适合轻中量底操，Texas Rig、Free Rig、Rubber Jig 可以打岸边硬物和稀疏 cover；移动饵只是活性高时的补充。</v>
       </c>
       <c r="AI6" t="str" s="1">
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
+      </c>
+      <c r="AJ6" t="str" s="1">
         <v>1</v>
       </c>
-      <c r="AJ6" t="str" s="1">
-        <v/>
-      </c>
       <c r="AK6" t="str" s="1">
         <v/>
       </c>
       <c r="AL6" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM6" t="str" s="1">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 7'轻中量底操</v>
       </c>
       <c r="AN6" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>实战泛用 / 7' M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO6" t="str" s="1">
+        <v>实战泛用枪柄 7' M Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP6" t="str" s="1">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP6" t="str" s="1">
+      <c r="AQ6" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ6" t="str" s="1">
+      <c r="AR6" t="str" s="1">
         <v>UPC: 36282135598; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -3538,33 +3556,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH7" t="str" s="1">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用枪柄 7' MH Fast，用于 cover 外缘和硬结构慢拖，Texas Rig、Rubber Jig、Free Rig 的优势在刺鱼余量和软硬饵切换宽容。</v>
       </c>
       <c r="AI7" t="str" s="1">
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
+      </c>
+      <c r="AJ7" t="str" s="1">
         <v>1</v>
       </c>
-      <c r="AJ7" t="str" s="1">
-        <v/>
-      </c>
       <c r="AK7" t="str" s="1">
         <v/>
       </c>
       <c r="AL7" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM7" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'中重型底操</v>
       </c>
       <c r="AN7" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>实战泛用 / 7' MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO7" t="str" s="1">
+        <v>实战泛用枪柄 7' MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP7" t="str" s="1">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP7" t="str" s="1">
+      <c r="AQ7" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ7" t="str" s="1">
+      <c r="AR7" t="str" s="1">
         <v>UPC: 36282135604; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -3669,33 +3690,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH8" t="str" s="1">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用枪柄 7'3" MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI8" t="str" s="1">
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
+      </c>
+      <c r="AJ8" t="str" s="1">
         <v>1</v>
       </c>
-      <c r="AJ8" t="str" s="1">
-        <v/>
-      </c>
       <c r="AK8" t="str" s="1">
         <v/>
       </c>
       <c r="AL8" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM8" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'3"中重型底操</v>
       </c>
       <c r="AN8" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>实战泛用 / 7'3" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO8" t="str" s="1">
+        <v>实战泛用枪柄 7'3" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP8" t="str" s="1">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP8" t="str" s="1">
+      <c r="AQ8" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ8" t="str" s="1">
+      <c r="AR8" t="str" s="1">
         <v>UPC: 36282143357; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -3800,33 +3824,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH9" t="str" s="1">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用枪柄 7'3" H Moderate Fast，拉动阻力较大的移动饵更顺手，Spinnerbait、Chatterbait、Swim Jig 适合草边大范围搜索，收线张力要保持连续。</v>
       </c>
       <c r="AI9" t="str" s="1">
+        <v>Spinnerbait / Chatterbait / Swim Jig / Crankbait / Lipless Crankbait</v>
+      </c>
+      <c r="AJ9" t="str" s="1">
         <v>1</v>
       </c>
-      <c r="AJ9" t="str" s="1">
-        <v/>
-      </c>
       <c r="AK9" t="str" s="1">
         <v/>
       </c>
       <c r="AL9" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM9" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 草边开阔水强搜索 / 7'3"重型移动饵</v>
       </c>
       <c r="AN9" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>实战泛用 / 7'3" H 中重型 moving bait</v>
       </c>
       <c r="AO9" t="str" s="1">
+        <v>实战泛用枪柄 7'3" H Moderate Fast，14-30 lb线组配置下，Spinnerbait、Chatterbait、Swim Jig 优先，H power 适合拉动阻力较大的移动饵；搜索效率和控鱼余量优先。</v>
+      </c>
+      <c r="AP9" t="str" s="1">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP9" t="str" s="1">
+      <c r="AQ9" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ9" t="str" s="1">
+      <c r="AR9" t="str" s="1">
         <v>UPC: 36282143364; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -3931,33 +3958,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH10" t="str" s="1">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用枪柄 7'6" H Moderate Fast，拉动阻力较大的移动饵更顺手，Spinnerbait、Chatterbait、Swim Jig 适合草边大范围搜索，收线张力要保持连续。</v>
       </c>
       <c r="AI10" t="str" s="1">
+        <v>Spinnerbait / Chatterbait / Swim Jig / Crankbait / Lipless Crankbait</v>
+      </c>
+      <c r="AJ10" t="str" s="1">
         <v>1</v>
       </c>
-      <c r="AJ10" t="str" s="1">
-        <v/>
-      </c>
       <c r="AK10" t="str" s="1">
         <v/>
       </c>
       <c r="AL10" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM10" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 草边开阔水强搜索 / 7'6"重型移动饵</v>
       </c>
       <c r="AN10" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>实战泛用 / 7'6" H 中重型 moving bait</v>
       </c>
       <c r="AO10" t="str" s="1">
+        <v>实战泛用枪柄 7'6" H Moderate Fast，14-30 lb线组配置下，Spinnerbait、Chatterbait、Swim Jig 优先，H power 适合拉动阻力较大的移动饵；搜索效率和控鱼余量优先。</v>
+      </c>
+      <c r="AP10" t="str" s="1">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP10" t="str" s="1">
+      <c r="AQ10" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ10" t="str" s="1">
+      <c r="AR10" t="str" s="1">
         <v>UPC: 36282135611; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -4062,33 +4092,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH11" t="str" s="2">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用直柄 6' M Fast，偏直柄精细泛用，Neko Rig、Wacky Rig、Down Shot 适合岸边轻量软饵；小 Minnow 只是补充搜索路线。</v>
       </c>
       <c r="AI11" t="str" s="2">
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
+      </c>
+      <c r="AJ11" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ11" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK11" t="str" s="2">
         <v/>
       </c>
       <c r="AL11" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM11" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 6'直柄泛用</v>
       </c>
       <c r="AN11" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>实战泛用 / 6' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO11" t="str" s="2">
+        <v>实战泛用直柄 6' M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP11" t="str" s="2">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP11" t="str" s="2">
+      <c r="AQ11" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ11" t="str" s="2">
+      <c r="AR11" t="str" s="2">
         <v>UPC: 36282135857; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -4193,33 +4226,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH12" t="str" s="2">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用直柄 6'6" M Fast，适合细线控饵，Neko Rig、Wacky Rig、Down Shot 的重点是松线管理和轻口判断，硬饵只做短距离补充。</v>
       </c>
       <c r="AI12" t="str" s="2">
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
+      </c>
+      <c r="AJ12" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ12" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK12" t="str" s="2">
         <v/>
       </c>
       <c r="AL12" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM12" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 6'6"直柄泛用</v>
       </c>
       <c r="AN12" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>实战泛用 / 6'6" M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO12" t="str" s="2">
+        <v>实战泛用直柄 6'6" M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP12" t="str" s="2">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP12" t="str" s="2">
+      <c r="AQ12" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ12" t="str" s="2">
+      <c r="AR12" t="str" s="2">
         <v>UPC: 36282135628; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -4324,33 +4360,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH13" t="str" s="2">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用直柄 6'6" M Fast，用于 Neko / Wacky 更自然，Neko Rig、Wacky Rig、Down Shot 可覆盖轻量打点和慢节奏搜索，别用太重的饵压竿。</v>
       </c>
       <c r="AI13" t="str" s="2">
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
+      </c>
+      <c r="AJ13" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ13" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK13" t="str" s="2">
         <v/>
       </c>
       <c r="AL13" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM13" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 6'6"直柄泛用</v>
       </c>
       <c r="AN13" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>实战泛用 / 6'6" M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO13" t="str" s="2">
+        <v>实战泛用直柄 6'6" M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP13" t="str" s="2">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP13" t="str" s="2">
+      <c r="AQ13" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ13" t="str" s="2">
+      <c r="AR13" t="str" s="2">
         <v>UPC: 36282135864; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -4455,33 +4494,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH14" t="str" s="2">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用直柄 6'9" ML Moderate Fast，用于清水或轻压场更自然，Down Shot、Neko Rig、Wacky Rig 动作要小，补刺靠节奏和线张力。</v>
       </c>
       <c r="AI14" t="str" s="2">
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
+      </c>
+      <c r="AJ14" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ14" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK14" t="str" s="2">
         <v/>
       </c>
       <c r="AL14" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM14" t="str" s="2">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线和轻压场 / 6'9"直柄精细</v>
       </c>
       <c r="AN14" t="str" s="2">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>实战泛用 / 6'9" ML Down Shot / Neko 精细</v>
       </c>
       <c r="AO14" t="str" s="2">
+        <v>实战泛用直柄 6'9" ML Moderate Fast，6-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，适合细线慢拖、轻抖和看线；微弱咬口反馈比强力控鱼更重要。</v>
+      </c>
+      <c r="AP14" t="str" s="2">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP14" t="str" s="2">
+      <c r="AQ14" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ14" t="str" s="2">
+      <c r="AR14" t="str" s="2">
         <v>UPC: 36282143371; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -4586,33 +4628,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH15" t="str" s="2">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用直柄 6'9" ML Moderate Fast，适合细线慢节奏，Down Shot、Neko Rig、Wacky Rig 以控松线和读轻口为主，不适合粗暴硬拔。</v>
       </c>
       <c r="AI15" t="str" s="2">
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
+      </c>
+      <c r="AJ15" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ15" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK15" t="str" s="2">
         <v/>
       </c>
       <c r="AL15" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM15" t="str" s="2">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线和轻压场 / 6'9"直柄精细</v>
       </c>
       <c r="AN15" t="str" s="2">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>实战泛用 / 6'9" ML Down Shot / Neko 精细</v>
       </c>
       <c r="AO15" t="str" s="2">
+        <v>实战泛用直柄 6'9" ML Moderate Fast，6-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，适合细线慢拖、轻抖和看线；微弱咬口反馈比强力控鱼更重要。</v>
+      </c>
+      <c r="AP15" t="str" s="2">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP15" t="str" s="2">
+      <c r="AQ15" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ15" t="str" s="2">
+      <c r="AR15" t="str" s="2">
         <v>UPC: 36282143388; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -4717,33 +4762,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH16" t="str" s="2">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用直柄 7' M Fast，用于 Neko / Wacky 更自然，Neko Rig、Wacky Rig、Down Shot 可覆盖轻量打点和慢节奏搜索，别用太重的饵压竿。</v>
       </c>
       <c r="AI16" t="str" s="2">
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
+      </c>
+      <c r="AJ16" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ16" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK16" t="str" s="2">
         <v/>
       </c>
       <c r="AL16" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM16" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'直柄泛用</v>
       </c>
       <c r="AN16" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>实战泛用 / 7' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO16" t="str" s="2">
+        <v>实战泛用直柄 7' M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP16" t="str" s="2">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP16" t="str" s="2">
+      <c r="AQ16" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ16" t="str" s="2">
+      <c r="AR16" t="str" s="2">
         <v>UPC: 36282135635; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -4848,33 +4896,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH17" t="str" s="2">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用直柄 7' M Fast，偏直柄精细泛用，Neko Rig、Wacky Rig、Down Shot 适合岸边轻量软饵；小 Minnow 只是补充搜索路线。</v>
       </c>
       <c r="AI17" t="str" s="2">
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
+      </c>
+      <c r="AJ17" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ17" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK17" t="str" s="2">
         <v/>
       </c>
       <c r="AL17" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM17" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'直柄泛用</v>
       </c>
       <c r="AN17" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>实战泛用 / 7' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO17" t="str" s="2">
+        <v>实战泛用直柄 7' M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP17" t="str" s="2">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP17" t="str" s="2">
+      <c r="AQ17" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ17" t="str" s="2">
+      <c r="AR17" t="str" s="2">
         <v>UPC: 36282135871; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -4979,33 +5030,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH18" t="str" s="2">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用直柄 7' MH Fast，比常规精细竿更能承受稍重钓组，Shaky Head、Free Rig、Neko Rig 适合开阔结构和深一点的标点，仍以控线为先。</v>
       </c>
       <c r="AI18" t="str" s="2">
+        <v>Shaky Head / Free Rig / Neko Rig / Small Swimbait / Swim Jig</v>
+      </c>
+      <c r="AJ18" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ18" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK18" t="str" s="2">
         <v/>
       </c>
       <c r="AL18" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM18" t="str" s="2">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开阔结构与稍重精细 / 7'直柄强精细</v>
       </c>
       <c r="AN18" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>实战泛用 / 7' MH Shaky Head / Free Rig 直柄</v>
       </c>
       <c r="AO18" t="str" s="2">
+        <v>实战泛用直柄 7' MH Fast，8-14 lb线组配置下，Shaky Head、Free Rig、Neko Rig 优先，适合比常规精细更重的钓组；保留直柄控线优势，同时有更好的刺鱼余量。</v>
+      </c>
+      <c r="AP18" t="str" s="2">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP18" t="str" s="2">
+      <c r="AQ18" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ18" t="str" s="2">
+      <c r="AR18" t="str" s="2">
         <v>UPC: 36282135642; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -5110,33 +5164,36 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH19" t="str" s="2">
-        <v>耐用泛用，维护成本低</v>
+        <v>实战泛用直柄 7'6" M Fast，用于 Neko / Wacky 更自然，Neko Rig、Wacky Rig、Down Shot 可覆盖轻量打点和慢节奏搜索，别用太重的饵压竿。</v>
       </c>
       <c r="AI19" t="str" s="2">
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
+      </c>
+      <c r="AJ19" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ19" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK19" t="str" s="2">
         <v/>
       </c>
       <c r="AL19" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM19" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'6"直柄泛用</v>
       </c>
       <c r="AN19" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>实战泛用 / 7'6" M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO19" t="str" s="2">
+        <v>实战泛用直柄 7'6" M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP19" t="str" s="2">
         <v>The Max Rod Series expands on the trusted Abu Garcia Max platform, designed for serious anglers seeking both performance and value. Each rod is constructed with a lightweight 24-ton graphite blank and durable stainless steel one-piece guides, delivering a sensitive, and responsive feel ideal for a wide range of techniques. Outfitted with EVA split-grip handles and custom Abu reel seats, they offer a secure, ergonomic grip that minimizes fatigue during extended use. The Max Rod Series delivers dependable performance without compromise.</v>
       </c>
-      <c r="AP19" t="str" s="2">
+      <c r="AQ19" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ19" t="str" s="2">
+      <c r="AR19" t="str" s="2">
         <v>UPC: 36282135888; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -5241,10 +5298,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH20" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用枪柄 6'6" M Fast，抛投负担较轻，Texas Rig、Free Rig、Rubber Jig 适合短中距离打点；需要搜索时再切 Spinnerbait / Chatterbait。</v>
       </c>
       <c r="AI20" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ20" t="str" s="1">
         <v/>
@@ -5253,21 +5310,24 @@
         <v/>
       </c>
       <c r="AL20" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM20" t="str" s="1">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 6'6"轻中量底操</v>
       </c>
       <c r="AN20" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 6'6" M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO20" t="str" s="1">
+        <v>进阶泛用枪柄 6'6" M Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP20" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta® Casting rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP20" t="str" s="1">
+      <c r="AQ20" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ20" t="str" s="1">
+      <c r="AR20" t="str" s="1">
         <v>UPC: 36282038479</v>
       </c>
     </row>
@@ -5372,10 +5432,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH21" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用枪柄 6'6" MH Fast，更适合 Texas / Jig 路线，Texas Rig、Rubber Jig、Free Rig 先保证落点和读底，鱼活性高时可切移动饵提高覆盖。</v>
       </c>
       <c r="AI21" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ21" t="str" s="1">
         <v/>
@@ -5384,21 +5444,24 @@
         <v/>
       </c>
       <c r="AL21" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM21" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 6'6"中重型底操</v>
       </c>
       <c r="AN21" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 6'6" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO21" t="str" s="1">
+        <v>进阶泛用枪柄 6'6" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP21" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta® Casting rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP21" t="str" s="1">
+      <c r="AQ21" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ21" t="str" s="1">
+      <c r="AR21" t="str" s="1">
         <v>UPC: 36282038486</v>
       </c>
     </row>
@@ -5503,10 +5566,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH22" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用枪柄 6'9" MH Fast，用于 cover 外缘和硬结构慢拖，Texas Rig、Rubber Jig、Free Rig 的优势在刺鱼余量和软硬饵切换宽容。</v>
       </c>
       <c r="AI22" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ22" t="str" s="1">
         <v/>
@@ -5515,21 +5578,24 @@
         <v/>
       </c>
       <c r="AL22" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM22" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 6'9"中重型底操</v>
       </c>
       <c r="AN22" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 6'9" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO22" t="str" s="1">
+        <v>进阶泛用枪柄 6'9" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP22" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta® Casting rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP22" t="str" s="1">
+      <c r="AQ22" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ22" t="str" s="1">
+      <c r="AR22" t="str" s="1">
         <v>UPC: 36282038493</v>
       </c>
     </row>
@@ -5634,10 +5700,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH23" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用枪柄 6'9" MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI23" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ23" t="str" s="1">
         <v/>
@@ -5646,21 +5712,24 @@
         <v/>
       </c>
       <c r="AL23" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM23" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 6'9"中重型底操</v>
       </c>
       <c r="AN23" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 6'9" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO23" t="str" s="1">
+        <v>进阶泛用枪柄 6'9" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP23" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta® Casting rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP23" t="str" s="1">
+      <c r="AQ23" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ23" t="str" s="1">
+      <c r="AR23" t="str" s="1">
         <v>UPC: 36282038509</v>
       </c>
     </row>
@@ -5765,10 +5834,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH24" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用枪柄 7' M Fast，适合轻中量底操，Texas Rig、Free Rig、Rubber Jig 可以打岸边硬物和稀疏 cover；移动饵只是活性高时的补充。</v>
       </c>
       <c r="AI24" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ24" t="str" s="1">
         <v/>
@@ -5777,21 +5846,24 @@
         <v/>
       </c>
       <c r="AL24" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM24" t="str" s="1">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 7'轻中量底操</v>
       </c>
       <c r="AN24" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 7' M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO24" t="str" s="1">
+        <v>进阶泛用枪柄 7' M Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP24" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta® Casting rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP24" t="str" s="1">
+      <c r="AQ24" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ24" t="str" s="1">
+      <c r="AR24" t="str" s="1">
         <v>UPC: 36282038516</v>
       </c>
     </row>
@@ -5896,10 +5968,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH25" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用枪柄 7' MH Fast，用于 cover 外缘和硬结构慢拖，Texas Rig、Rubber Jig、Free Rig 的优势在刺鱼余量和软硬饵切换宽容。</v>
       </c>
       <c r="AI25" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ25" t="str" s="1">
         <v/>
@@ -5908,21 +5980,24 @@
         <v/>
       </c>
       <c r="AL25" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM25" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'中重型底操</v>
       </c>
       <c r="AN25" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 7' MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO25" t="str" s="1">
+        <v>进阶泛用枪柄 7' MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP25" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta® Casting rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP25" t="str" s="1">
+      <c r="AQ25" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ25" t="str" s="1">
+      <c r="AR25" t="str" s="1">
         <v>UPC: 36282038523</v>
       </c>
     </row>
@@ -6027,10 +6102,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH26" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用枪柄 7' H Fast，偏重线底操，Heavy Texas、Rubber Jig、Football Jig 适合木桩、石堆和厚草边慢拖，重点是读底后稳定刺鱼。</v>
       </c>
       <c r="AI26" t="str" s="1">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ26" t="str" s="1">
         <v/>
@@ -6039,21 +6114,24 @@
         <v/>
       </c>
       <c r="AL26" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM26" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'强力底操</v>
       </c>
       <c r="AN26" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 7' H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO26" t="str" s="1">
+        <v>进阶泛用枪柄 7' H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP26" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta® Casting rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP26" t="str" s="1">
+      <c r="AQ26" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ26" t="str" s="1">
+      <c r="AR26" t="str" s="1">
         <v>UPC: 36282038530</v>
       </c>
     </row>
@@ -6158,10 +6236,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH27" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用枪柄 7'3" MH Fast，更适合 Texas / Jig 路线，Texas Rig、Rubber Jig、Free Rig 先保证落点和读底，鱼活性高时可切移动饵提高覆盖。</v>
       </c>
       <c r="AI27" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ27" t="str" s="1">
         <v/>
@@ -6170,21 +6248,24 @@
         <v/>
       </c>
       <c r="AL27" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM27" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'3"中重型底操</v>
       </c>
       <c r="AN27" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 7'3" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO27" t="str" s="1">
+        <v>进阶泛用枪柄 7'3" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP27" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta® Casting rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP27" t="str" s="1">
+      <c r="AQ27" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ27" t="str" s="1">
+      <c r="AR27" t="str" s="1">
         <v>UPC: 36282038547</v>
       </c>
     </row>
@@ -6289,10 +6370,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH28" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用枪柄 7'3" H Fast，偏重线底操，Heavy Texas、Rubber Jig、Football Jig 适合木桩、石堆和厚草边慢拖，重点是读底后稳定刺鱼。</v>
       </c>
       <c r="AI28" t="str" s="1">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ28" t="str" s="1">
         <v/>
@@ -6301,21 +6382,24 @@
         <v/>
       </c>
       <c r="AL28" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM28" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'3"强力底操</v>
       </c>
       <c r="AN28" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 7'3" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO28" t="str" s="1">
+        <v>进阶泛用枪柄 7'3" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP28" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta® Casting rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP28" t="str" s="1">
+      <c r="AQ28" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ28" t="str" s="1">
+      <c r="AR28" t="str" s="1">
         <v>UPC: 36282038554</v>
       </c>
     </row>
@@ -6420,10 +6504,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH29" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用枪柄 7'6" MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI29" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ29" t="str" s="1">
         <v/>
@@ -6432,21 +6516,24 @@
         <v/>
       </c>
       <c r="AL29" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM29" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'6"中重型底操</v>
       </c>
       <c r="AN29" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 7'6" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO29" t="str" s="1">
+        <v>进阶泛用枪柄 7'6" MH Fast，12-25 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP29" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta® Casting rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP29" t="str" s="1">
+      <c r="AQ29" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ29" t="str" s="1">
+      <c r="AR29" t="str" s="1">
         <v>UPC: 36282038561</v>
       </c>
     </row>
@@ -6551,10 +6638,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH30" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用枪柄 7'6" H Fast，偏重线底操，Heavy Texas、Rubber Jig、Football Jig 适合木桩、石堆和厚草边慢拖，重点是读底后稳定刺鱼。</v>
       </c>
       <c r="AI30" t="str" s="1">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ30" t="str" s="1">
         <v/>
@@ -6563,21 +6650,24 @@
         <v/>
       </c>
       <c r="AL30" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM30" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'6"强力底操</v>
       </c>
       <c r="AN30" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 7'6" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO30" t="str" s="1">
+        <v>进阶泛用枪柄 7'6" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP30" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta® Casting rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP30" t="str" s="1">
+      <c r="AQ30" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ30" t="str" s="1">
+      <c r="AR30" t="str" s="1">
         <v>UPC: 36282038578</v>
       </c>
     </row>
@@ -6682,10 +6772,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH31" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用枪柄 7' M Moderate，偏 crankbait 节奏，Crankbait、Shad Crank、Squarebill 要保持泳层和回收速度；挂底或碰障后用竿身缓冲带过。</v>
       </c>
       <c r="AI31" t="str" s="2">
-        <v/>
+        <v>Crankbait / Shad Crank / Squarebill / Lipless Crankbait / Chatterbait</v>
       </c>
       <c r="AJ31" t="str" s="2">
         <v/>
@@ -6694,21 +6784,24 @@
         <v/>
       </c>
       <c r="AL31" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM31" t="str" s="2">
-        <v>卷阻饵 / 搜索</v>
+        <v>淡水 Bass / 开阔水域卷阻搜索 / 7'Crankbait</v>
       </c>
       <c r="AN31" t="str" s="2">
-        <v>适合 crankbait 和 moving bait / 卷收节奏稳定 / 搜索型作钓更顺手</v>
+        <v>进阶泛用 / 7' M crankbait / shad 专项</v>
       </c>
       <c r="AO31" t="str" s="2">
+        <v>进阶泛用枪柄 7' M Moderate，8-17 lb线组配置下，Crankbait、Shad Crank、Squarebill 优先，稳定卷收和挂鱼缓冲比快速刺鱼更关键；适合沿草边、石滩和浅中层水线搜索。</v>
+      </c>
+      <c r="AP31" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta® Winch Casting rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP31" t="str" s="2">
+      <c r="AQ31" t="str" s="2">
         <v>Feature: 30-ton graphite for a lightweight design</v>
       </c>
-      <c r="AQ31" t="str" s="2">
+      <c r="AR31" t="str" s="2">
         <v>UPC: 36282038585</v>
       </c>
     </row>
@@ -6813,10 +6906,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH32" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量直柄 6'8" ML Moderate Fast，用于清水或轻压场更自然，Down Shot、Neko Rig、Wacky Rig 动作要小，补刺靠节奏和线张力。</v>
       </c>
       <c r="AI32" t="str" s="1">
-        <v/>
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
       </c>
       <c r="AJ32" t="str" s="1">
         <v/>
@@ -6825,21 +6918,24 @@
         <v/>
       </c>
       <c r="AL32" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM32" t="str" s="1">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线和轻压场 / 6'8"直柄精细</v>
       </c>
       <c r="AN32" t="str" s="1">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>竞赛轻量 / 6'8" ML Down Shot / Neko 精细</v>
       </c>
       <c r="AO32" t="str" s="1">
+        <v>竞赛轻量直柄 6'8" ML Moderate Fast，4-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，适合细线慢拖、轻抖和看线；微弱咬口反馈比强力控鱼更重要。</v>
+      </c>
+      <c r="AP32" t="str" s="1">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP32" t="str" s="1">
+      <c r="AQ32" t="str" s="1">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ32" t="str" s="1">
+      <c r="AR32" t="str" s="1">
         <v>UPC: 36282038776</v>
       </c>
     </row>
@@ -6944,10 +7040,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH33" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量直柄 7' ML Fast，适合细线慢节奏，Down Shot、Neko Rig、Wacky Rig 以控松线和读轻口为主，不适合粗暴硬拔。</v>
       </c>
       <c r="AI33" t="str" s="1">
-        <v/>
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
       </c>
       <c r="AJ33" t="str" s="1">
         <v/>
@@ -6956,21 +7052,24 @@
         <v/>
       </c>
       <c r="AL33" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM33" t="str" s="1">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线和轻压场 / 7'直柄精细</v>
       </c>
       <c r="AN33" t="str" s="1">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>竞赛轻量 / 7' ML Down Shot / Neko 精细</v>
       </c>
       <c r="AO33" t="str" s="1">
+        <v>竞赛轻量直柄 7' ML Fast，6-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，适合细线慢拖、轻抖和看线；微弱咬口反馈比强力控鱼更重要。</v>
+      </c>
+      <c r="AP33" t="str" s="1">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP33" t="str" s="1">
+      <c r="AQ33" t="str" s="1">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ33" t="str" s="1">
+      <c r="AR33" t="str" s="1">
         <v>UPC: 36282038783</v>
       </c>
     </row>
@@ -7075,10 +7174,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH34" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量直柄 7' M Fast，用于 Neko / Wacky 更自然，Neko Rig、Wacky Rig、Down Shot 可覆盖轻量打点和慢节奏搜索，别用太重的饵压竿。</v>
       </c>
       <c r="AI34" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ34" t="str" s="1">
         <v/>
@@ -7087,21 +7186,24 @@
         <v/>
       </c>
       <c r="AL34" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM34" t="str" s="1">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'直柄泛用</v>
       </c>
       <c r="AN34" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>竞赛轻量 / 7' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO34" t="str" s="1">
+        <v>竞赛轻量直柄 7' M Fast，8-14 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP34" t="str" s="1">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP34" t="str" s="1">
+      <c r="AQ34" t="str" s="1">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ34" t="str" s="1">
+      <c r="AR34" t="str" s="1">
         <v>UPC: 36282038790</v>
       </c>
     </row>
@@ -7206,10 +7308,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH35" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量直柄 7' MH Fast，比常规精细竿更能承受稍重钓组，Shaky Head、Free Rig、Neko Rig 适合开阔结构和深一点的标点，仍以控线为先。</v>
       </c>
       <c r="AI35" t="str" s="1">
-        <v/>
+        <v>Shaky Head / Free Rig / Neko Rig / Small Swimbait / Swim Jig</v>
       </c>
       <c r="AJ35" t="str" s="1">
         <v/>
@@ -7218,21 +7320,24 @@
         <v/>
       </c>
       <c r="AL35" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM35" t="str" s="1">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开阔结构与稍重精细 / 7'直柄强精细</v>
       </c>
       <c r="AN35" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7' MH Shaky Head / Free Rig 直柄</v>
       </c>
       <c r="AO35" t="str" s="1">
+        <v>竞赛轻量直柄 7' MH Fast，10-17 lb线组配置下，Shaky Head、Free Rig、Neko Rig 优先，适合比常规精细更重的钓组；保留直柄控线优势，同时有更好的刺鱼余量。</v>
+      </c>
+      <c r="AP35" t="str" s="1">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP35" t="str" s="1">
+      <c r="AQ35" t="str" s="1">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ35" t="str" s="1">
+      <c r="AR35" t="str" s="1">
         <v>UPC: 36282038806</v>
       </c>
     </row>
@@ -7337,10 +7442,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH36" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量直柄 7'1" M Fast，适合细线控饵，Neko Rig、Wacky Rig、Down Shot 的重点是松线管理和轻口判断，硬饵只做短距离补充。</v>
       </c>
       <c r="AI36" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ36" t="str" s="1">
         <v/>
@@ -7349,21 +7454,24 @@
         <v/>
       </c>
       <c r="AL36" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM36" t="str" s="1">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'1"直柄泛用</v>
       </c>
       <c r="AN36" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>竞赛轻量 / 7'1" M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO36" t="str" s="1">
+        <v>竞赛轻量直柄 7'1" M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP36" t="str" s="1">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP36" t="str" s="1">
+      <c r="AQ36" t="str" s="1">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ36" t="str" s="1">
+      <c r="AR36" t="str" s="1">
         <v>UPC: 36282038813</v>
       </c>
     </row>
@@ -7468,10 +7576,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH37" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量直柄 7'4" M Fast，用于 Neko / Wacky 更自然，Neko Rig、Wacky Rig、Down Shot 可覆盖轻量打点和慢节奏搜索，别用太重的饵压竿。</v>
       </c>
       <c r="AI37" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ37" t="str" s="1">
         <v/>
@@ -7480,21 +7588,24 @@
         <v/>
       </c>
       <c r="AL37" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM37" t="str" s="1">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'4"直柄泛用</v>
       </c>
       <c r="AN37" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>竞赛轻量 / 7'4" M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO37" t="str" s="1">
+        <v>竞赛轻量直柄 7'4" M Fast，8-14 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP37" t="str" s="1">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP37" t="str" s="1">
+      <c r="AQ37" t="str" s="1">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ37" t="str" s="1">
+      <c r="AR37" t="str" s="1">
         <v>UPC: 36282038820</v>
       </c>
     </row>
@@ -7599,10 +7710,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH38" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用直柄 6'6" M Fast，偏直柄精细泛用，Neko Rig、Wacky Rig、Down Shot 适合岸边轻量软饵；小 Minnow 只是补充搜索路线。</v>
       </c>
       <c r="AI38" t="str" s="2">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ38" t="str" s="2">
         <v/>
@@ -7611,21 +7722,24 @@
         <v/>
       </c>
       <c r="AL38" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM38" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 6'6"直柄泛用</v>
       </c>
       <c r="AN38" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 6'6" M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO38" t="str" s="2">
+        <v>进阶泛用直柄 6'6" M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP38" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP38" t="str" s="2">
+      <c r="AQ38" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ38" t="str" s="2">
+      <c r="AR38" t="str" s="2">
         <v>UPC: 36282038370</v>
       </c>
     </row>
@@ -7730,10 +7844,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH39" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用直柄 6'6" M Fast，适合细线控饵，Neko Rig、Wacky Rig、Down Shot 的重点是松线管理和轻口判断，硬饵只做短距离补充。</v>
       </c>
       <c r="AI39" t="str" s="2">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ39" t="str" s="2">
         <v/>
@@ -7742,21 +7856,24 @@
         <v/>
       </c>
       <c r="AL39" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM39" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 6'6"直柄泛用</v>
       </c>
       <c r="AN39" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 6'6" M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO39" t="str" s="2">
+        <v>进阶泛用直柄 6'6" M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP39" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP39" t="str" s="2">
+      <c r="AQ39" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ39" t="str" s="2">
+      <c r="AR39" t="str" s="2">
         <v>UPC: 36282038387</v>
       </c>
     </row>
@@ -7861,10 +7978,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH40" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用直柄 6'6" MH Fast，比常规精细竿更能承受稍重钓组，Shaky Head、Free Rig、Neko Rig 适合开阔结构和深一点的标点，仍以控线为先。</v>
       </c>
       <c r="AI40" t="str" s="2">
-        <v/>
+        <v>Shaky Head / Free Rig / Neko Rig / Small Swimbait / Swim Jig</v>
       </c>
       <c r="AJ40" t="str" s="2">
         <v/>
@@ -7873,21 +7990,24 @@
         <v/>
       </c>
       <c r="AL40" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM40" t="str" s="2">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开阔结构与稍重精细 / 6'6"直柄强精细</v>
       </c>
       <c r="AN40" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 6'6" MH Shaky Head / Free Rig 直柄</v>
       </c>
       <c r="AO40" t="str" s="2">
+        <v>进阶泛用直柄 6'6" MH Fast，8-14 lb线组配置下，Shaky Head、Free Rig、Neko Rig 优先，适合比常规精细更重的钓组；保留直柄控线优势，同时有更好的刺鱼余量。</v>
+      </c>
+      <c r="AP40" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP40" t="str" s="2">
+      <c r="AQ40" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ40" t="str" s="2">
+      <c r="AR40" t="str" s="2">
         <v>UPC: 36282038394</v>
       </c>
     </row>
@@ -7992,10 +8112,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH41" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用直柄 6'6" MH Fast，比常规精细竿更能承受稍重钓组，Shaky Head、Free Rig、Neko Rig 适合开阔结构和深一点的标点，仍以控线为先。</v>
       </c>
       <c r="AI41" t="str" s="2">
-        <v/>
+        <v>Shaky Head / Free Rig / Neko Rig / Small Swimbait / Swim Jig</v>
       </c>
       <c r="AJ41" t="str" s="2">
         <v/>
@@ -8004,21 +8124,24 @@
         <v/>
       </c>
       <c r="AL41" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM41" t="str" s="2">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开阔结构与稍重精细 / 6'6"直柄强精细</v>
       </c>
       <c r="AN41" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 6'6" MH Shaky Head / Free Rig 直柄</v>
       </c>
       <c r="AO41" t="str" s="2">
+        <v>进阶泛用直柄 6'6" MH Fast，8-14 lb线组配置下，Shaky Head、Free Rig、Neko Rig 优先，适合比常规精细更重的钓组；保留直柄控线优势，同时有更好的刺鱼余量。</v>
+      </c>
+      <c r="AP41" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP41" t="str" s="2">
+      <c r="AQ41" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ41" t="str" s="2">
+      <c r="AR41" t="str" s="2">
         <v>UPC: 36282038400</v>
       </c>
     </row>
@@ -8123,10 +8246,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH42" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用直柄 6'9" ML Fast，适合细线慢节奏，Down Shot、Neko Rig、Wacky Rig 以控松线和读轻口为主，不适合粗暴硬拔。</v>
       </c>
       <c r="AI42" t="str" s="2">
-        <v/>
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
       </c>
       <c r="AJ42" t="str" s="2">
         <v/>
@@ -8135,21 +8258,24 @@
         <v/>
       </c>
       <c r="AL42" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM42" t="str" s="2">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线和轻压场 / 6'9"直柄精细</v>
       </c>
       <c r="AN42" t="str" s="2">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>进阶泛用 / 6'9" ML Down Shot / Neko 精细</v>
       </c>
       <c r="AO42" t="str" s="2">
+        <v>进阶泛用直柄 6'9" ML Fast，6-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，适合细线慢拖、轻抖和看线；微弱咬口反馈比强力控鱼更重要。</v>
+      </c>
+      <c r="AP42" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP42" t="str" s="2">
+      <c r="AQ42" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ42" t="str" s="2">
+      <c r="AR42" t="str" s="2">
         <v>UPC: 36282038417</v>
       </c>
     </row>
@@ -8254,10 +8380,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH43" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用直柄 6'9" ML Fast，用于清水或轻压场更自然，Down Shot、Neko Rig、Wacky Rig 动作要小，补刺靠节奏和线张力。</v>
       </c>
       <c r="AI43" t="str" s="2">
-        <v/>
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
       </c>
       <c r="AJ43" t="str" s="2">
         <v/>
@@ -8266,21 +8392,24 @@
         <v/>
       </c>
       <c r="AL43" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM43" t="str" s="2">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线和轻压场 / 6'9"直柄精细</v>
       </c>
       <c r="AN43" t="str" s="2">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>进阶泛用 / 6'9" ML Down Shot / Neko 精细</v>
       </c>
       <c r="AO43" t="str" s="2">
+        <v>进阶泛用直柄 6'9" ML Fast，6-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，适合细线慢拖、轻抖和看线；微弱咬口反馈比强力控鱼更重要。</v>
+      </c>
+      <c r="AP43" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP43" t="str" s="2">
+      <c r="AQ43" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ43" t="str" s="2">
+      <c r="AR43" t="str" s="2">
         <v>UPC: 36282038424</v>
       </c>
     </row>
@@ -8385,10 +8514,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH44" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用直柄 7' M Fast，偏直柄精细泛用，Neko Rig、Wacky Rig、Down Shot 适合岸边轻量软饵；小 Minnow 只是补充搜索路线。</v>
       </c>
       <c r="AI44" t="str" s="2">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ44" t="str" s="2">
         <v/>
@@ -8397,21 +8526,24 @@
         <v/>
       </c>
       <c r="AL44" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM44" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'直柄泛用</v>
       </c>
       <c r="AN44" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 7' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO44" t="str" s="2">
+        <v>进阶泛用直柄 7' M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP44" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP44" t="str" s="2">
+      <c r="AQ44" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ44" t="str" s="2">
+      <c r="AR44" t="str" s="2">
         <v>UPC: 36282038431</v>
       </c>
     </row>
@@ -8516,10 +8648,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH45" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用直柄 7' M Fast，适合细线控饵，Neko Rig、Wacky Rig、Down Shot 的重点是松线管理和轻口判断，硬饵只做短距离补充。</v>
       </c>
       <c r="AI45" t="str" s="2">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ45" t="str" s="2">
         <v/>
@@ -8528,21 +8660,24 @@
         <v/>
       </c>
       <c r="AL45" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM45" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'直柄泛用</v>
       </c>
       <c r="AN45" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 7' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO45" t="str" s="2">
+        <v>进阶泛用直柄 7' M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP45" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP45" t="str" s="2">
+      <c r="AQ45" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ45" t="str" s="2">
+      <c r="AR45" t="str" s="2">
         <v>UPC: 36282038448</v>
       </c>
     </row>
@@ -8647,10 +8782,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH46" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用直柄 7' MH Fast，比常规精细竿更能承受稍重钓组，Shaky Head、Free Rig、Neko Rig 适合开阔结构和深一点的标点，仍以控线为先。</v>
       </c>
       <c r="AI46" t="str" s="2">
-        <v/>
+        <v>Shaky Head / Free Rig / Neko Rig / Small Swimbait / Swim Jig</v>
       </c>
       <c r="AJ46" t="str" s="2">
         <v/>
@@ -8659,21 +8794,24 @@
         <v/>
       </c>
       <c r="AL46" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM46" t="str" s="2">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开阔结构与稍重精细 / 7'直柄强精细</v>
       </c>
       <c r="AN46" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 7' MH Shaky Head / Free Rig 直柄</v>
       </c>
       <c r="AO46" t="str" s="2">
+        <v>进阶泛用直柄 7' MH Fast，8-14 lb线组配置下，Shaky Head、Free Rig、Neko Rig 优先，适合比常规精细更重的钓组；保留直柄控线优势，同时有更好的刺鱼余量。</v>
+      </c>
+      <c r="AP46" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP46" t="str" s="2">
+      <c r="AQ46" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ46" t="str" s="2">
+      <c r="AR46" t="str" s="2">
         <v>UPC: 36282038455</v>
       </c>
     </row>
@@ -8778,10 +8916,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH47" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>进阶泛用直柄 7'4" M Fast，偏直柄精细泛用，Neko Rig、Wacky Rig、Down Shot 适合岸边轻量软饵；小 Minnow 只是补充搜索路线。</v>
       </c>
       <c r="AI47" t="str" s="2">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ47" t="str" s="2">
         <v/>
@@ -8790,21 +8928,24 @@
         <v/>
       </c>
       <c r="AL47" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM47" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'4"直柄泛用</v>
       </c>
       <c r="AN47" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 7'4" M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO47" t="str" s="2">
+        <v>进阶泛用直柄 7'4" M Fast，8-14 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP47" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series provide a lightweight and well-balanced feel with superior components to deliver on the water every time.</v>
       </c>
-      <c r="AP47" t="str" s="2">
+      <c r="AQ47" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ47" t="str" s="2">
+      <c r="AR47" t="str" s="2">
         <v>UPC: 36282038462</v>
       </c>
     </row>
@@ -8909,10 +9050,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH48" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Flipping 枪柄 7'6" MH Fast，用于 cover 内打点时，Flipping Jig 和 Punching 要压低弹道进洞；刺鱼后直接把鱼带离草根和木桩。</v>
       </c>
       <c r="AI48" t="str" s="1">
-        <v/>
+        <v>Flipping Jig / Punching / Heavy Texas / Creature Bait / Heavy Cover Jig</v>
       </c>
       <c r="AJ48" t="str" s="1">
         <v/>
@@ -8921,21 +9062,24 @@
         <v/>
       </c>
       <c r="AL48" t="str" s="1">
-        <v>淡水 / bass / 重障碍</v>
+        <v/>
       </c>
       <c r="AM48" t="str" s="1">
-        <v>Flipping / cover 打点</v>
+        <v>淡水 Bass / 草洞木桩与密集 cover / 7'6"重障碍打点</v>
       </c>
       <c r="AN48" t="str" s="1">
-        <v>适合重障碍打点 / 近距离投放更稳 / 强控鱼能力更突出</v>
+        <v>Flipping / 7'6" MH Flipping / Punching 打点</v>
       </c>
       <c r="AO48" t="str" s="1">
+        <v>Flipping 枪柄 7'6" MH Fast，12-20 lb线组配置下，Flipping Jig、Punching、Heavy Texas 优先，适合近距离低弹道入障；12-20 lb 线组下刺鱼和把鱼拉离 cover 是主要价值。</v>
+      </c>
+      <c r="AP48" t="str" s="1">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP48" t="str" s="1">
+      <c r="AQ48" t="str" s="1">
         <v>Feature: 36-ton graphite with Powerlux™ 200 resin technology for ultra-light thin blanks with superior impact and fracture resistance​</v>
       </c>
-      <c r="AQ48" t="str" s="1">
+      <c r="AR48" t="str" s="1">
         <v>UPC: 36282038738</v>
       </c>
     </row>
@@ -9040,10 +9184,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH49" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 6'10" M Moderate Fast，偏浅中层移动饵，Crankbait、Shad、Minnow 适合沿岸线稳定卷收；软饵只作为慢口补充，不是主轴。</v>
       </c>
       <c r="AI49" t="str" s="2">
-        <v/>
+        <v>Crankbait / Shad / Minnow / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ49" t="str" s="2">
         <v/>
@@ -9052,21 +9196,24 @@
         <v/>
       </c>
       <c r="AL49" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM49" t="str" s="2">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 浅中层硬饵搜索 / 6'10"移动饵泛用</v>
       </c>
       <c r="AN49" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>竞赛轻量 / 6'10" M 小 crank / minnow 搜索</v>
       </c>
       <c r="AO49" t="str" s="2">
+        <v>竞赛轻量枪柄 6'10" M Moderate Fast，8-17 lb线组配置下，Crankbait、Shad、Minnow 优先，适合沿岸线和硬物边做稳定卷收；软饵只作为鱼口慢时的补充。</v>
+      </c>
+      <c r="AP49" t="str" s="2">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP49" t="str" s="2">
+      <c r="AQ49" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ49" t="str" s="2">
+      <c r="AR49" t="str" s="2">
         <v>UPC: 36282038592</v>
       </c>
     </row>
@@ -9171,10 +9318,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH50" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7' M Moderate Fast，以稳定卷收为核心，Crankbait、Shad Crank、Squarebill 适合沿草边、石滩和浅中层水线搜索，短咬时不宜立刻大幅扬竿。</v>
       </c>
       <c r="AI50" t="str" s="2">
-        <v/>
+        <v>Crankbait / Shad Crank / Squarebill / Lipless Crankbait / Chatterbait</v>
       </c>
       <c r="AJ50" t="str" s="2">
         <v/>
@@ -9183,21 +9330,24 @@
         <v/>
       </c>
       <c r="AL50" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM50" t="str" s="2">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 开阔水域卷阻搜索 / 7'Crankbait</v>
       </c>
       <c r="AN50" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>竞赛轻量 / 7' M crankbait / shad 专项</v>
       </c>
       <c r="AO50" t="str" s="2">
+        <v>竞赛轻量枪柄 7' M Moderate Fast，8-17 lb线组配置下，Crankbait、Shad Crank、Squarebill 优先，稳定卷收和挂鱼缓冲比快速刺鱼更关键；适合沿草边、石滩和浅中层水线搜索。</v>
+      </c>
+      <c r="AP50" t="str" s="2">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP50" t="str" s="2">
+      <c r="AQ50" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ50" t="str" s="2">
+      <c r="AR50" t="str" s="2">
         <v>UPC: 36282038615</v>
       </c>
     </row>
@@ -9302,10 +9452,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH51" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7' M Fast，抛投负担较轻，Texas Rig、Free Rig、Rubber Jig 适合短中距离打点；需要搜索时再切 Spinnerbait / Chatterbait。</v>
       </c>
       <c r="AI51" t="str" s="2">
-        <v/>
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ51" t="str" s="2">
         <v/>
@@ -9314,21 +9464,24 @@
         <v/>
       </c>
       <c r="AL51" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM51" t="str" s="2">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 7'轻中量底操</v>
       </c>
       <c r="AN51" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>竞赛轻量 / 7' M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO51" t="str" s="2">
+        <v>竞赛轻量枪柄 7' M Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP51" t="str" s="2">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP51" t="str" s="2">
+      <c r="AQ51" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ51" t="str" s="2">
+      <c r="AR51" t="str" s="2">
         <v>UPC: 36282038608</v>
       </c>
     </row>
@@ -9433,10 +9586,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH52" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7' MH Moderate Fast，偏 crankbait 节奏，Deep Crankbait、Crankbait、Lipless Crankbait 要保持泳层和回收速度；挂底或碰障后用竿身缓冲带过。</v>
       </c>
       <c r="AI52" t="str" s="2">
-        <v/>
+        <v>Deep Crankbait / Crankbait / Lipless Crankbait / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ52" t="str" s="2">
         <v/>
@@ -9445,21 +9598,24 @@
         <v/>
       </c>
       <c r="AL52" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM52" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 开阔水域卷阻搜索 / 7'Crankbait</v>
       </c>
       <c r="AN52" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7' MH crankbait / shad 专项</v>
       </c>
       <c r="AO52" t="str" s="2">
+        <v>竞赛轻量枪柄 7' MH Moderate Fast，12-20 lb线组配置下，Deep Crankbait、Crankbait、Lipless Crankbait 优先，稳定卷收和挂鱼缓冲比快速刺鱼更关键；适合沿草边、石滩和浅中层水线搜索。</v>
+      </c>
+      <c r="AP52" t="str" s="2">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP52" t="str" s="2">
+      <c r="AQ52" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ52" t="str" s="2">
+      <c r="AR52" t="str" s="2">
         <v>UPC: 36282038639</v>
       </c>
     </row>
@@ -9564,10 +9720,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH53" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7' MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI53" t="str" s="2">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ53" t="str" s="2">
         <v/>
@@ -9576,21 +9732,24 @@
         <v/>
       </c>
       <c r="AL53" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM53" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'中重型底操</v>
       </c>
       <c r="AN53" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7' MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO53" t="str" s="2">
+        <v>竞赛轻量枪柄 7' MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP53" t="str" s="2">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP53" t="str" s="2">
+      <c r="AQ53" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ53" t="str" s="2">
+      <c r="AR53" t="str" s="2">
         <v>UPC: 36282038622</v>
       </c>
     </row>
@@ -9695,10 +9854,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH54" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7'1" M Fast，更偏 BFS 轻量路线，Small Minnow、Shad、Small Crankbait 可以在岸边障碍和小水面之间切换，重点是出线轻和落点准。</v>
       </c>
       <c r="AI54" t="str" s="2">
-        <v/>
+        <v>Small Minnow / Shad / Small Crankbait / Neko Rig / No Sinker</v>
       </c>
       <c r="AJ54" t="str" s="2">
         <v/>
@@ -9707,21 +9866,24 @@
         <v/>
       </c>
       <c r="AL54" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM54" t="str" s="2">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 小场地细线轻饵 / 7'1"枪柄 BFS</v>
       </c>
       <c r="AN54" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>竞赛轻量 / 7'1" M BFS 精细轻饵</v>
       </c>
       <c r="AO54" t="str" s="2">
+        <v>竞赛轻量枪柄 7'1" M Fast，8-15 lb线组配置下，Small Minnow、Shad、Small Crankbait 优先，低弹道轻抛和细线控线是核心；鱼口变轻时可在小硬饵与软饵间切换。</v>
+      </c>
+      <c r="AP54" t="str" s="2">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP54" t="str" s="2">
+      <c r="AQ54" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ54" t="str" s="2">
+      <c r="AR54" t="str" s="2">
         <v>UPC: 36282038653</v>
       </c>
     </row>
@@ -9826,10 +9988,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH55" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7'1" ML Moderate Fast，核心是轻饵启动和控线，Small Minnow、Shad、Small Crankbait 适合小标点低弹道抛投，软硬饵切换要控制饵重上限。</v>
       </c>
       <c r="AI55" t="str" s="2">
-        <v/>
+        <v>Small Minnow / Shad / Small Crankbait / Neko Rig / No Sinker</v>
       </c>
       <c r="AJ55" t="str" s="2">
         <v/>
@@ -9838,21 +10000,24 @@
         <v/>
       </c>
       <c r="AL55" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM55" t="str" s="2">
-        <v>枪柄精细轻饵</v>
+        <v>淡水 Bass / 小场地细线轻饵 / 7'1"枪柄 BFS</v>
       </c>
       <c r="AN55" t="str" s="2">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>竞赛轻量 / 7'1" ML BFS 精细轻饵</v>
       </c>
       <c r="AO55" t="str" s="2">
+        <v>竞赛轻量枪柄 7'1" ML Moderate Fast，6-12 lb线组配置下，Small Minnow、Shad、Small Crankbait 优先，低弹道轻抛和细线控线是核心；鱼口变轻时可在小硬饵与软饵间切换。</v>
+      </c>
+      <c r="AP55" t="str" s="2">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP55" t="str" s="2">
+      <c r="AQ55" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ55" t="str" s="2">
+      <c r="AR55" t="str" s="2">
         <v>UPC: 36282038646</v>
       </c>
     </row>
@@ -9957,10 +10122,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH56" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7'1" MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI56" t="str" s="2">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ56" t="str" s="2">
         <v/>
@@ -9969,21 +10134,24 @@
         <v/>
       </c>
       <c r="AL56" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM56" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'1"中重型底操</v>
       </c>
       <c r="AN56" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7'1" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO56" t="str" s="2">
+        <v>竞赛轻量枪柄 7'1" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP56" t="str" s="2">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP56" t="str" s="2">
+      <c r="AQ56" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ56" t="str" s="2">
+      <c r="AR56" t="str" s="2">
         <v>UPC: 36282038660</v>
       </c>
     </row>
@@ -10088,10 +10256,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH57" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7'3" MH Fast，更适合 Texas / Jig 路线，Texas Rig、Rubber Jig、Free Rig 先保证落点和读底，鱼活性高时可切移动饵提高覆盖。</v>
       </c>
       <c r="AI57" t="str" s="2">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ57" t="str" s="2">
         <v/>
@@ -10100,21 +10268,24 @@
         <v/>
       </c>
       <c r="AL57" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM57" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'3"中重型底操</v>
       </c>
       <c r="AN57" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7'3" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO57" t="str" s="2">
+        <v>竞赛轻量枪柄 7'3" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP57" t="str" s="2">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP57" t="str" s="2">
+      <c r="AQ57" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ57" t="str" s="2">
+      <c r="AR57" t="str" s="2">
         <v>UPC: 36282038677</v>
       </c>
     </row>
@@ -10219,10 +10390,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH58" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7'3" H Fast，用于强结构打点时，Heavy Texas、Rubber Jig、Football Jig 要让饵贴底通过障碍；中鱼后用竿腰把鱼带出标点。</v>
       </c>
       <c r="AI58" t="str" s="2">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ58" t="str" s="2">
         <v/>
@@ -10231,21 +10402,24 @@
         <v/>
       </c>
       <c r="AL58" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM58" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'3"强力底操</v>
       </c>
       <c r="AN58" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7'3" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO58" t="str" s="2">
+        <v>竞赛轻量枪柄 7'3" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP58" t="str" s="2">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP58" t="str" s="2">
+      <c r="AQ58" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ58" t="str" s="2">
+      <c r="AR58" t="str" s="2">
         <v>UPC: 36282038684</v>
       </c>
     </row>
@@ -10350,10 +10524,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH59" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7'4" MH Moderate，适合浅水窗口期，Topwater Plug、Jerkbait、Walking Bait 走停和抽停要留节奏；无表层口时可转 Spinnerbait / Chatterbait 搜索。</v>
       </c>
       <c r="AI59" t="str" s="2">
-        <v/>
+        <v>Topwater Plug / Jerkbait / Walking Bait / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ59" t="str" s="2">
         <v/>
@@ -10362,21 +10536,24 @@
         <v/>
       </c>
       <c r="AL59" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM59" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 浅水窗口期与草边表层 / 7'4"Topwater</v>
       </c>
       <c r="AN59" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7'4" MH topwater / jerkbait 搜索</v>
       </c>
       <c r="AO59" t="str" s="2">
+        <v>竞赛轻量枪柄 7'4" MH Moderate，10-20 lb线组配置下，Topwater Plug、Jerkbait、Walking Bait 优先，适合走停、抽停和短距离精准抛投；窗口期过后可切回移动饵搜索。</v>
+      </c>
+      <c r="AP59" t="str" s="2">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP59" t="str" s="2">
+      <c r="AQ59" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ59" t="str" s="2">
+      <c r="AR59" t="str" s="2">
         <v>UPC: 36282038707</v>
       </c>
     </row>
@@ -10481,10 +10658,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH60" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7'4" MH Moderate Fast，适合草边、浑水和硬物边搜索；Chatterbait、Swim Jig、Spinnerbait 需要稳定回收负荷，碰草后轻抖脱出。</v>
       </c>
       <c r="AI60" t="str" s="2">
-        <v/>
+        <v>Chatterbait / Swim Jig / Spinnerbait / Vibration / Lipless Crankbait</v>
       </c>
       <c r="AJ60" t="str" s="2">
         <v/>
@@ -10493,21 +10670,24 @@
         <v/>
       </c>
       <c r="AL60" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM60" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 草边与浑水搜索 / 7'4"bladed jig</v>
       </c>
       <c r="AN60" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7'4" MH Chatterbait / Swim Jig</v>
       </c>
       <c r="AO60" t="str" s="2">
+        <v>竞赛轻量枪柄 7'4" MH Moderate Fast，12-20 lb线组配置下，Chatterbait、Swim Jig、Spinnerbait 优先，适合带震动感的中速搜索；通过草边和硬物边时需要稳定回收负荷。</v>
+      </c>
+      <c r="AP60" t="str" s="2">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP60" t="str" s="2">
+      <c r="AQ60" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ60" t="str" s="2">
+      <c r="AR60" t="str" s="2">
         <v>UPC: 36282038691</v>
       </c>
     </row>
@@ -10612,10 +10792,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH61" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7'6" MH Moderate Fast，以稳定卷收为核心，Deep Crankbait、Crankbait、Lipless Crankbait 适合沿草边、石滩和浅中层水线搜索，短咬时不宜立刻大幅扬竿。</v>
       </c>
       <c r="AI61" t="str" s="2">
-        <v/>
+        <v>Deep Crankbait / Crankbait / Lipless Crankbait / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ61" t="str" s="2">
         <v/>
@@ -10624,21 +10804,24 @@
         <v/>
       </c>
       <c r="AL61" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM61" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 开阔水域卷阻搜索 / 7'6"Crankbait</v>
       </c>
       <c r="AN61" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7'6" MH crankbait / shad 专项</v>
       </c>
       <c r="AO61" t="str" s="2">
+        <v>竞赛轻量枪柄 7'6" MH Moderate Fast，12-20 lb线组配置下，Deep Crankbait、Crankbait、Lipless Crankbait 优先，稳定卷收和挂鱼缓冲比快速刺鱼更关键；适合沿草边、石滩和浅中层水线搜索。</v>
+      </c>
+      <c r="AP61" t="str" s="2">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP61" t="str" s="2">
+      <c r="AQ61" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ61" t="str" s="2">
+      <c r="AR61" t="str" s="2">
         <v>UPC: 36282038721</v>
       </c>
     </row>
@@ -10743,10 +10926,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH62" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7'6" MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI62" t="str" s="2">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ62" t="str" s="2">
         <v/>
@@ -10755,21 +10938,24 @@
         <v/>
       </c>
       <c r="AL62" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM62" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'6"中重型底操</v>
       </c>
       <c r="AN62" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7'6" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO62" t="str" s="2">
+        <v>竞赛轻量枪柄 7'6" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP62" t="str" s="2">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP62" t="str" s="2">
+      <c r="AQ62" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ62" t="str" s="2">
+      <c r="AR62" t="str" s="2">
         <v>UPC: 36282038714</v>
       </c>
     </row>
@@ -10874,10 +11060,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH63" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7'6" H Fast，用于强结构打点时，Heavy Texas、Rubber Jig、Football Jig 要让饵贴底通过障碍；中鱼后用竿腰把鱼带出标点。</v>
       </c>
       <c r="AI63" t="str" s="2">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ63" t="str" s="2">
         <v/>
@@ -10886,21 +11072,24 @@
         <v/>
       </c>
       <c r="AL63" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM63" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'6"强力底操</v>
       </c>
       <c r="AN63" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7'6" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO63" t="str" s="2">
+        <v>竞赛轻量枪柄 7'6" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP63" t="str" s="2">
         <v>Bringing tournament performance backed by the Veritas name. Veritas Tournament rods deliver exceptional performance​ offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP63" t="str" s="2">
+      <c r="AQ63" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ63" t="str" s="2">
+      <c r="AR63" t="str" s="2">
         <v>UPC: 36282038745</v>
       </c>
     </row>
@@ -11005,10 +11194,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH64" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>强负荷枪柄 7'5" MH Moderate Fast，以中大型泳饵扇形搜索为主，Swimbait、Soft Swimbait、Big Bait 适合慢收或贴结构通过，竿身缓冲比快速抽打更重要。</v>
       </c>
       <c r="AI64" t="str" s="1">
-        <v/>
+        <v>Swimbait / Soft Swimbait / Big Bait / Heavy Spinnerbait / Swim Jig</v>
       </c>
       <c r="AJ64" t="str" s="1">
         <v/>
@@ -11017,21 +11206,24 @@
         <v/>
       </c>
       <c r="AL64" t="str" s="1">
-        <v>淡水 / bass / 大饵强力</v>
+        <v/>
       </c>
       <c r="AM64" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 开阔水域中大型泳饵 / 7'5"搜索</v>
       </c>
       <c r="AN64" t="str" s="1">
-        <v>面向大饵、大目标和高负荷控鱼 / 强度余量更足 / 适合重饵或大鱼场景筛选</v>
+        <v>强负荷 / 7'5" MH Swimbait 兼重型移动饵</v>
       </c>
       <c r="AO64" t="str" s="1">
+        <v>强负荷枪柄 7'5" MH Moderate Fast，12-20 lb线组配置下，Swimbait、Soft Swimbait、Big Bait 优先，适合大水面扇形搜索；比底操竿更看重回收稳定和中鱼后持续施压。</v>
+      </c>
+      <c r="AP64" t="str" s="1">
         <v>Beast™ series rods have been designed to be paired with the Beast™ Reels to throw big baits for large powerful fish. The series utilizes an innovative two-piece design, as well as specialized tapers, specifically for swimbaits for bass up to large “pounder style” baits for muskie.</v>
       </c>
-      <c r="AP64" t="str" s="1">
+      <c r="AQ64" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ64" t="str" s="1">
+      <c r="AR64" t="str" s="1">
         <v>UPC: 36282038257</v>
       </c>
     </row>
@@ -11136,10 +11328,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH65" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>强负荷枪柄 7'9" H Moderate Fast，适合 Swimbait 路线，Swimbait、Soft Swimbait、Big Bait 可覆盖开阔水和草边外侧，重点保持泳姿和回收张力。</v>
       </c>
       <c r="AI65" t="str" s="1">
-        <v/>
+        <v>Swimbait / Soft Swimbait / Big Bait / Heavy Spinnerbait / Swim Jig</v>
       </c>
       <c r="AJ65" t="str" s="1">
         <v/>
@@ -11148,21 +11340,24 @@
         <v/>
       </c>
       <c r="AL65" t="str" s="1">
-        <v>淡水 / bass / 大饵强力</v>
+        <v/>
       </c>
       <c r="AM65" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 开阔水域中大型泳饵 / 7'9"搜索</v>
       </c>
       <c r="AN65" t="str" s="1">
-        <v>面向大饵、大目标和高负荷控鱼 / 强度余量更足 / 适合重饵或大鱼场景筛选</v>
+        <v>强负荷 / 7'9" H Swimbait 兼重型移动饵</v>
       </c>
       <c r="AO65" t="str" s="1">
+        <v>强负荷枪柄 7'9" H Moderate Fast，15-25 lb线组配置下，Swimbait、Soft Swimbait、Big Bait 优先，适合大水面扇形搜索；比底操竿更看重回收稳定和中鱼后持续施压。</v>
+      </c>
+      <c r="AP65" t="str" s="1">
         <v>Beast™ series rods have been designed to be paired with the Beast™ Reels to throw big baits for large powerful fish. The series utilizes an innovative two-piece design, as well as specialized tapers, specifically for swimbaits for bass up to large “pounder style” baits for muskie.</v>
       </c>
-      <c r="AP65" t="str" s="1">
+      <c r="AQ65" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ65" t="str" s="1">
+      <c r="AR65" t="str" s="1">
         <v>UPC: 36282038264</v>
       </c>
     </row>
@@ -11267,10 +11462,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH66" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>强负荷枪柄 8' XH Fast，适合开阔水域压水层慢收；Big Bait、Large Soft Swimbait、Muskie Swimbait 回收阻力高，抛投节奏和中鱼后的持续施压要更稳。</v>
       </c>
       <c r="AI66" t="str" s="1">
-        <v/>
+        <v>Big Bait / Large Soft Swimbait / Muskie Swimbait / Bucktail</v>
       </c>
       <c r="AJ66" t="str" s="1">
         <v/>
@@ -11279,21 +11474,24 @@
         <v/>
       </c>
       <c r="AL66" t="str" s="1">
-        <v>淡水 / bass / 大饵强力</v>
+        <v/>
       </c>
       <c r="AM66" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 大水面 Swimbait 搜索 / 8'强力远投</v>
       </c>
       <c r="AN66" t="str" s="1">
-        <v>面向大饵、大目标和高负荷控鱼 / 强度余量更足 / 适合重饵或大鱼场景筛选</v>
+        <v>强负荷 / 8' XH Big Bait / Swimbait 强力搜索</v>
       </c>
       <c r="AO66" t="str" s="1">
+        <v>强负荷枪柄 8' XH Fast，15-30 lb线组配置下，Big Bait、Large Soft Swimbait、Muskie Swimbait 优先，适合开阔水域压水层慢收；竿身余量用于承受大饵回收阻力和中鱼后控鱼。</v>
+      </c>
+      <c r="AP66" t="str" s="1">
         <v>Beast™ series rods have been designed to be paired with the Beast™ Reels to throw big baits for large powerful fish. The series utilizes an innovative two-piece design, as well as specialized tapers, specifically for swimbaits for bass up to large “pounder style” baits for muskie.</v>
       </c>
-      <c r="AP66" t="str" s="1">
+      <c r="AQ66" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ66" t="str" s="1">
+      <c r="AR66" t="str" s="1">
         <v>UPC: 36282038271</v>
       </c>
     </row>
@@ -11398,10 +11596,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH67" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>强负荷枪柄 8'6" H Fast，承担高负荷大饵，Muskie Swimbait、Pounder Soft Swimbait、Big Bait 要留足挥竿空间；40-80 lb 线组 下更重视连续抛投后的控鱼稳定。</v>
       </c>
       <c r="AI67" t="str" s="1">
-        <v/>
+        <v>Muskie Swimbait / Pounder Soft Swimbait / Big Bait / Bucktail</v>
       </c>
       <c r="AJ67" t="str" s="1">
         <v/>
@@ -11410,21 +11608,24 @@
         <v/>
       </c>
       <c r="AL67" t="str" s="1">
-        <v>淡水 / bass / 大饵强力</v>
+        <v/>
       </c>
       <c r="AM67" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水大型掠食鱼 / 大水面重型大饵 / 8'6"高负荷抛投</v>
       </c>
       <c r="AN67" t="str" s="1">
-        <v>面向大饵、大目标和高负荷控鱼 / 强度余量更足 / 适合重饵或大鱼场景筛选</v>
+        <v>强负荷 / 8'6" H Muskie / Pounder 大饵竿</v>
       </c>
       <c r="AO67" t="str" s="1">
+        <v>强负荷枪柄 8'6" H Fast，40-80 lb线组配置下，Muskie Swimbait、Pounder Soft Swimbait、Big Bait 优先，重饵连续抛投和大鱼控线压力更高；40-80 lb 线组更适合高负荷控鱼。</v>
+      </c>
+      <c r="AP67" t="str" s="1">
         <v>Beast™ series rods have been designed to be paired with the Beast™ Reels to throw big baits for large powerful fish. The series utilizes an innovative two-piece design, as well as specialized tapers, specifically for swimbaits for bass up to large “pounder style” baits for muskie.</v>
       </c>
-      <c r="AP67" t="str" s="1">
+      <c r="AQ67" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ67" t="str" s="1">
+      <c r="AR67" t="str" s="1">
         <v>UPC: 36282038288</v>
       </c>
     </row>
@@ -11529,10 +11730,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH68" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>强负荷枪柄 9'5" XXH Fast，承担高负荷大饵，Muskie Swimbait、Pounder Soft Swimbait、Big Bait 要留足挥竿空间；80-100 lb 线组 下更重视连续抛投后的控鱼稳定。</v>
       </c>
       <c r="AI68" t="str" s="1">
-        <v/>
+        <v>Muskie Swimbait / Pounder Soft Swimbait / Big Bait / Bucktail</v>
       </c>
       <c r="AJ68" t="str" s="1">
         <v/>
@@ -11541,21 +11742,24 @@
         <v/>
       </c>
       <c r="AL68" t="str" s="1">
-        <v>淡水 / bass / 大饵强力</v>
+        <v/>
       </c>
       <c r="AM68" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水大型掠食鱼 / 大水面重型大饵 / 9'5"高负荷抛投</v>
       </c>
       <c r="AN68" t="str" s="1">
-        <v>面向大饵、大目标和高负荷控鱼 / 强度余量更足 / 适合重饵或大鱼场景筛选</v>
+        <v>强负荷 / 9'5" XXH Muskie / Pounder 大饵竿</v>
       </c>
       <c r="AO68" t="str" s="1">
+        <v>强负荷枪柄 9'5" XXH Fast，80-100 lb线组配置下，Muskie Swimbait、Pounder Soft Swimbait、Big Bait 优先，重饵连续抛投和大鱼控线压力更高；80-100 lb 线组更适合高负荷控鱼。</v>
+      </c>
+      <c r="AP68" t="str" s="1">
         <v>Beast™ series rods have been designed to be paired with the Beast™ Reels to throw big baits for large powerful fish. The series utilizes an innovative two-piece design, as well as specialized tapers, specifically for swimbaits for bass up to large “pounder style” baits for muskie.</v>
       </c>
-      <c r="AP68" t="str" s="1">
+      <c r="AQ68" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ68" t="str" s="1">
+      <c r="AR68" t="str" s="1">
         <v>UPC: 36282038295</v>
       </c>
     </row>
@@ -11660,10 +11864,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH69" t="str" s="2">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>强负荷直柄 7' ML Fast，按6-12 lb 线组控制饵重，Small Swimbait、Soft Swimbait、Underspin 更适合慢收和轻负荷搜索，操作边界应放在小型软泳饵和轻负荷连续搜索。</v>
       </c>
       <c r="AI69" t="str" s="2">
-        <v/>
+        <v>Small Swimbait / Soft Swimbait / Underspin / Swim Jig / Spinnerbait</v>
       </c>
       <c r="AJ69" t="str" s="2">
         <v/>
@@ -11672,21 +11876,24 @@
         <v/>
       </c>
       <c r="AL69" t="str" s="2">
-        <v>淡水 / bass / 大饵强力</v>
+        <v/>
       </c>
       <c r="AM69" t="str" s="2">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开放水域小型软泳饵 / 7'直柄轻负荷搜索</v>
       </c>
       <c r="AN69" t="str" s="2">
-        <v>面向大饵、大目标和高负荷控鱼 / 强度余量更足 / 适合重饵或大鱼场景筛选</v>
+        <v>强负荷 / 7' ML 小型 Swimbait / Underspin</v>
       </c>
       <c r="AO69" t="str" s="2">
+        <v>强负荷直柄 7' ML Fast，6-12 lb线组配置下，Small Swimbait、Soft Swimbait、Underspin 优先，按直柄和6-12 lb 线组控制饵重；适合慢收小泳饵和轻负荷连续搜索。</v>
+      </c>
+      <c r="AP69" t="str" s="2">
         <v>Beast™ series rods have been designed to be paired with the Beast™ Reels to throw big baits for large powerful fish. Constructed from 30-ton graphite and specialized tapers, these rods were specifically designed for throwing swimbaits for bass and up to large “pounder style” baits for muskie.</v>
       </c>
-      <c r="AP69" t="str" s="2">
+      <c r="AQ69" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ69" t="str" s="2">
+      <c r="AR69" t="str" s="2">
         <v>UPC: 36282038301</v>
       </c>
     </row>
@@ -11791,10 +11998,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH70" t="str" s="2">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>强负荷直柄 7' M Fast，按8-17 lb 线组控制饵重，Soft Swimbait、Small Swimbait、Underspin 更适合慢收和轻负荷搜索，操作边界应放在小型软泳饵和轻负荷连续搜索。</v>
       </c>
       <c r="AI70" t="str" s="2">
-        <v/>
+        <v>Soft Swimbait / Small Swimbait / Underspin / Swim Jig / Spinnerbait</v>
       </c>
       <c r="AJ70" t="str" s="2">
         <v/>
@@ -11803,21 +12010,24 @@
         <v/>
       </c>
       <c r="AL70" t="str" s="2">
-        <v>淡水 / bass / 大饵强力</v>
+        <v/>
       </c>
       <c r="AM70" t="str" s="2">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开放水域小型软泳饵 / 7'直柄轻负荷搜索</v>
       </c>
       <c r="AN70" t="str" s="2">
-        <v>面向大饵、大目标和高负荷控鱼 / 强度余量更足 / 适合重饵或大鱼场景筛选</v>
+        <v>强负荷 / 7' M 小型 Swimbait / Underspin</v>
       </c>
       <c r="AO70" t="str" s="2">
+        <v>强负荷直柄 7' M Fast，8-17 lb线组配置下，Soft Swimbait、Small Swimbait、Underspin 优先，按直柄和8-17 lb 线组控制饵重；适合慢收小泳饵和轻负荷连续搜索。</v>
+      </c>
+      <c r="AP70" t="str" s="2">
         <v>Beast™ series rods have been designed to be paired with the Beast™ Reels to throw big baits for large powerful fish. Constructed from 30-ton graphite and specialized tapers, these rods were specifically designed for throwing swimbaits for bass and up to large “pounder style” baits for muskie.</v>
       </c>
-      <c r="AP70" t="str" s="2">
+      <c r="AQ70" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ70" t="str" s="2">
+      <c r="AR70" t="str" s="2">
         <v>UPC: 36282038318</v>
       </c>
     </row>
@@ -11922,10 +12132,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH71" t="str" s="2">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>强负荷直柄 7' MH Fast，按12-20 lb 线组控制饵重，Soft Swimbait、Small Swimbait、Underspin 更适合慢收和轻负荷搜索，操作边界应放在小型软泳饵和轻负荷连续搜索。</v>
       </c>
       <c r="AI71" t="str" s="2">
-        <v/>
+        <v>Soft Swimbait / Small Swimbait / Underspin / Swim Jig / Spinnerbait</v>
       </c>
       <c r="AJ71" t="str" s="2">
         <v/>
@@ -11934,21 +12144,24 @@
         <v/>
       </c>
       <c r="AL71" t="str" s="2">
-        <v>淡水 / bass / 大饵强力</v>
+        <v/>
       </c>
       <c r="AM71" t="str" s="2">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开放水域小型软泳饵 / 7'直柄轻负荷搜索</v>
       </c>
       <c r="AN71" t="str" s="2">
-        <v>面向大饵、大目标和高负荷控鱼 / 强度余量更足 / 适合重饵或大鱼场景筛选</v>
+        <v>强负荷 / 7' MH 小型 Swimbait / Underspin</v>
       </c>
       <c r="AO71" t="str" s="2">
+        <v>强负荷直柄 7' MH Fast，12-20 lb线组配置下，Soft Swimbait、Small Swimbait、Underspin 优先，按直柄和12-20 lb 线组控制饵重；适合慢收小泳饵和轻负荷连续搜索。</v>
+      </c>
+      <c r="AP71" t="str" s="2">
         <v>Beast™ series rods have been designed to be paired with the Beast™ Reels to throw big baits for large powerful fish. Constructed from 30-ton graphite and specialized tapers, these rods were specifically designed for throwing swimbaits for bass and up to large “pounder style” baits for muskie.</v>
       </c>
-      <c r="AP71" t="str" s="2">
+      <c r="AQ71" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ71" t="str" s="2">
+      <c r="AR71" t="str" s="2">
         <v>UPC: 36282038325</v>
       </c>
     </row>
@@ -12053,10 +12266,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH72" t="str" s="2">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>强负荷直柄 7'6" MH Fast，按12-20 lb 线组控制饵重，Soft Swimbait、Small Swimbait、Underspin 更适合慢收和轻负荷搜索，操作边界应放在小型软泳饵和轻负荷连续搜索。</v>
       </c>
       <c r="AI72" t="str" s="2">
-        <v/>
+        <v>Soft Swimbait / Small Swimbait / Underspin / Swim Jig / Spinnerbait</v>
       </c>
       <c r="AJ72" t="str" s="2">
         <v/>
@@ -12065,21 +12278,24 @@
         <v/>
       </c>
       <c r="AL72" t="str" s="2">
-        <v>淡水 / bass / 大饵强力</v>
+        <v/>
       </c>
       <c r="AM72" t="str" s="2">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开放水域小型软泳饵 / 7'6"直柄轻负荷搜索</v>
       </c>
       <c r="AN72" t="str" s="2">
-        <v>面向大饵、大目标和高负荷控鱼 / 强度余量更足 / 适合重饵或大鱼场景筛选</v>
+        <v>强负荷 / 7'6" MH 小型 Swimbait / Underspin</v>
       </c>
       <c r="AO72" t="str" s="2">
+        <v>强负荷直柄 7'6" MH Fast，12-20 lb线组配置下，Soft Swimbait、Small Swimbait、Underspin 优先，按直柄和12-20 lb 线组控制饵重；适合慢收小泳饵和轻负荷连续搜索。</v>
+      </c>
+      <c r="AP72" t="str" s="2">
         <v>Beast™ series rods have been designed to be paired with the Beast™ Reels to throw big baits for large powerful fish. Constructed from 30-ton graphite and specialized tapers, these rods were specifically designed for throwing swimbaits for bass and up to large “pounder style” baits for muskie.</v>
       </c>
-      <c r="AP72" t="str" s="2">
+      <c r="AQ72" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ72" t="str" s="2">
+      <c r="AR72" t="str" s="2">
         <v>UPC: 36282038332</v>
       </c>
     </row>
@@ -12184,10 +12400,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH73" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 6'10" M Moderate Fast，以稳定卷收为核心，Crankbait、Shad Crank、Squarebill 适合沿草边、石滩和浅中层水线搜索，短咬时不宜立刻大幅扬竿。</v>
       </c>
       <c r="AI73" t="str" s="1">
-        <v/>
+        <v>Crankbait / Shad Crank / Squarebill / Lipless Crankbait / Chatterbait</v>
       </c>
       <c r="AJ73" t="str" s="1">
         <v/>
@@ -12196,21 +12412,24 @@
         <v/>
       </c>
       <c r="AL73" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM73" t="str" s="1">
-        <v>卷阻饵 / 搜索</v>
+        <v>淡水 Bass / 开阔水域卷阻搜索 / 6'10"Crankbait</v>
       </c>
       <c r="AN73" t="str" s="1">
-        <v>适合 crankbait 和 moving bait / 卷收节奏稳定 / 搜索型作钓更顺手</v>
+        <v>轻量高感 / 6'10" M crankbait / shad 专项</v>
       </c>
       <c r="AO73" t="str" s="1">
+        <v>轻量高感枪柄 6'10" M Moderate Fast，8-17 lb线组配置下，Crankbait、Shad Crank、Squarebill 优先，稳定卷收和挂鱼缓冲比快速刺鱼更关键；适合沿草边、石滩和浅中层水线搜索。</v>
+      </c>
+      <c r="AP73" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP73" t="str" s="1">
+      <c r="AQ73" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ73" t="str" s="1">
+      <c r="AR73" t="str" s="1">
         <v>UPC: 036282736047; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -12315,10 +12534,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH74" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7' M Moderate Fast，偏 crankbait 节奏，Crankbait、Shad Crank、Squarebill 要保持泳层和回收速度；挂底或碰障后用竿身缓冲带过。</v>
       </c>
       <c r="AI74" t="str" s="1">
-        <v/>
+        <v>Crankbait / Shad Crank / Squarebill / Lipless Crankbait / Chatterbait</v>
       </c>
       <c r="AJ74" t="str" s="1">
         <v/>
@@ -12327,21 +12546,24 @@
         <v/>
       </c>
       <c r="AL74" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM74" t="str" s="1">
-        <v>卷阻饵 / 搜索</v>
+        <v>淡水 Bass / 开阔水域卷阻搜索 / 7'Crankbait</v>
       </c>
       <c r="AN74" t="str" s="1">
-        <v>适合 crankbait 和 moving bait / 卷收节奏稳定 / 搜索型作钓更顺手</v>
+        <v>轻量高感 / 7' M crankbait / shad 专项</v>
       </c>
       <c r="AO74" t="str" s="1">
+        <v>轻量高感枪柄 7' M Moderate Fast，8-17 lb线组配置下，Crankbait、Shad Crank、Squarebill 优先，稳定卷收和挂鱼缓冲比快速刺鱼更关键；适合沿草边、石滩和浅中层水线搜索。</v>
+      </c>
+      <c r="AP74" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP74" t="str" s="1">
+      <c r="AQ74" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ74" t="str" s="1">
+      <c r="AR74" t="str" s="1">
         <v>UPC: 036282736054; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -12446,10 +12668,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH75" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7' MH Moderate Fast，以稳定卷收为核心，Deep Crankbait、Crankbait、Lipless Crankbait 适合沿草边、石滩和浅中层水线搜索，短咬时不宜立刻大幅扬竿。</v>
       </c>
       <c r="AI75" t="str" s="1">
-        <v/>
+        <v>Deep Crankbait / Crankbait / Lipless Crankbait / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ75" t="str" s="1">
         <v/>
@@ -12458,21 +12680,24 @@
         <v/>
       </c>
       <c r="AL75" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM75" t="str" s="1">
-        <v>卷阻饵 / 搜索</v>
+        <v>淡水 Bass / 开阔水域卷阻搜索 / 7'Crankbait</v>
       </c>
       <c r="AN75" t="str" s="1">
-        <v>适合 crankbait 和 moving bait / 卷收节奏稳定 / 搜索型作钓更顺手</v>
+        <v>轻量高感 / 7' MH crankbait / shad 专项</v>
       </c>
       <c r="AO75" t="str" s="1">
+        <v>轻量高感枪柄 7' MH Moderate Fast，12-20 lb线组配置下，Deep Crankbait、Crankbait、Lipless Crankbait 优先，稳定卷收和挂鱼缓冲比快速刺鱼更关键；适合沿草边、石滩和浅中层水线搜索。</v>
+      </c>
+      <c r="AP75" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP75" t="str" s="1">
+      <c r="AQ75" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ75" t="str" s="1">
+      <c r="AR75" t="str" s="1">
         <v>UPC: 036282736061; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -12577,10 +12802,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH76" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Finesse 直柄 6'6" MH Fast，适合细线精细操作，Shaky Head、Neko Rig、Wacky Rig 不需要大动作抽竿，咬口判断和补刺节奏更关键。</v>
       </c>
       <c r="AI76" t="str" s="2">
-        <v/>
+        <v>Shaky Head / Neko Rig / Wacky Rig / Small Swimbait / Down Shot</v>
       </c>
       <c r="AJ76" t="str" s="2">
         <v/>
@@ -12589,21 +12814,24 @@
         <v/>
       </c>
       <c r="AL76" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM76" t="str" s="2">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线与轻压场 / 6'6"精细软饵</v>
       </c>
       <c r="AN76" t="str" s="2">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>Finesse / 6'6" MH finesse bait 精细操作</v>
       </c>
       <c r="AO76" t="str" s="2">
+        <v>Finesse 直柄 6'6" MH Fast，6-14 lb线组配置下，Shaky Head、Neko Rig、Wacky Rig 优先，重点在控松线、读轻口和小幅度控饵；6-14 lb 线组下更适合细致控线。</v>
+      </c>
+      <c r="AP76" t="str" s="2">
         <v>The Ike Signature Series Finesse Spinning Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with finesse baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Finesse Series Spinning Rod construction creates the ideal performance for lightweight, finesse focused presentations.</v>
       </c>
-      <c r="AP76" t="str" s="2">
+      <c r="AQ76" t="str" s="2">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ76" t="str" s="2">
+      <c r="AR76" t="str" s="2">
         <v>UPC: 036282118492</v>
       </c>
     </row>
@@ -12708,10 +12936,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH77" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Finesse 直柄 6'10" ML Medium Fast，用于 finesse bait 时要放慢节奏，Down Shot、Neko Rig、Wacky Rig 重在控松线、看线和小幅度牵动。</v>
       </c>
       <c r="AI77" t="str" s="2">
-        <v/>
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
       </c>
       <c r="AJ77" t="str" s="2">
         <v/>
@@ -12720,21 +12948,24 @@
         <v/>
       </c>
       <c r="AL77" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM77" t="str" s="2">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线与轻压场 / 6'10"精细软饵</v>
       </c>
       <c r="AN77" t="str" s="2">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>Finesse / 6'10" ML finesse bait 精细操作</v>
       </c>
       <c r="AO77" t="str" s="2">
+        <v>Finesse 直柄 6'10" ML Medium Fast，4-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，重点在控松线、读轻口和小幅度控饵；4-10 lb 线组下更适合细致控线。</v>
+      </c>
+      <c r="AP77" t="str" s="2">
         <v>The Ike Signature Series Finesse Spinning Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with finesse baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Finesse Series Spinning Rod construction creates the ideal performance for lightweight, finesse focused presentations.</v>
       </c>
-      <c r="AP77" t="str" s="2">
+      <c r="AQ77" t="str" s="2">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ77" t="str" s="2">
+      <c r="AR77" t="str" s="2">
         <v>UPC: 036282118508</v>
       </c>
     </row>
@@ -12839,10 +13070,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH78" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Finesse 直柄 7' M Fast，适合细线精细操作，Down Shot、Neko Rig、Wacky Rig 不需要大动作抽竿，咬口判断和补刺节奏更关键。</v>
       </c>
       <c r="AI78" t="str" s="2">
-        <v/>
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
       </c>
       <c r="AJ78" t="str" s="2">
         <v/>
@@ -12851,21 +13082,24 @@
         <v/>
       </c>
       <c r="AL78" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM78" t="str" s="2">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线与轻压场 / 7'精细软饵</v>
       </c>
       <c r="AN78" t="str" s="2">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>Finesse / 7' M finesse bait 精细操作</v>
       </c>
       <c r="AO78" t="str" s="2">
+        <v>Finesse 直柄 7' M Fast，6-12 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，重点在控松线、读轻口和小幅度控饵；6-12 lb 线组下更适合细致控线。</v>
+      </c>
+      <c r="AP78" t="str" s="2">
         <v>The Ike Signature Series Finesse Spinning Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with finesse baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Finesse Series Spinning Rod construction creates the ideal performance for lightweight, finesse focused presentations.</v>
       </c>
-      <c r="AP78" t="str" s="2">
+      <c r="AQ78" t="str" s="2">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ78" t="str" s="2">
+      <c r="AR78" t="str" s="2">
         <v>UPC: 036282118515</v>
       </c>
     </row>
@@ -12970,10 +13204,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH79" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Finesse 直柄 7'4" ML Medium Fast，用于 finesse bait 时要放慢节奏，Down Shot、Neko Rig、Wacky Rig 重在控松线、看线和小幅度牵动。</v>
       </c>
       <c r="AI79" t="str" s="2">
-        <v/>
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
       </c>
       <c r="AJ79" t="str" s="2">
         <v/>
@@ -12982,21 +13216,24 @@
         <v/>
       </c>
       <c r="AL79" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM79" t="str" s="2">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线与轻压场 / 7'4"精细软饵</v>
       </c>
       <c r="AN79" t="str" s="2">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>Finesse / 7'4" ML finesse bait 精细操作</v>
       </c>
       <c r="AO79" t="str" s="2">
+        <v>Finesse 直柄 7'4" ML Medium Fast，4-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，重点在控松线、读轻口和小幅度控饵；4-10 lb 线组下更适合细致控线。</v>
+      </c>
+      <c r="AP79" t="str" s="2">
         <v>The Ike Signature Series Finesse Spinning Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with finesse baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Finesse Series Spinning Rod construction creates the ideal performance for lightweight, finesse focused presentations.</v>
       </c>
-      <c r="AP79" t="str" s="2">
+      <c r="AQ79" t="str" s="2">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ79" t="str" s="2">
+      <c r="AR79" t="str" s="2">
         <v>UPC: 036282118522</v>
       </c>
     </row>
@@ -13101,10 +13338,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH80" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Finesse 直柄 7'6" MH Fast，适合细线精细操作，Shaky Head、Neko Rig、Wacky Rig 不需要大动作抽竿，咬口判断和补刺节奏更关键。</v>
       </c>
       <c r="AI80" t="str" s="2">
-        <v/>
+        <v>Shaky Head / Neko Rig / Wacky Rig / Small Swimbait / Down Shot</v>
       </c>
       <c r="AJ80" t="str" s="2">
         <v/>
@@ -13113,21 +13350,24 @@
         <v/>
       </c>
       <c r="AL80" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM80" t="str" s="2">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线与轻压场 / 7'6"精细软饵</v>
       </c>
       <c r="AN80" t="str" s="2">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>Finesse / 7'6" MH finesse bait 精细操作</v>
       </c>
       <c r="AO80" t="str" s="2">
+        <v>Finesse 直柄 7'6" MH Fast，6-14 lb线组配置下，Shaky Head、Neko Rig、Wacky Rig 优先，重点在控松线、读轻口和小幅度控饵；6-14 lb 线组下更适合细致控线。</v>
+      </c>
+      <c r="AP80" t="str" s="2">
         <v>The Ike Signature Series Finesse Spinning Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with finesse baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Finesse Series Spinning Rod construction creates the ideal performance for lightweight, finesse focused presentations.</v>
       </c>
-      <c r="AP80" t="str" s="2">
+      <c r="AQ80" t="str" s="2">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ80" t="str" s="2">
+      <c r="AR80" t="str" s="2">
         <v>UPC: 036282118539</v>
       </c>
     </row>
@@ -13232,10 +13472,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH81" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Finesse 直柄 7' ML/M Fast，用于 finesse bait 时要放慢节奏，Down Shot、Neko Rig、Wacky Rig 重在控松线、看线和小幅度牵动。</v>
       </c>
       <c r="AI81" t="str" s="2">
-        <v/>
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
       </c>
       <c r="AJ81" t="str" s="2">
         <v/>
@@ -13244,21 +13484,24 @@
         <v/>
       </c>
       <c r="AL81" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM81" t="str" s="2">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线与轻压场 / 7'精细软饵</v>
       </c>
       <c r="AN81" t="str" s="2">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>Finesse / 7' ML/M finesse bait 精细操作</v>
       </c>
       <c r="AO81" t="str" s="2">
+        <v>Finesse 直柄 7' ML/M Fast，6-12 lb / 8-14 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，重点在控松线、读轻口和小幅度控饵；6-12 lb / 8-14 lb 线组下更适合细致控线。</v>
+      </c>
+      <c r="AP81" t="str" s="2">
         <v>The Ike Signature Series Finesse Spinning Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with finesse baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Finesse Series Spinning Rod construction creates the ideal performance for lightweight, finesse focused presentations.</v>
       </c>
-      <c r="AP81" t="str" s="2">
+      <c r="AQ81" t="str" s="2">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ81" t="str" s="2">
+      <c r="AR81" t="str" s="2">
         <v>UPC: 036282034549</v>
       </c>
     </row>
@@ -13363,10 +13606,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH82" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感直柄 6'6" M Fast，用于 Neko / Wacky 更自然，Neko Rig、Wacky Rig、Down Shot 可覆盖轻量打点和慢节奏搜索，别用太重的饵压竿。</v>
       </c>
       <c r="AI82" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ82" t="str" s="1">
         <v/>
@@ -13375,21 +13618,24 @@
         <v/>
       </c>
       <c r="AL82" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM82" t="str" s="1">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 6'6"直柄泛用</v>
       </c>
       <c r="AN82" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>轻量高感 / 6'6" M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO82" t="str" s="1">
+        <v>轻量高感直柄 6'6" M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP82" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP82" t="str" s="1">
+      <c r="AQ82" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ82" t="str" s="1">
+      <c r="AR82" t="str" s="1">
         <v>UPC: 036282736153; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -13494,10 +13740,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH83" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感直柄 6'6" M Fast，偏直柄精细泛用，Neko Rig、Wacky Rig、Down Shot 适合岸边轻量软饵；小 Minnow 只是补充搜索路线。</v>
       </c>
       <c r="AI83" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ83" t="str" s="1">
         <v/>
@@ -13506,21 +13752,24 @@
         <v/>
       </c>
       <c r="AL83" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM83" t="str" s="1">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 6'6"直柄泛用</v>
       </c>
       <c r="AN83" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>轻量高感 / 6'6" M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO83" t="str" s="1">
+        <v>轻量高感直柄 6'6" M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP83" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP83" t="str" s="1">
+      <c r="AQ83" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ83" t="str" s="1">
+      <c r="AR83" t="str" s="1">
         <v>UPC: 036282736160; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -13625,10 +13874,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH84" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感直柄 6'6" MH Extra Fast，比常规精细竿更能承受稍重钓组，Shaky Head、Free Rig、Neko Rig 适合开阔结构和深一点的标点，仍以控线为先。</v>
       </c>
       <c r="AI84" t="str" s="1">
-        <v/>
+        <v>Shaky Head / Free Rig / Neko Rig / Small Swimbait / Swim Jig</v>
       </c>
       <c r="AJ84" t="str" s="1">
         <v/>
@@ -13637,21 +13886,24 @@
         <v/>
       </c>
       <c r="AL84" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM84" t="str" s="1">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开阔结构与稍重精细 / 6'6"直柄强精细</v>
       </c>
       <c r="AN84" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 6'6" MH Shaky Head / Free Rig 直柄</v>
       </c>
       <c r="AO84" t="str" s="1">
+        <v>轻量高感直柄 6'6" MH Extra Fast，8-14 lb线组配置下，Shaky Head、Free Rig、Neko Rig 优先，适合比常规精细更重的钓组；保留直柄控线优势，同时有更好的刺鱼余量。</v>
+      </c>
+      <c r="AP84" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP84" t="str" s="1">
+      <c r="AQ84" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ84" t="str" s="1">
+      <c r="AR84" t="str" s="1">
         <v>UPC: 036282736177; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -13756,10 +14008,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH85" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感直柄 6'6" MH Extra Fast，比常规精细竿更能承受稍重钓组，Shaky Head、Free Rig、Neko Rig 适合开阔结构和深一点的标点，仍以控线为先。</v>
       </c>
       <c r="AI85" t="str" s="1">
-        <v/>
+        <v>Shaky Head / Free Rig / Neko Rig / Small Swimbait / Swim Jig</v>
       </c>
       <c r="AJ85" t="str" s="1">
         <v/>
@@ -13768,21 +14020,24 @@
         <v/>
       </c>
       <c r="AL85" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM85" t="str" s="1">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开阔结构与稍重精细 / 6'6"直柄强精细</v>
       </c>
       <c r="AN85" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 6'6" MH Shaky Head / Free Rig 直柄</v>
       </c>
       <c r="AO85" t="str" s="1">
+        <v>轻量高感直柄 6'6" MH Extra Fast，8-14 lb线组配置下，Shaky Head、Free Rig、Neko Rig 优先，适合比常规精细更重的钓组；保留直柄控线优势，同时有更好的刺鱼余量。</v>
+      </c>
+      <c r="AP85" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP85" t="str" s="1">
+      <c r="AQ85" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ85" t="str" s="1">
+      <c r="AR85" t="str" s="1">
         <v>UPC: 036282736184; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -13887,10 +14142,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH86" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感直柄 6'9" ML Fast，适合细线慢节奏，Down Shot、Neko Rig、Wacky Rig 以控松线和读轻口为主，不适合粗暴硬拔。</v>
       </c>
       <c r="AI86" t="str" s="1">
-        <v/>
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
       </c>
       <c r="AJ86" t="str" s="1">
         <v/>
@@ -13899,21 +14154,24 @@
         <v/>
       </c>
       <c r="AL86" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM86" t="str" s="1">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线和轻压场 / 6'9"直柄精细</v>
       </c>
       <c r="AN86" t="str" s="1">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>轻量高感 / 6'9" ML Down Shot / Neko 精细</v>
       </c>
       <c r="AO86" t="str" s="1">
+        <v>轻量高感直柄 6'9" ML Fast，6-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，适合细线慢拖、轻抖和看线；微弱咬口反馈比强力控鱼更重要。</v>
+      </c>
+      <c r="AP86" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP86" t="str" s="1">
+      <c r="AQ86" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ86" t="str" s="1">
+      <c r="AR86" t="str" s="1">
         <v>UPC: 036282736191; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -14018,10 +14276,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH87" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感直柄 7' M Fast，适合细线控饵，Neko Rig、Wacky Rig、Down Shot 的重点是松线管理和轻口判断，硬饵只做短距离补充。</v>
       </c>
       <c r="AI87" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ87" t="str" s="1">
         <v/>
@@ -14030,21 +14288,24 @@
         <v/>
       </c>
       <c r="AL87" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM87" t="str" s="1">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'直柄泛用</v>
       </c>
       <c r="AN87" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>轻量高感 / 7' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO87" t="str" s="1">
+        <v>轻量高感直柄 7' M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP87" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP87" t="str" s="1">
+      <c r="AQ87" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ87" t="str" s="1">
+      <c r="AR87" t="str" s="1">
         <v>UPC: 036282736207; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -14149,10 +14410,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH88" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感直柄 7' M Fast，用于 Neko / Wacky 更自然，Neko Rig、Wacky Rig、Down Shot 可覆盖轻量打点和慢节奏搜索，别用太重的饵压竿。</v>
       </c>
       <c r="AI88" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ88" t="str" s="1">
         <v/>
@@ -14161,21 +14422,24 @@
         <v/>
       </c>
       <c r="AL88" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM88" t="str" s="1">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'直柄泛用</v>
       </c>
       <c r="AN88" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>轻量高感 / 7' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO88" t="str" s="1">
+        <v>轻量高感直柄 7' M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP88" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP88" t="str" s="1">
+      <c r="AQ88" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ88" t="str" s="1">
+      <c r="AR88" t="str" s="1">
         <v>UPC: 036282736214; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -14280,10 +14544,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH89" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感直柄 7' MH Extra Fast，比常规精细竿更能承受稍重钓组，Shaky Head、Free Rig、Neko Rig 适合开阔结构和深一点的标点，仍以控线为先。</v>
       </c>
       <c r="AI89" t="str" s="1">
-        <v/>
+        <v>Shaky Head / Free Rig / Neko Rig / Small Swimbait / Swim Jig</v>
       </c>
       <c r="AJ89" t="str" s="1">
         <v/>
@@ -14292,21 +14556,24 @@
         <v/>
       </c>
       <c r="AL89" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM89" t="str" s="1">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开阔结构与稍重精细 / 7'直柄强精细</v>
       </c>
       <c r="AN89" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 7' MH Shaky Head / Free Rig 直柄</v>
       </c>
       <c r="AO89" t="str" s="1">
+        <v>轻量高感直柄 7' MH Extra Fast，8-14 lb线组配置下，Shaky Head、Free Rig、Neko Rig 优先，适合比常规精细更重的钓组；保留直柄控线优势，同时有更好的刺鱼余量。</v>
+      </c>
+      <c r="AP89" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP89" t="str" s="1">
+      <c r="AQ89" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ89" t="str" s="1">
+      <c r="AR89" t="str" s="1">
         <v>UPC: 036282736221; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -14411,10 +14678,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH90" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感直柄 7'6" M Fast，适合细线控饵，Neko Rig、Wacky Rig、Down Shot 的重点是松线管理和轻口判断，硬饵只做短距离补充。</v>
       </c>
       <c r="AI90" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ90" t="str" s="1">
         <v/>
@@ -14423,21 +14690,24 @@
         <v/>
       </c>
       <c r="AL90" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM90" t="str" s="1">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'6"直柄泛用</v>
       </c>
       <c r="AN90" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>轻量高感 / 7'6" M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO90" t="str" s="1">
+        <v>轻量高感直柄 7'6" M Fast，8-14 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP90" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP90" t="str" s="1">
+      <c r="AQ90" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ90" t="str" s="1">
+      <c r="AR90" t="str" s="1">
         <v>UPC: 036282736238; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -14542,10 +14812,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH91" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7'6" MH Fast，适合草面搜索和重 cover 控鱼，Frog、Punching、Heavy Texas 的重点是抛准、等口和出障速度。</v>
       </c>
       <c r="AI91" t="str" s="2">
-        <v/>
+        <v>Frog / Punching / Heavy Texas / Swim Jig / Heavy Cover Jig</v>
       </c>
       <c r="AJ91" t="str" s="2">
         <v/>
@@ -14554,21 +14824,24 @@
         <v/>
       </c>
       <c r="AL91" t="str" s="2">
-        <v>淡水 / bass / 重障碍</v>
+        <v/>
       </c>
       <c r="AM91" t="str" s="2">
-        <v>Frog / 强障碍</v>
+        <v>淡水 Bass / 浮草草垫与浅水 cover / 7'6"Frog</v>
       </c>
       <c r="AN91" t="str" s="2">
-        <v>适合 Frog 和草区障碍 / 控鱼力量更足 / 出鱼效率优先</v>
+        <v>轻量高感 / 7'6" MH Frog / cover 强控鱼</v>
       </c>
       <c r="AO91" t="str" s="2">
+        <v>轻量高感枪柄 7'6" MH Fast，12-25 lb线组配置下，Frog、Punching、Heavy Texas 优先，草面开口后需要快速收线和压住鱼；兼顾 Punching 时更看重腰力和容错。</v>
+      </c>
+      <c r="AP91" t="str" s="2">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP91" t="str" s="2">
+      <c r="AQ91" t="str" s="2">
         <v>Feature: Powerlux® 100 delivers a 15% stronger* and 5% lighter** rod, while remaining lightweight and well balanced</v>
       </c>
-      <c r="AQ91" t="str" s="2">
+      <c r="AR91" t="str" s="2">
         <v>UPC: 036282736016; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -14673,10 +14946,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH92" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 6'6" M Fast，抛投负担较轻，Texas Rig、Free Rig、Rubber Jig 适合短中距离打点；需要搜索时再切 Spinnerbait / Chatterbait。</v>
       </c>
       <c r="AI92" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ92" t="str" s="1">
         <v/>
@@ -14685,21 +14958,24 @@
         <v/>
       </c>
       <c r="AL92" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM92" t="str" s="1">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 6'6"轻中量底操</v>
       </c>
       <c r="AN92" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>轻量高感 / 6'6" M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO92" t="str" s="1">
+        <v>轻量高感枪柄 6'6" M Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP92" t="str" s="1">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP92" t="str" s="1">
+      <c r="AQ92" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ92" t="str" s="1">
+      <c r="AR92" t="str" s="1">
         <v>UPC: 036282735880; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -14804,10 +15080,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH93" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 6'6" M Extra Fast，适合轻中量底操，Texas Rig、Free Rig、Rubber Jig 可以打岸边硬物和稀疏 cover；移动饵只是活性高时的补充。</v>
       </c>
       <c r="AI93" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ93" t="str" s="1">
         <v/>
@@ -14816,21 +15092,24 @@
         <v/>
       </c>
       <c r="AL93" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM93" t="str" s="1">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 6'6"轻中量底操</v>
       </c>
       <c r="AN93" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>轻量高感 / 6'6" M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO93" t="str" s="1">
+        <v>轻量高感枪柄 6'6" M Extra Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP93" t="str" s="1">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP93" t="str" s="1">
+      <c r="AQ93" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ93" t="str" s="1">
+      <c r="AR93" t="str" s="1">
         <v>UPC: 036282735897; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -14935,10 +15214,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH94" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 6'6" MH Extra Fast，用于 cover 外缘和硬结构慢拖，Texas Rig、Rubber Jig、Free Rig 的优势在刺鱼余量和软硬饵切换宽容。</v>
       </c>
       <c r="AI94" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ94" t="str" s="1">
         <v/>
@@ -14947,21 +15226,24 @@
         <v/>
       </c>
       <c r="AL94" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM94" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 6'6"中重型底操</v>
       </c>
       <c r="AN94" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 6'6" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO94" t="str" s="1">
+        <v>轻量高感枪柄 6'6" MH Extra Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP94" t="str" s="1">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP94" t="str" s="1">
+      <c r="AQ94" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ94" t="str" s="1">
+      <c r="AR94" t="str" s="1">
         <v>UPC: 036282735903; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -15066,10 +15348,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH95" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 6'10" ML Fast，适合细线轻饵打点，Neko Rig、Down Shot、No Sinker 要控制落点和松线；小 crank 可做短距离搜索补充。</v>
       </c>
       <c r="AI95" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Small Crankbait</v>
       </c>
       <c r="AJ95" t="str" s="1">
         <v/>
@@ -15078,21 +15360,24 @@
         <v/>
       </c>
       <c r="AL95" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM95" t="str" s="1">
-        <v>枪柄精细轻饵</v>
+        <v>淡水 Bass / 小场地轻线打点 / 6'10"枪柄精细轻饵</v>
       </c>
       <c r="AN95" t="str" s="1">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>轻量高感 / 6'10" ML Neko / No Sinker 轻量打点</v>
       </c>
       <c r="AO95" t="str" s="1">
+        <v>轻量高感枪柄 6'10" ML Fast，6-12 lb线组配置下，Neko Rig、Down Shot、No Sinker 优先，适合小标点低弹道抛投；小 crank 只作为补充搜索路线。</v>
+      </c>
+      <c r="AP95" t="str" s="1">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP95" t="str" s="1">
+      <c r="AQ95" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ95" t="str" s="1">
+      <c r="AR95" t="str" s="1">
         <v>UPC: 036282735910; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -15197,10 +15482,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH96" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 6'10" M Fast，抛投负担较轻，Texas Rig、Free Rig、Rubber Jig 适合短中距离打点；需要搜索时再切 Spinnerbait / Chatterbait。</v>
       </c>
       <c r="AI96" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ96" t="str" s="1">
         <v/>
@@ -15209,21 +15494,24 @@
         <v/>
       </c>
       <c r="AL96" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM96" t="str" s="1">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 6'10"轻中量底操</v>
       </c>
       <c r="AN96" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>轻量高感 / 6'10" M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO96" t="str" s="1">
+        <v>轻量高感枪柄 6'10" M Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP96" t="str" s="1">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP96" t="str" s="1">
+      <c r="AQ96" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ96" t="str" s="1">
+      <c r="AR96" t="str" s="1">
         <v>UPC: 036282735927; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -15328,10 +15616,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH97" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 6'10" MH Fast，用于 cover 外缘和硬结构慢拖，Texas Rig、Rubber Jig、Free Rig 的优势在刺鱼余量和软硬饵切换宽容。</v>
       </c>
       <c r="AI97" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ97" t="str" s="1">
         <v/>
@@ -15340,21 +15628,24 @@
         <v/>
       </c>
       <c r="AL97" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM97" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 6'10"中重型底操</v>
       </c>
       <c r="AN97" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 6'10" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO97" t="str" s="1">
+        <v>轻量高感枪柄 6'10" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP97" t="str" s="1">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP97" t="str" s="1">
+      <c r="AQ97" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ97" t="str" s="1">
+      <c r="AR97" t="str" s="1">
         <v>UPC: 036282735934; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -15459,10 +15750,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH98" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7' M Fast，抛投负担较轻，Texas Rig、Free Rig、Rubber Jig 适合短中距离打点；需要搜索时再切 Spinnerbait / Chatterbait。</v>
       </c>
       <c r="AI98" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ98" t="str" s="1">
         <v/>
@@ -15471,21 +15762,24 @@
         <v/>
       </c>
       <c r="AL98" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM98" t="str" s="1">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 7'轻中量底操</v>
       </c>
       <c r="AN98" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>轻量高感 / 7' M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO98" t="str" s="1">
+        <v>轻量高感枪柄 7' M Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP98" t="str" s="1">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP98" t="str" s="1">
+      <c r="AQ98" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ98" t="str" s="1">
+      <c r="AR98" t="str" s="1">
         <v>UPC: 036282735941; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -15590,10 +15884,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH99" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7' MH Extra Fast，更适合 Texas / Jig 路线，Texas Rig、Rubber Jig、Free Rig 先保证落点和读底，鱼活性高时可切移动饵提高覆盖。</v>
       </c>
       <c r="AI99" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ99" t="str" s="1">
         <v/>
@@ -15602,21 +15896,24 @@
         <v/>
       </c>
       <c r="AL99" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM99" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'中重型底操</v>
       </c>
       <c r="AN99" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 7' MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO99" t="str" s="1">
+        <v>轻量高感枪柄 7' MH Extra Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP99" t="str" s="1">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP99" t="str" s="1">
+      <c r="AQ99" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ99" t="str" s="1">
+      <c r="AR99" t="str" s="1">
         <v>UPC: 036282735958; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -15721,10 +16018,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH100" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7' H Fast，用于强结构打点时，Heavy Texas、Rubber Jig、Football Jig 要让饵贴底通过障碍；中鱼后用竿腰把鱼带出标点。</v>
       </c>
       <c r="AI100" t="str" s="1">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ100" t="str" s="1">
         <v/>
@@ -15733,21 +16030,24 @@
         <v/>
       </c>
       <c r="AL100" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM100" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'强力底操</v>
       </c>
       <c r="AN100" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 7' H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO100" t="str" s="1">
+        <v>轻量高感枪柄 7' H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP100" t="str" s="1">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP100" t="str" s="1">
+      <c r="AQ100" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ100" t="str" s="1">
+      <c r="AR100" t="str" s="1">
         <v>UPC: 036282735965; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -15852,10 +16152,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH101" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7'3" MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI101" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ101" t="str" s="1">
         <v/>
@@ -15864,21 +16164,24 @@
         <v/>
       </c>
       <c r="AL101" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM101" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'3"中重型底操</v>
       </c>
       <c r="AN101" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 7'3" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO101" t="str" s="1">
+        <v>轻量高感枪柄 7'3" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP101" t="str" s="1">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP101" t="str" s="1">
+      <c r="AQ101" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ101" t="str" s="1">
+      <c r="AR101" t="str" s="1">
         <v>UPC: 036282735972; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -15983,10 +16286,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH102" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7'3" H Fast，用于强结构打点时，Heavy Texas、Rubber Jig、Football Jig 要让饵贴底通过障碍；中鱼后用竿腰把鱼带出标点。</v>
       </c>
       <c r="AI102" t="str" s="1">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ102" t="str" s="1">
         <v/>
@@ -15995,21 +16298,24 @@
         <v/>
       </c>
       <c r="AL102" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM102" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'3"强力底操</v>
       </c>
       <c r="AN102" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 7'3" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO102" t="str" s="1">
+        <v>轻量高感枪柄 7'3" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP102" t="str" s="1">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP102" t="str" s="1">
+      <c r="AQ102" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ102" t="str" s="1">
+      <c r="AR102" t="str" s="1">
         <v>UPC: 036282735989; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -16114,10 +16420,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH103" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7'4" MH Fast，用于 cover 外缘和硬结构慢拖，Texas Rig、Rubber Jig、Free Rig 的优势在刺鱼余量和软硬饵切换宽容。</v>
       </c>
       <c r="AI103" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ103" t="str" s="1">
         <v/>
@@ -16126,21 +16432,24 @@
         <v/>
       </c>
       <c r="AL103" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM103" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'4"中重型底操</v>
       </c>
       <c r="AN103" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 7'4" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO103" t="str" s="1">
+        <v>轻量高感枪柄 7'4" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP103" t="str" s="1">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP103" t="str" s="1">
+      <c r="AQ103" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ103" t="str" s="1">
+      <c r="AR103" t="str" s="1">
         <v>UPC: 036282735996; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -16245,10 +16554,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH104" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7'6" MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI104" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ104" t="str" s="1">
         <v/>
@@ -16257,21 +16566,24 @@
         <v/>
       </c>
       <c r="AL104" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM104" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'6"中重型底操</v>
       </c>
       <c r="AN104" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 7'6" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO104" t="str" s="1">
+        <v>轻量高感枪柄 7'6" MH Fast，12-25 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP104" t="str" s="1">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP104" t="str" s="1">
+      <c r="AQ104" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ104" t="str" s="1">
+      <c r="AR104" t="str" s="1">
         <v>UPC: 036282736009; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -16376,10 +16688,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH105" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7'6" H Fast，偏重线底操，Heavy Texas、Rubber Jig、Football Jig 适合木桩、石堆和厚草边慢拖，重点是读底后稳定刺鱼。</v>
       </c>
       <c r="AI105" t="str" s="1">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ105" t="str" s="1">
         <v/>
@@ -16388,21 +16700,24 @@
         <v/>
       </c>
       <c r="AL105" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM105" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'6"强力底操</v>
       </c>
       <c r="AN105" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 7'6" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO105" t="str" s="1">
+        <v>轻量高感枪柄 7'6" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP105" t="str" s="1">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP105" t="str" s="1">
+      <c r="AQ105" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ105" t="str" s="1">
+      <c r="AR105" t="str" s="1">
         <v>UPC: 036282736023; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -16507,10 +16822,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH106" t="str" s="2">
-        <v>maximized casting distance with lighter lures / finesse / lightweight lure use</v>
+        <v>轻量高感直柄 7'1" M Fast，更偏 BFS 轻量路线，Neko Rig、Down Shot、No Sinker 可以在岸边障碍和小水面之间切换，重点是出线轻和落点准。</v>
       </c>
       <c r="AI106" t="str" s="2">
-        <v/>
+        <v>Neko Rig / Down Shot / No Sinker / Small Minnow / Small Crankbait</v>
       </c>
       <c r="AJ106" t="str" s="2">
         <v/>
@@ -16519,21 +16834,24 @@
         <v/>
       </c>
       <c r="AL106" t="str" s="2">
-        <v>淡水 / bass / BFS</v>
+        <v/>
       </c>
       <c r="AM106" t="str" s="2">
-        <v>精细轻饵</v>
+        <v>淡水 Bass / 小场地细线轻饵 / 7'1"直柄 BFS</v>
       </c>
       <c r="AN106" t="str" s="2">
-        <v>小饵抛投更轻松 / 精细操控直接 / 适合轻量硬饵和小型钓组</v>
+        <v>轻量高感 / 7'1" M BFS 精细轻饵</v>
       </c>
       <c r="AO106" t="str" s="2">
+        <v>轻量高感直柄 7'1" M Fast，6-12 lb线组配置下，Neko Rig、Down Shot、No Sinker 优先，低弹道轻抛和细线控线是核心；鱼口变轻时可在小硬饵与软饵间切换。</v>
+      </c>
+      <c r="AP106" t="str" s="2">
         <v>Designed specifically for BFS techniques, the next generation of Veritas rods feature Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The Veritas BFS rods use unique actions that excel at throwing ultra-lightweight lures. The Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled withtitanium alloy guides with zirconium inserts and EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP106" t="str" s="2">
+      <c r="AQ106" t="str" s="2">
         <v>Feature: Powerlux® 100 resin system allows a thin, ultra-light blank construction with superior impact and fracture resistance</v>
       </c>
-      <c r="AQ106" t="str" s="2">
+      <c r="AR106" t="str" s="2">
         <v>UPC: 036282736252; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -16638,10 +16956,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH107" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Delay 枪柄 6'6" MH Moderate，适合 reaction bait 抽停和连续卷收；Crankbait、Jerkbait、Topwater Plug 需要给鱼追咬窗口，挂鱼后靠调性缓冲短咬。</v>
       </c>
       <c r="AI107" t="str" s="1">
-        <v/>
+        <v>Crankbait / Jerkbait / Topwater Plug / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ107" t="str" s="1">
         <v/>
@@ -16650,21 +16968,24 @@
         <v/>
       </c>
       <c r="AL107" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM107" t="str" s="1">
-        <v>卷阻饵 / 搜索</v>
+        <v>淡水 Bass / 开放水域 reaction bait / 6'6"抽停搜索</v>
       </c>
       <c r="AN107" t="str" s="1">
-        <v>适合 crankbait 和 moving bait / 卷收节奏稳定 / 搜索型作钓更顺手</v>
+        <v>Delay / 6'6" MH reaction bait / moving bait</v>
       </c>
       <c r="AO107" t="str" s="1">
+        <v>Delay 枪柄 6'6" MH Moderate，12-20 lb线组配置下，Crankbait、Jerkbait、Topwater Plug 优先，抽停和连续卷收都要保持节奏；短咬时竿身缓冲能提高挂鱼稳定性。</v>
+      </c>
+      <c r="AP107" t="str" s="1">
         <v>The Ike Signature Series Delay Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with reaction baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Delay Series Casting Rod construction creates the ideal parabolic action for moving baits.</v>
       </c>
-      <c r="AP107" t="str" s="1">
+      <c r="AQ107" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ107" t="str" s="1">
+      <c r="AR107" t="str" s="1">
         <v>UPC: 036282118546</v>
       </c>
     </row>
@@ -16769,10 +17090,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH108" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Delay 枪柄 6'8" M Moderate，适合 reaction bait 抽停和连续卷收；Crankbait、Jerkbait、Topwater Plug 需要给鱼追咬窗口，挂鱼后靠调性缓冲短咬。</v>
       </c>
       <c r="AI108" t="str" s="1">
-        <v/>
+        <v>Crankbait / Jerkbait / Topwater Plug / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ108" t="str" s="1">
         <v/>
@@ -16781,21 +17102,24 @@
         <v/>
       </c>
       <c r="AL108" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM108" t="str" s="1">
-        <v>卷阻饵 / 搜索</v>
+        <v>淡水 Bass / 开放水域 reaction bait / 6'8"抽停搜索</v>
       </c>
       <c r="AN108" t="str" s="1">
-        <v>适合 crankbait 和 moving bait / 卷收节奏稳定 / 搜索型作钓更顺手</v>
+        <v>Delay / 6'8" M reaction bait / moving bait</v>
       </c>
       <c r="AO108" t="str" s="1">
+        <v>Delay 枪柄 6'8" M Moderate，6-14 lb线组配置下，Crankbait、Jerkbait、Topwater Plug 优先，抽停和连续卷收都要保持节奏；短咬时竿身缓冲能提高挂鱼稳定性。</v>
+      </c>
+      <c r="AP108" t="str" s="1">
         <v>The Ike Signature Series Delay Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with reaction baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Delay Series Casting Rod construction creates the ideal parabolic action for moving baits.</v>
       </c>
-      <c r="AP108" t="str" s="1">
+      <c r="AQ108" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ108" t="str" s="1">
+      <c r="AR108" t="str" s="1">
         <v>UPC: 036282118553</v>
       </c>
     </row>
@@ -16900,10 +17224,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH109" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Delay 枪柄 7' M Moderate，适合 reaction bait 抽停和连续卷收；Crankbait、Jerkbait、Topwater Plug 需要给鱼追咬窗口，挂鱼后靠调性缓冲短咬。</v>
       </c>
       <c r="AI109" t="str" s="1">
-        <v/>
+        <v>Crankbait / Jerkbait / Topwater Plug / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ109" t="str" s="1">
         <v/>
@@ -16912,21 +17236,24 @@
         <v/>
       </c>
       <c r="AL109" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM109" t="str" s="1">
-        <v>卷阻饵 / 搜索</v>
+        <v>淡水 Bass / 开放水域 reaction bait / 7'抽停搜索</v>
       </c>
       <c r="AN109" t="str" s="1">
-        <v>适合 crankbait 和 moving bait / 卷收节奏稳定 / 搜索型作钓更顺手</v>
+        <v>Delay / 7' M reaction bait / moving bait</v>
       </c>
       <c r="AO109" t="str" s="1">
+        <v>Delay 枪柄 7' M Moderate，10-20 lb线组配置下，Crankbait、Jerkbait、Topwater Plug 优先，抽停和连续卷收都要保持节奏；短咬时竿身缓冲能提高挂鱼稳定性。</v>
+      </c>
+      <c r="AP109" t="str" s="1">
         <v>The Ike Signature Series Delay Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with reaction baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Delay Series Casting Rod construction creates the ideal parabolic action for moving baits.</v>
       </c>
-      <c r="AP109" t="str" s="1">
+      <c r="AQ109" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ109" t="str" s="1">
+      <c r="AR109" t="str" s="1">
         <v>UPC: 036282118560</v>
       </c>
     </row>
@@ -17031,10 +17358,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH110" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Delay 枪柄 7'3" M Moderate，适合 reaction bait 抽停和连续卷收；Crankbait、Jerkbait、Topwater Plug 需要给鱼追咬窗口，挂鱼后靠调性缓冲短咬。</v>
       </c>
       <c r="AI110" t="str" s="1">
-        <v/>
+        <v>Crankbait / Jerkbait / Topwater Plug / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ110" t="str" s="1">
         <v/>
@@ -17043,21 +17370,24 @@
         <v/>
       </c>
       <c r="AL110" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM110" t="str" s="1">
-        <v>卷阻饵 / 搜索</v>
+        <v>淡水 Bass / 开放水域 reaction bait / 7'3"抽停搜索</v>
       </c>
       <c r="AN110" t="str" s="1">
-        <v>适合 crankbait 和 moving bait / 卷收节奏稳定 / 搜索型作钓更顺手</v>
+        <v>Delay / 7'3" M reaction bait / moving bait</v>
       </c>
       <c r="AO110" t="str" s="1">
+        <v>Delay 枪柄 7'3" M Moderate，12-20 lb线组配置下，Crankbait、Jerkbait、Topwater Plug 优先，抽停和连续卷收都要保持节奏；短咬时竿身缓冲能提高挂鱼稳定性。</v>
+      </c>
+      <c r="AP110" t="str" s="1">
         <v>The Ike Signature Series Delay Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with reaction baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Delay Series Casting Rod construction creates the ideal parabolic action for moving baits.</v>
       </c>
-      <c r="AP110" t="str" s="1">
+      <c r="AQ110" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ110" t="str" s="1">
+      <c r="AR110" t="str" s="1">
         <v>UPC: 036282118577</v>
       </c>
     </row>
@@ -17162,10 +17492,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH111" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Delay 枪柄 7'6" M Moderate，适合 reaction bait 抽停和连续卷收；Crankbait、Jerkbait、Topwater Plug 需要给鱼追咬窗口，挂鱼后靠调性缓冲短咬。</v>
       </c>
       <c r="AI111" t="str" s="1">
-        <v/>
+        <v>Crankbait / Jerkbait / Topwater Plug / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ111" t="str" s="1">
         <v/>
@@ -17174,21 +17504,24 @@
         <v/>
       </c>
       <c r="AL111" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM111" t="str" s="1">
-        <v>卷阻饵 / 搜索</v>
+        <v>淡水 Bass / 开放水域 reaction bait / 7'6"抽停搜索</v>
       </c>
       <c r="AN111" t="str" s="1">
-        <v>适合 crankbait 和 moving bait / 卷收节奏稳定 / 搜索型作钓更顺手</v>
+        <v>Delay / 7'6" M reaction bait / moving bait</v>
       </c>
       <c r="AO111" t="str" s="1">
+        <v>Delay 枪柄 7'6" M Moderate，10-20 lb线组配置下，Crankbait、Jerkbait、Topwater Plug 优先，抽停和连续卷收都要保持节奏；短咬时竿身缓冲能提高挂鱼稳定性。</v>
+      </c>
+      <c r="AP111" t="str" s="1">
         <v>The Ike Signature Series Delay Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with reaction baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Delay Series Casting Rod construction creates the ideal parabolic action for moving baits.</v>
       </c>
-      <c r="AP111" t="str" s="1">
+      <c r="AQ111" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ111" t="str" s="1">
+      <c r="AR111" t="str" s="1">
         <v>UPC: 036282118584</v>
       </c>
     </row>
@@ -17293,10 +17626,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH112" t="str" s="2">
-        <v>maximized casting distance with lighter lures / finesse / lightweight lure use</v>
+        <v>轻量高感枪柄 7'1" M Fast，核心是轻饵启动和控线，Small Minnow、Shad、Small Crankbait 适合小标点低弹道抛投，软硬饵切换要控制饵重上限。</v>
       </c>
       <c r="AI112" t="str" s="2">
-        <v/>
+        <v>Small Minnow / Shad / Small Crankbait / Neko Rig / No Sinker</v>
       </c>
       <c r="AJ112" t="str" s="2">
         <v/>
@@ -17305,21 +17638,24 @@
         <v/>
       </c>
       <c r="AL112" t="str" s="2">
-        <v>淡水 / bass / BFS</v>
+        <v/>
       </c>
       <c r="AM112" t="str" s="2">
-        <v>精细轻饵</v>
+        <v>淡水 Bass / 小场地细线轻饵 / 7'1"枪柄 BFS</v>
       </c>
       <c r="AN112" t="str" s="2">
-        <v>小饵抛投更轻松 / 精细操控直接 / 适合轻量硬饵和小型钓组</v>
+        <v>轻量高感 / 7'1" M BFS 精细轻饵</v>
       </c>
       <c r="AO112" t="str" s="2">
+        <v>轻量高感枪柄 7'1" M Fast，8-15 lb线组配置下，Small Minnow、Shad、Small Crankbait 优先，低弹道轻抛和细线控线是核心；鱼口变轻时可在小硬饵与软饵间切换。</v>
+      </c>
+      <c r="AP112" t="str" s="2">
         <v>Designed specifically for BFS techniques, the next generation of Veritas rods feature Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The Veritas BFS rods use unique actions that excel at throwing ultra-lightweight lures. The Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled withtitanium alloy guides with zirconium inserts and EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP112" t="str" s="2">
+      <c r="AQ112" t="str" s="2">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ112" t="str" s="2">
+      <c r="AR112" t="str" s="2">
         <v>UPC: 036282736245; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -17424,10 +17760,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH113" t="str" s="2">
-        <v>maximized casting distance with lighter lures / finesse / lightweight lure use</v>
+        <v>轻量高感枪柄 7'1" ML Moderate Fast，适合细线小卷阻饵，Small Crankbait、Shad Crank、Small Minnow 可低弹道进入窄标点；鱼口变轻时再切 No Sinker / Neko。</v>
       </c>
       <c r="AI113" t="str" s="2">
-        <v/>
+        <v>Small Crankbait / Shad Crank / Small Minnow / No Sinker / Neko Rig</v>
       </c>
       <c r="AJ113" t="str" s="2">
         <v/>
@@ -17436,21 +17772,24 @@
         <v/>
       </c>
       <c r="AL113" t="str" s="2">
-        <v>淡水 / bass / BFS</v>
+        <v/>
       </c>
       <c r="AM113" t="str" s="2">
-        <v>精细轻饵</v>
+        <v>淡水 Bass / 小河道与近岸浅中层 / 7'1"BFS 卷阻搜索</v>
       </c>
       <c r="AN113" t="str" s="2">
-        <v>小饵抛投更轻松 / 精细操控直接 / 适合轻量硬饵和小型钓组</v>
+        <v>轻量高感 / 7'1" ML BFS 小 crank / 小 minnow</v>
       </c>
       <c r="AO113" t="str" s="2">
+        <v>轻量高感枪柄 7'1" ML Moderate Fast，6-12 lb线组配置下，Small Crankbait、Shad Crank、Small Minnow 优先，轻量卷阻饵可以低弹道抛进窄标点；细线下还能切回 Neko / No Sinker。</v>
+      </c>
+      <c r="AP113" t="str" s="2">
         <v>Designed specifically for BFS techniques, the next generation of Veritas rods feature Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The Veritas BFS rods use unique actions that excel at throwing ultra-lightweight lures. The Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled withtitanium alloy guides with zirconium inserts and EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP113" t="str" s="2">
+      <c r="AQ113" t="str" s="2">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ113" t="str" s="2">
+      <c r="AR113" t="str" s="2">
         <v>UPC: 036282736269; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -17555,10 +17894,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH114" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感直柄 7' M Moderate Fast，以稳定卷收为核心，Crankbait、Shad Crank、Squarebill 适合沿草边、石滩和浅中层水线搜索，短咬时不宜立刻大幅扬竿。</v>
       </c>
       <c r="AI114" t="str" s="1">
-        <v/>
+        <v>Crankbait / Shad Crank / Squarebill / Lipless Crankbait / Chatterbait</v>
       </c>
       <c r="AJ114" t="str" s="1">
         <v/>
@@ -17567,21 +17906,24 @@
         <v/>
       </c>
       <c r="AL114" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM114" t="str" s="1">
-        <v>卷阻饵 / 搜索</v>
+        <v>淡水 Bass / 开阔水域卷阻搜索 / 7'Crankbait</v>
       </c>
       <c r="AN114" t="str" s="1">
-        <v>适合 crankbait 和 moving bait / 卷收节奏稳定 / 搜索型作钓更顺手</v>
+        <v>轻量高感 / 7' M crankbait / shad 专项</v>
       </c>
       <c r="AO114" t="str" s="1">
+        <v>轻量高感直柄 7' M Moderate Fast，8-17 lb线组配置下，Crankbait、Shad Crank、Squarebill 优先，稳定卷收和挂鱼缓冲比快速刺鱼更关键；适合沿草边、石滩和浅中层水线搜索。</v>
+      </c>
+      <c r="AP114" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP114" t="str" s="1">
+      <c r="AQ114" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ114" t="str" s="1">
+      <c r="AR114" t="str" s="1">
         <v>UPC: 036282736115; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -17686,10 +18028,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH115" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感直柄 7'2" ML Moderate Fast，偏 crankbait 节奏，Crankbait、Shad Crank、Squarebill 要保持泳层和回收速度；挂底或碰障后用竿身缓冲带过。</v>
       </c>
       <c r="AI115" t="str" s="1">
-        <v/>
+        <v>Crankbait / Shad Crank / Squarebill / Lipless Crankbait / Chatterbait</v>
       </c>
       <c r="AJ115" t="str" s="1">
         <v/>
@@ -17698,21 +18040,24 @@
         <v/>
       </c>
       <c r="AL115" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM115" t="str" s="1">
-        <v>卷阻饵 / 搜索</v>
+        <v>淡水 Bass / 开阔水域卷阻搜索 / 7'2"Crankbait</v>
       </c>
       <c r="AN115" t="str" s="1">
-        <v>适合 crankbait 和 moving bait / 卷收节奏稳定 / 搜索型作钓更顺手</v>
+        <v>轻量高感 / 7'2" ML crankbait / shad 专项</v>
       </c>
       <c r="AO115" t="str" s="1">
+        <v>轻量高感直柄 7'2" ML Moderate Fast，4-10 lb线组配置下，Crankbait、Shad Crank、Squarebill 优先，稳定卷收和挂鱼缓冲比快速刺鱼更关键；适合沿草边、石滩和浅中层水线搜索。</v>
+      </c>
+      <c r="AP115" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP115" t="str" s="1">
+      <c r="AQ115" t="str" s="1">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ115" t="str" s="1">
+      <c r="AR115" t="str" s="1">
         <v>UPC: 036282736122; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -17817,10 +18162,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH116" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Power Fishing 枪柄 7' M Fast，适合快速覆盖水层，Spinnerbait、Chatterbait、Swim Jig 先搜索活性鱼；标点明确后可切 Texas / Rubber Jig 补打。</v>
       </c>
       <c r="AI116" t="str" s="2">
-        <v/>
+        <v>Spinnerbait / Chatterbait / Swim Jig / Texas Rig / Rubber Jig</v>
       </c>
       <c r="AJ116" t="str" s="2">
         <v/>
@@ -17829,21 +18174,24 @@
         <v/>
       </c>
       <c r="AL116" t="str" s="2">
-        <v>淡水 / bass / power fishing</v>
+        <v/>
       </c>
       <c r="AM116" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 草边硬物与开阔水搜索 / 7'power fishing</v>
       </c>
       <c r="AN116" t="str" s="2">
-        <v>适合 reaction bait 和 power fishing 技法 / 搜索效率高 / 中重型控鱼更从容</v>
+        <v>Power Fishing / 7' M Spinnerbait / Chatterbait 强搜索</v>
       </c>
       <c r="AO116" t="str" s="2">
+        <v>Power Fishing 枪柄 7' M Fast，10-17 lb线组配置下，Spinnerbait、Chatterbait、Swim Jig 优先，适合快速覆盖水层后切 Texas 或 Jig 补打；移动饵和底操之间切换宽容。</v>
+      </c>
+      <c r="AP116" t="str" s="2">
         <v>The Ike Signature Series Power Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with reaction baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Power Series Casting Rod construction creates the ideal actions for power fishing techniques.</v>
       </c>
-      <c r="AP116" t="str" s="2">
+      <c r="AQ116" t="str" s="2">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ116" t="str" s="2">
+      <c r="AR116" t="str" s="2">
         <v>UPC: 036282118591</v>
       </c>
     </row>
@@ -17948,10 +18296,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH117" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Power Fishing 枪柄 7' MH Fast，适合快速覆盖水层，Spinnerbait、Chatterbait、Swim Jig 先搜索活性鱼；标点明确后可切 Texas / Rubber Jig 补打。</v>
       </c>
       <c r="AI117" t="str" s="2">
-        <v/>
+        <v>Spinnerbait / Chatterbait / Swim Jig / Texas Rig / Rubber Jig</v>
       </c>
       <c r="AJ117" t="str" s="2">
         <v/>
@@ -17960,21 +18308,24 @@
         <v/>
       </c>
       <c r="AL117" t="str" s="2">
-        <v>淡水 / bass / power fishing</v>
+        <v/>
       </c>
       <c r="AM117" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 草边硬物与开阔水搜索 / 7'power fishing</v>
       </c>
       <c r="AN117" t="str" s="2">
-        <v>适合 reaction bait 和 power fishing 技法 / 搜索效率高 / 中重型控鱼更从容</v>
+        <v>Power Fishing / 7' MH Spinnerbait / Chatterbait 强搜索</v>
       </c>
       <c r="AO117" t="str" s="2">
+        <v>Power Fishing 枪柄 7' MH Fast，12-20 lb线组配置下，Spinnerbait、Chatterbait、Swim Jig 优先，适合快速覆盖水层后切 Texas 或 Jig 补打；移动饵和底操之间切换宽容。</v>
+      </c>
+      <c r="AP117" t="str" s="2">
         <v>The Ike Signature Series Power Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with reaction baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Power Series Casting Rod construction creates the ideal actions for power fishing techniques.</v>
       </c>
-      <c r="AP117" t="str" s="2">
+      <c r="AQ117" t="str" s="2">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ117" t="str" s="2">
+      <c r="AR117" t="str" s="2">
         <v>UPC: 036282118607</v>
       </c>
     </row>
@@ -18079,10 +18430,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH118" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Power Fishing 枪柄 7'2" MH Fast，适合快速覆盖水层，Spinnerbait、Chatterbait、Swim Jig 先搜索活性鱼；标点明确后可切 Texas / Rubber Jig 补打。</v>
       </c>
       <c r="AI118" t="str" s="2">
-        <v/>
+        <v>Spinnerbait / Chatterbait / Swim Jig / Texas Rig / Rubber Jig</v>
       </c>
       <c r="AJ118" t="str" s="2">
         <v/>
@@ -18091,21 +18442,24 @@
         <v/>
       </c>
       <c r="AL118" t="str" s="2">
-        <v>淡水 / bass / power fishing</v>
+        <v/>
       </c>
       <c r="AM118" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 草边硬物与开阔水搜索 / 7'2"power fishing</v>
       </c>
       <c r="AN118" t="str" s="2">
-        <v>适合 reaction bait 和 power fishing 技法 / 搜索效率高 / 中重型控鱼更从容</v>
+        <v>Power Fishing / 7'2" MH Spinnerbait / Chatterbait 强搜索</v>
       </c>
       <c r="AO118" t="str" s="2">
+        <v>Power Fishing 枪柄 7'2" MH Fast，12-20 lb线组配置下，Spinnerbait、Chatterbait、Swim Jig 优先，适合快速覆盖水层后切 Texas 或 Jig 补打；移动饵和底操之间切换宽容。</v>
+      </c>
+      <c r="AP118" t="str" s="2">
         <v>The Ike Signature Series Power Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with reaction baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Power Series Casting Rod construction creates the ideal actions for power fishing techniques.</v>
       </c>
-      <c r="AP118" t="str" s="2">
+      <c r="AQ118" t="str" s="2">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ118" t="str" s="2">
+      <c r="AR118" t="str" s="2">
         <v>UPC: 036282118614</v>
       </c>
     </row>
@@ -18210,10 +18564,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH119" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Power Fishing 枪柄 7'4" MH Fast，适合快速覆盖水层，Spinnerbait、Chatterbait、Swim Jig 先搜索活性鱼；标点明确后可切 Texas / Rubber Jig 补打。</v>
       </c>
       <c r="AI119" t="str" s="2">
-        <v/>
+        <v>Spinnerbait / Chatterbait / Swim Jig / Texas Rig / Rubber Jig</v>
       </c>
       <c r="AJ119" t="str" s="2">
         <v/>
@@ -18222,21 +18576,24 @@
         <v/>
       </c>
       <c r="AL119" t="str" s="2">
-        <v>淡水 / bass / power fishing</v>
+        <v/>
       </c>
       <c r="AM119" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 草边硬物与开阔水搜索 / 7'4"power fishing</v>
       </c>
       <c r="AN119" t="str" s="2">
-        <v>适合 reaction bait 和 power fishing 技法 / 搜索效率高 / 中重型控鱼更从容</v>
+        <v>Power Fishing / 7'4" MH Spinnerbait / Chatterbait 强搜索</v>
       </c>
       <c r="AO119" t="str" s="2">
+        <v>Power Fishing 枪柄 7'4" MH Fast，12-20 lb线组配置下，Spinnerbait、Chatterbait、Swim Jig 优先，适合快速覆盖水层后切 Texas 或 Jig 补打；移动饵和底操之间切换宽容。</v>
+      </c>
+      <c r="AP119" t="str" s="2">
         <v>The Ike Signature Series Power Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with reaction baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Power Series Casting Rod construction creates the ideal actions for power fishing techniques.</v>
       </c>
-      <c r="AP119" t="str" s="2">
+      <c r="AQ119" t="str" s="2">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ119" t="str" s="2">
+      <c r="AR119" t="str" s="2">
         <v>UPC: 036282118621</v>
       </c>
     </row>
@@ -18341,10 +18698,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH120" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Power Fishing 枪柄 7'6" MH Fast，适合快速覆盖水层，Spinnerbait、Chatterbait、Swim Jig 先搜索活性鱼；标点明确后可切 Texas / Rubber Jig 补打。</v>
       </c>
       <c r="AI120" t="str" s="2">
-        <v/>
+        <v>Spinnerbait / Chatterbait / Swim Jig / Texas Rig / Rubber Jig</v>
       </c>
       <c r="AJ120" t="str" s="2">
         <v/>
@@ -18353,21 +18710,24 @@
         <v/>
       </c>
       <c r="AL120" t="str" s="2">
-        <v>淡水 / bass / power fishing</v>
+        <v/>
       </c>
       <c r="AM120" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 草边硬物与开阔水搜索 / 7'6"power fishing</v>
       </c>
       <c r="AN120" t="str" s="2">
-        <v>适合 reaction bait 和 power fishing 技法 / 搜索效率高 / 中重型控鱼更从容</v>
+        <v>Power Fishing / 7'6" MH Spinnerbait / Chatterbait 强搜索</v>
       </c>
       <c r="AO120" t="str" s="2">
+        <v>Power Fishing 枪柄 7'6" MH Fast，12-20 lb线组配置下，Spinnerbait、Chatterbait、Swim Jig 优先，适合快速覆盖水层后切 Texas 或 Jig 补打；移动饵和底操之间切换宽容。</v>
+      </c>
+      <c r="AP120" t="str" s="2">
         <v>The Ike Signature Series Power Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with reaction baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Power Series Casting Rod construction creates the ideal actions for power fishing techniques.</v>
       </c>
-      <c r="AP120" t="str" s="2">
+      <c r="AQ120" t="str" s="2">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ120" t="str" s="2">
+      <c r="AR120" t="str" s="2">
         <v>UPC: 036282118638</v>
       </c>
     </row>
@@ -18472,10 +18832,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH121" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>Power Fishing 枪柄 7' M/MH Fast，适合快速覆盖水层，Spinnerbait、Chatterbait、Swim Jig 先搜索活性鱼；标点明确后可切 Texas / Rubber Jig 补打。</v>
       </c>
       <c r="AI121" t="str" s="2">
-        <v/>
+        <v>Spinnerbait / Chatterbait / Swim Jig / Texas Rig / Rubber Jig</v>
       </c>
       <c r="AJ121" t="str" s="2">
         <v/>
@@ -18484,21 +18844,24 @@
         <v/>
       </c>
       <c r="AL121" t="str" s="2">
-        <v>淡水 / bass / power fishing</v>
+        <v/>
       </c>
       <c r="AM121" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 草边硬物与开阔水搜索 / 7'power fishing</v>
       </c>
       <c r="AN121" t="str" s="2">
-        <v>适合 reaction bait 和 power fishing 技法 / 搜索效率高 / 中重型控鱼更从容</v>
+        <v>Power Fishing / 7' M/MH Spinnerbait / Chatterbait 强搜索</v>
       </c>
       <c r="AO121" t="str" s="2">
+        <v>Power Fishing 枪柄 7' M/MH Fast，8-17 lb / 10-20 lb线组配置下，Spinnerbait、Chatterbait、Swim Jig 优先，适合快速覆盖水层后切 Texas 或 Jig 补打；移动饵和底操之间切换宽容。</v>
+      </c>
+      <c r="AP121" t="str" s="2">
         <v>The Ike Signature Series Power Rods have been precisely developed with Mike Iaconelli to achieve top tier performance with reaction baits. Made with premium 30-ton graphite blanks and Powerlux 200 resin, the Abu Garcia Ike Power Series Casting Rod construction creates the ideal actions for power fishing techniques.</v>
       </c>
-      <c r="AP121" t="str" s="2">
+      <c r="AQ121" t="str" s="2">
         <v>Guide Type: Stainless Steel Zirconium</v>
       </c>
-      <c r="AQ121" t="str" s="2">
+      <c r="AR121" t="str" s="2">
         <v>UPC: 036282034532</v>
       </c>
     </row>
@@ -18603,10 +18966,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH122" t="str" s="1">
-        <v>maximized casting distance with lighter lures / finesse / lightweight lure use</v>
+        <v>高阶轻量直柄 7'1" M Fast，更偏 BFS 轻量路线，Neko Rig、Down Shot、No Sinker 可以在岸边障碍和小水面之间切换，重点是出线轻和落点准。</v>
       </c>
       <c r="AI122" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Down Shot / No Sinker / Small Minnow / Small Crankbait</v>
       </c>
       <c r="AJ122" t="str" s="1">
         <v/>
@@ -18615,21 +18978,24 @@
         <v/>
       </c>
       <c r="AL122" t="str" s="1">
-        <v>淡水 / bass / BFS</v>
+        <v/>
       </c>
       <c r="AM122" t="str" s="1">
-        <v>精细轻饵</v>
+        <v>淡水 Bass / 小场地细线轻饵 / 7'1"直柄 BFS</v>
       </c>
       <c r="AN122" t="str" s="1">
-        <v>小饵抛投更轻松 / 精细操控直接 / 适合轻量硬饵和小型钓组</v>
+        <v>高阶轻量 / 7'1" M BFS 精细轻饵</v>
       </c>
       <c r="AO122" t="str" s="1">
+        <v>高阶轻量直柄 7'1" M Fast，6-12 lb线组配置下，Neko Rig、Down Shot、No Sinker 优先，低弹道轻抛和细线控线是核心；鱼口变轻时可在小硬饵与软饵间切换。</v>
+      </c>
+      <c r="AP122" t="str" s="1">
         <v>Introducing Abu Garcia’s lightest rod series with the Abu Garcia® Zenon™ rods. The NEW Bait Finesse models feature the perfect power and action to throw lightweight baits. Featuring premium carbon blanks and our exclusive Powerlux® 1000 resin system, these rods deliver powerful ultra-light sensitive blanks with higher break strengths and improved impact and fracture resistance without increasing overall weight or blank diameters. Fuji® reel seat improves comfort for all-day fishing. Coupled with titanium alloy guides with nitride silicon inserts and a carbon handle split grip design, the Abu Garcia Zenon rods are optimized for performance.</v>
       </c>
-      <c r="AP122" t="str" s="1">
+      <c r="AQ122" t="str" s="1">
         <v>Feature: Powerlux® 1000 delivers Abu Garcia’s lightest and most sensitive rod ever</v>
       </c>
-      <c r="AQ122" t="str" s="1">
+      <c r="AR122" t="str" s="1">
         <v>UPC: 036282118072</v>
       </c>
     </row>
@@ -18734,33 +19100,36 @@
         <v>Stainless steel / aluminum oxide guide train</v>
       </c>
       <c r="AH123" t="str" s="2">
-        <v>耐用泛用，适合日常淡水路亚</v>
+        <v>入门耐用直柄 6'6" M Fast，适合细线控饵，Neko Rig、Wacky Rig、Down Shot 的重点是松线管理和轻口判断，硬饵只做短距离补充。</v>
       </c>
       <c r="AI123" t="str" s="2">
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
+      </c>
+      <c r="AJ123" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ123" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK123" t="str" s="2">
         <v/>
       </c>
       <c r="AL123" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM123" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 6'6"直柄泛用</v>
       </c>
       <c r="AN123" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>入门耐用 / 6'6" M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO123" t="str" s="2">
+        <v>入门耐用直柄 6'6" M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP123" t="str" s="2">
         <v>The updated Vengeance series of fishing rods delivers on-the-water performance and style in a balanced, lightweight design. Construction starts with a 24-ton intermediate modulus graphite blank that is paired with stainless steel guides. Split grip EVA handles ensure comfort and durability for the long haul. The Vengeance series of casting rods delivers excellent performance at a great value.</v>
       </c>
-      <c r="AP123" t="str" s="2">
+      <c r="AQ123" t="str" s="2">
         <v>Guide Type: Stainless Steel/Aluminum Oxide</v>
       </c>
-      <c r="AQ123" t="str" s="2">
+      <c r="AR123" t="str" s="2">
         <v>UPC: 036282117754; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -18865,33 +19234,36 @@
         <v>Stainless steel / aluminum oxide guide train</v>
       </c>
       <c r="AH124" t="str" s="2">
-        <v>耐用泛用，适合日常淡水路亚</v>
+        <v>入门耐用直柄 6'9" ML Fast，用于清水或轻压场更自然，Down Shot、Neko Rig、Wacky Rig 动作要小，补刺靠节奏和线张力。</v>
       </c>
       <c r="AI124" t="str" s="2">
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
+      </c>
+      <c r="AJ124" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ124" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK124" t="str" s="2">
         <v/>
       </c>
       <c r="AL124" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM124" t="str" s="2">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线和轻压场 / 6'9"直柄精细</v>
       </c>
       <c r="AN124" t="str" s="2">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>入门耐用 / 6'9" ML Down Shot / Neko 精细</v>
       </c>
       <c r="AO124" t="str" s="2">
+        <v>入门耐用直柄 6'9" ML Fast，6-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，适合细线慢拖、轻抖和看线；微弱咬口反馈比强力控鱼更重要。</v>
+      </c>
+      <c r="AP124" t="str" s="2">
         <v>The updated Vengeance series of fishing rods delivers on-the-water performance and style in a balanced, lightweight design. Construction starts with a 24-ton intermediate modulus graphite blank that is paired with stainless steel guides. Split grip EVA handles ensure comfort and durability for the long haul. The Vengeance series of casting rods delivers excellent performance at a great value.</v>
       </c>
-      <c r="AP124" t="str" s="2">
+      <c r="AQ124" t="str" s="2">
         <v>Guide Type: Stainless Steel/Aluminum Oxide</v>
       </c>
-      <c r="AQ124" t="str" s="2">
+      <c r="AR124" t="str" s="2">
         <v>UPC: 036282117778; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -18996,33 +19368,36 @@
         <v>Stainless steel / aluminum oxide guide train</v>
       </c>
       <c r="AH125" t="str" s="2">
-        <v>耐用泛用，适合日常淡水路亚</v>
+        <v>入门耐用直柄 7' M Fast，偏直柄精细泛用，Neko Rig、Wacky Rig、Down Shot 适合岸边轻量软饵；小 Minnow 只是补充搜索路线。</v>
       </c>
       <c r="AI125" t="str" s="2">
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
+      </c>
+      <c r="AJ125" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ125" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK125" t="str" s="2">
         <v/>
       </c>
       <c r="AL125" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM125" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'直柄泛用</v>
       </c>
       <c r="AN125" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>入门耐用 / 7' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO125" t="str" s="2">
+        <v>入门耐用直柄 7' M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP125" t="str" s="2">
         <v>The updated Vengeance series of fishing rods delivers on-the-water performance and style in a balanced, lightweight design. Construction starts with a 24-ton intermediate modulus graphite blank that is paired with stainless steel guides. Split grip EVA handles ensure comfort and durability for the long haul. The Vengeance series of casting rods delivers excellent performance at a great value.</v>
       </c>
-      <c r="AP125" t="str" s="2">
+      <c r="AQ125" t="str" s="2">
         <v>Guide Type: Stainless Steel/Aluminum Oxide</v>
       </c>
-      <c r="AQ125" t="str" s="2">
+      <c r="AR125" t="str" s="2">
         <v>UPC: 036282117785; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -19127,33 +19502,36 @@
         <v>Stainless steel / aluminum oxide guide train</v>
       </c>
       <c r="AH126" t="str" s="2">
-        <v>耐用泛用，适合日常淡水路亚</v>
+        <v>入门耐用直柄 7' MH Fast，比常规精细竿更能承受稍重钓组，Shaky Head、Free Rig、Neko Rig 适合开阔结构和深一点的标点，仍以控线为先。</v>
       </c>
       <c r="AI126" t="str" s="2">
+        <v>Shaky Head / Free Rig / Neko Rig / Small Swimbait / Swim Jig</v>
+      </c>
+      <c r="AJ126" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ126" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK126" t="str" s="2">
         <v/>
       </c>
       <c r="AL126" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM126" t="str" s="2">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开阔结构与稍重精细 / 7'直柄强精细</v>
       </c>
       <c r="AN126" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>入门耐用 / 7' MH Shaky Head / Free Rig 直柄</v>
       </c>
       <c r="AO126" t="str" s="2">
+        <v>入门耐用直柄 7' MH Fast，8-15 lb线组配置下，Shaky Head、Free Rig、Neko Rig 优先，适合比常规精细更重的钓组；保留直柄控线优势，同时有更好的刺鱼余量。</v>
+      </c>
+      <c r="AP126" t="str" s="2">
         <v>The updated Vengeance series of fishing rods delivers on-the-water performance and style in a balanced, lightweight design. Construction starts with a 24-ton intermediate modulus graphite blank that is paired with stainless steel guides. Split grip EVA handles ensure comfort and durability for the long haul. The Vengeance series of casting rods delivers excellent performance at a great value.</v>
       </c>
-      <c r="AP126" t="str" s="2">
+      <c r="AQ126" t="str" s="2">
         <v>Guide Type: Stainless Steel/Aluminum Oxide</v>
       </c>
-      <c r="AQ126" t="str" s="2">
+      <c r="AR126" t="str" s="2">
         <v>UPC: 036282117808; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -19258,33 +19636,36 @@
         <v>Stainless steel / aluminum oxide guide train</v>
       </c>
       <c r="AH127" t="str" s="2">
-        <v>耐用泛用，适合日常淡水路亚</v>
+        <v>入门耐用直柄 6'6" M Fast，用于 Neko / Wacky 更自然，Neko Rig、Wacky Rig、Down Shot 可覆盖轻量打点和慢节奏搜索，别用太重的饵压竿。</v>
       </c>
       <c r="AI127" t="str" s="2">
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
+      </c>
+      <c r="AJ127" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ127" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK127" t="str" s="2">
         <v/>
       </c>
       <c r="AL127" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM127" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 6'6"直柄泛用</v>
       </c>
       <c r="AN127" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>入门耐用 / 6'6" M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO127" t="str" s="2">
+        <v>入门耐用直柄 6'6" M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP127" t="str" s="2">
         <v>The updated Vengeance series of fishing rods delivers on-the-water performance and style in a balanced, lightweight design. Construction starts with a 24-ton intermediate modulus graphite blank that is paired with stainless steel guides. Split grip EVA handles ensure comfort and durability for the long haul. The Vengeance series of casting rods delivers excellent performance at a great value.</v>
       </c>
-      <c r="AP127" t="str" s="2">
+      <c r="AQ127" t="str" s="2">
         <v>Guide Type: Stainless Steel/Aluminum Oxide</v>
       </c>
-      <c r="AQ127" t="str" s="2">
+      <c r="AR127" t="str" s="2">
         <v>UPC: 036282117761; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -19389,33 +19770,36 @@
         <v>Stainless steel / aluminum oxide guide train</v>
       </c>
       <c r="AH128" t="str" s="2">
-        <v>耐用泛用，适合日常淡水路亚</v>
+        <v>入门耐用直柄 7' M Fast，偏直柄精细泛用，Neko Rig、Wacky Rig、Down Shot 适合岸边轻量软饵；小 Minnow 只是补充搜索路线。</v>
       </c>
       <c r="AI128" t="str" s="2">
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
+      </c>
+      <c r="AJ128" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ128" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK128" t="str" s="2">
         <v/>
       </c>
       <c r="AL128" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM128" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'直柄泛用</v>
       </c>
       <c r="AN128" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>入门耐用 / 7' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO128" t="str" s="2">
+        <v>入门耐用直柄 7' M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP128" t="str" s="2">
         <v>The updated Vengeance series of fishing rods delivers on-the-water performance and style in a balanced, lightweight design. Construction starts with a 24-ton intermediate modulus graphite blank that is paired with stainless steel guides. Split grip EVA handles ensure comfort and durability for the long haul. The Vengeance series of casting rods delivers excellent performance at a great value.</v>
       </c>
-      <c r="AP128" t="str" s="2">
+      <c r="AQ128" t="str" s="2">
         <v>Guide Type: Stainless Steel/Aluminum Oxide</v>
       </c>
-      <c r="AQ128" t="str" s="2">
+      <c r="AR128" t="str" s="2">
         <v>UPC: 036282117792; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -19520,10 +19904,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH129" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感直柄 6'9" ML Fast，适合细线慢节奏，Down Shot、Neko Rig、Wacky Rig 以控松线和读轻口为主，不适合粗暴硬拔。</v>
       </c>
       <c r="AI129" t="str" s="1">
-        <v/>
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
       </c>
       <c r="AJ129" t="str" s="1">
         <v/>
@@ -19532,21 +19916,24 @@
         <v/>
       </c>
       <c r="AL129" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM129" t="str" s="1">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线和轻压场 / 6'9"直柄精细</v>
       </c>
       <c r="AN129" t="str" s="1">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>轻量高感 / 6'9" ML Down Shot / Neko 精细</v>
       </c>
       <c r="AO129" t="str" s="1">
+        <v>轻量高感直柄 6'9" ML Fast，6-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，适合细线慢拖、轻抖和看线；微弱咬口反馈比强力控鱼更重要。</v>
+      </c>
+      <c r="AP129" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and Winn® advanced polymer Dri-Tac grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP129" t="str" s="1">
+      <c r="AQ129" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ129" t="str" s="1">
+      <c r="AR129" t="str" s="1">
         <v>UPC: 036282031968; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -19651,10 +20038,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH130" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感直柄 7' M Fast，用于 Neko / Wacky 更自然，Neko Rig、Wacky Rig、Down Shot 可覆盖轻量打点和慢节奏搜索，别用太重的饵压竿。</v>
       </c>
       <c r="AI130" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ130" t="str" s="1">
         <v/>
@@ -19663,21 +20050,24 @@
         <v/>
       </c>
       <c r="AL130" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM130" t="str" s="1">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'直柄泛用</v>
       </c>
       <c r="AN130" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>轻量高感 / 7' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO130" t="str" s="1">
+        <v>轻量高感直柄 7' M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP130" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and Winn® advanced polymer Dri-Tac grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP130" t="str" s="1">
+      <c r="AQ130" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ130" t="str" s="1">
+      <c r="AR130" t="str" s="1">
         <v>UPC: 036282031975; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -19782,10 +20172,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH131" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感直柄 7' MH Extra Fast，比常规精细竿更能承受稍重钓组，Shaky Head、Free Rig、Neko Rig 适合开阔结构和深一点的标点，仍以控线为先。</v>
       </c>
       <c r="AI131" t="str" s="1">
-        <v/>
+        <v>Shaky Head / Free Rig / Neko Rig / Small Swimbait / Swim Jig</v>
       </c>
       <c r="AJ131" t="str" s="1">
         <v/>
@@ -19794,21 +20184,24 @@
         <v/>
       </c>
       <c r="AL131" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM131" t="str" s="1">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开阔结构与稍重精细 / 7'直柄强精细</v>
       </c>
       <c r="AN131" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 7' MH Shaky Head / Free Rig 直柄</v>
       </c>
       <c r="AO131" t="str" s="1">
+        <v>轻量高感直柄 7' MH Extra Fast，8-14 lb线组配置下，Shaky Head、Free Rig、Neko Rig 优先，适合比常规精细更重的钓组；保留直柄控线优势，同时有更好的刺鱼余量。</v>
+      </c>
+      <c r="AP131" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and Winn® advanced polymer Dri-Tac grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP131" t="str" s="1">
+      <c r="AQ131" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ131" t="str" s="1">
+      <c r="AR131" t="str" s="1">
         <v>UPC: 036282031982; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -19913,10 +20306,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH132" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量直柄 6'10" ML Fast，适合细线慢节奏，Down Shot、Neko Rig、Wacky Rig 以控松线和读轻口为主，不适合粗暴硬拔。</v>
       </c>
       <c r="AI132" t="str" s="2">
-        <v/>
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
       </c>
       <c r="AJ132" t="str" s="2">
         <v/>
@@ -19925,21 +20318,24 @@
         <v/>
       </c>
       <c r="AL132" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM132" t="str" s="2">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线和轻压场 / 6'10"直柄精细</v>
       </c>
       <c r="AN132" t="str" s="2">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>竞赛轻量 / 6'10" ML Down Shot / Neko 精细</v>
       </c>
       <c r="AO132" t="str" s="2">
+        <v>竞赛轻量直柄 6'10" ML Fast，6-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，适合细线慢拖、轻抖和看线；微弱咬口反馈比强力控鱼更重要。</v>
+      </c>
+      <c r="AP132" t="str" s="2">
         <v>Offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The Abu Garcia® custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and a carbon handle split grip design, the new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP132" t="str" s="2">
+      <c r="AQ132" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ132" t="str" s="2">
+      <c r="AR132" t="str" s="2">
         <v>UPC: 036282077997</v>
       </c>
     </row>
@@ -20044,10 +20440,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH133" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量直柄 7' M Fast，用于 Neko / Wacky 更自然，Neko Rig、Wacky Rig、Down Shot 可覆盖轻量打点和慢节奏搜索，别用太重的饵压竿。</v>
       </c>
       <c r="AI133" t="str" s="2">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ133" t="str" s="2">
         <v/>
@@ -20056,21 +20452,24 @@
         <v/>
       </c>
       <c r="AL133" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM133" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'直柄泛用</v>
       </c>
       <c r="AN133" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>竞赛轻量 / 7' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO133" t="str" s="2">
+        <v>竞赛轻量直柄 7' M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP133" t="str" s="2">
         <v>Offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The Abu Garcia® custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and a carbon handle split grip design, the new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP133" t="str" s="2">
+      <c r="AQ133" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ133" t="str" s="2">
+      <c r="AR133" t="str" s="2">
         <v>UPC: 036282078000</v>
       </c>
     </row>
@@ -20175,10 +20574,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH134" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量直柄 7' MH Fast，比常规精细竿更能承受稍重钓组，Shaky Head、Free Rig、Neko Rig 适合开阔结构和深一点的标点，仍以控线为先。</v>
       </c>
       <c r="AI134" t="str" s="2">
-        <v/>
+        <v>Shaky Head / Free Rig / Neko Rig / Small Swimbait / Swim Jig</v>
       </c>
       <c r="AJ134" t="str" s="2">
         <v/>
@@ -20187,21 +20586,24 @@
         <v/>
       </c>
       <c r="AL134" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM134" t="str" s="2">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开阔结构与稍重精细 / 7'直柄强精细</v>
       </c>
       <c r="AN134" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7' MH Shaky Head / Free Rig 直柄</v>
       </c>
       <c r="AO134" t="str" s="2">
+        <v>竞赛轻量直柄 7' MH Fast，8-14 lb线组配置下，Shaky Head、Free Rig、Neko Rig 优先，适合比常规精细更重的钓组；保留直柄控线优势，同时有更好的刺鱼余量。</v>
+      </c>
+      <c r="AP134" t="str" s="2">
         <v>Offering serious anglers a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The Abu Garcia® custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and a carbon handle split grip design, the new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP134" t="str" s="2">
+      <c r="AQ134" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ134" t="str" s="2">
+      <c r="AR134" t="str" s="2">
         <v>UPC: 036282078017</v>
       </c>
     </row>
@@ -20306,10 +20708,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH135" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用直柄 7' M Fast，适合细线控饵，Neko Rig、Wacky Rig、Down Shot 的重点是松线管理和轻口判断，硬饵只做短距离补充。</v>
       </c>
       <c r="AI135" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ135" t="str" s="1">
         <v/>
@@ -20318,21 +20720,24 @@
         <v/>
       </c>
       <c r="AL135" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM135" t="str" s="1">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'直柄泛用</v>
       </c>
       <c r="AN135" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 7' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO135" t="str" s="1">
+        <v>进阶泛用直柄 7' M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP135" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods features a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP135" t="str" s="1">
+      <c r="AQ135" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ135" t="str" s="1">
+      <c r="AR135" t="str" s="1">
         <v>UPC: 036282075801; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -20437,10 +20842,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH136" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用直柄 6'9" ML Moderate Fast，适合细线慢节奏，Down Shot、Neko Rig、Wacky Rig 以控松线和读轻口为主，不适合粗暴硬拔。</v>
       </c>
       <c r="AI136" t="str" s="1">
-        <v/>
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
       </c>
       <c r="AJ136" t="str" s="1">
         <v/>
@@ -20449,21 +20854,24 @@
         <v/>
       </c>
       <c r="AL136" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM136" t="str" s="1">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线和轻压场 / 6'9"直柄精细</v>
       </c>
       <c r="AN136" t="str" s="1">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>进阶泛用 / 6'9" ML Down Shot / Neko 精细</v>
       </c>
       <c r="AO136" t="str" s="1">
+        <v>进阶泛用直柄 6'9" ML Moderate Fast，6-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，适合细线慢拖、轻抖和看线；微弱咬口反馈比强力控鱼更重要。</v>
+      </c>
+      <c r="AP136" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods features a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP136" t="str" s="1">
+      <c r="AQ136" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ136" t="str" s="1">
+      <c r="AR136" t="str" s="1">
         <v>UPC: 036282079243; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -20568,10 +20976,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH137" t="str" s="2">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用直柄 6'3" M Moderate Fast，可承担小硬饵轻抛，Small Crankbait、Shad、Minnow 适合岸边搜索；鱼口放慢时切 Wacky / Down Shot 更稳。</v>
       </c>
       <c r="AI137" t="str" s="2">
-        <v/>
+        <v>Small Crankbait / Shad / Minnow / Wacky Rig / Down Shot</v>
       </c>
       <c r="AJ137" t="str" s="2">
         <v/>
@@ -20580,21 +20988,24 @@
         <v/>
       </c>
       <c r="AL137" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM137" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边小硬饵与轻量软饵 / 6'3"直柄搜索</v>
       </c>
       <c r="AN137" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 6'3" M 小硬饵兼 Wacky</v>
       </c>
       <c r="AO137" t="str" s="2">
+        <v>进阶泛用直柄 6'3" M Moderate Fast，6-12 lb线组配置下，Small Crankbait、Shad、Minnow 优先，适合小 crank / shad 轻抛；鱼口变慢时可切 Wacky 或 Down Shot。</v>
+      </c>
+      <c r="AP137" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods features a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP137" t="str" s="2">
+      <c r="AQ137" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ137" t="str" s="2">
+      <c r="AR137" t="str" s="2">
         <v>UPC: 036282075733; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -20699,10 +21110,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH138" t="str" s="2">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用直柄 6'6" M Fast，适合细线控饵，Neko Rig、Wacky Rig、Down Shot 的重点是松线管理和轻口判断，硬饵只做短距离补充。</v>
       </c>
       <c r="AI138" t="str" s="2">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ138" t="str" s="2">
         <v/>
@@ -20711,21 +21122,24 @@
         <v/>
       </c>
       <c r="AL138" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM138" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 6'6"直柄泛用</v>
       </c>
       <c r="AN138" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 6'6" M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO138" t="str" s="2">
+        <v>进阶泛用直柄 6'6" M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP138" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods features a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP138" t="str" s="2">
+      <c r="AQ138" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ138" t="str" s="2">
+      <c r="AR138" t="str" s="2">
         <v>UPC: 036282075740; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -20830,10 +21244,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH139" t="str" s="2">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用直柄 6'6" MH Fast，比常规精细竿更能承受稍重钓组，Shaky Head、Free Rig、Neko Rig 适合开阔结构和深一点的标点，仍以控线为先。</v>
       </c>
       <c r="AI139" t="str" s="2">
-        <v/>
+        <v>Shaky Head / Free Rig / Neko Rig / Small Swimbait / Swim Jig</v>
       </c>
       <c r="AJ139" t="str" s="2">
         <v/>
@@ -20842,21 +21256,24 @@
         <v/>
       </c>
       <c r="AL139" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM139" t="str" s="2">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开阔结构与稍重精细 / 6'6"直柄强精细</v>
       </c>
       <c r="AN139" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 6'6" MH Shaky Head / Free Rig 直柄</v>
       </c>
       <c r="AO139" t="str" s="2">
+        <v>进阶泛用直柄 6'6" MH Fast，8-14 lb线组配置下，Shaky Head、Free Rig、Neko Rig 优先，适合比常规精细更重的钓组；保留直柄控线优势，同时有更好的刺鱼余量。</v>
+      </c>
+      <c r="AP139" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods features a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP139" t="str" s="2">
+      <c r="AQ139" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ139" t="str" s="2">
+      <c r="AR139" t="str" s="2">
         <v>UPC: 036282075764; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -20961,10 +21378,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH140" t="str" s="2">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用直柄 6'9" ML Fast，适合细线慢节奏，Down Shot、Neko Rig、Wacky Rig 以控松线和读轻口为主，不适合粗暴硬拔。</v>
       </c>
       <c r="AI140" t="str" s="2">
-        <v/>
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
       </c>
       <c r="AJ140" t="str" s="2">
         <v/>
@@ -20973,21 +21390,24 @@
         <v/>
       </c>
       <c r="AL140" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM140" t="str" s="2">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线和轻压场 / 6'9"直柄精细</v>
       </c>
       <c r="AN140" t="str" s="2">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>进阶泛用 / 6'9" ML Down Shot / Neko 精细</v>
       </c>
       <c r="AO140" t="str" s="2">
+        <v>进阶泛用直柄 6'9" ML Fast，6-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，适合细线慢拖、轻抖和看线；微弱咬口反馈比强力控鱼更重要。</v>
+      </c>
+      <c r="AP140" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods features a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP140" t="str" s="2">
+      <c r="AQ140" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ140" t="str" s="2">
+      <c r="AR140" t="str" s="2">
         <v>UPC: 036282075788; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -21092,10 +21512,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH141" t="str" s="2">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用直柄 7' M Fast，适合细线控饵，Neko Rig、Wacky Rig、Down Shot 的重点是松线管理和轻口判断，硬饵只做短距离补充。</v>
       </c>
       <c r="AI141" t="str" s="2">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ141" t="str" s="2">
         <v/>
@@ -21104,21 +21524,24 @@
         <v/>
       </c>
       <c r="AL141" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM141" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'直柄泛用</v>
       </c>
       <c r="AN141" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 7' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO141" t="str" s="2">
+        <v>进阶泛用直柄 7' M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP141" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods features a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP141" t="str" s="2">
+      <c r="AQ141" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ141" t="str" s="2">
+      <c r="AR141" t="str" s="2">
         <v>UPC: 036282075795; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -21223,10 +21646,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH142" t="str" s="2">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用直柄 7' MH Fast，比常规精细竿更能承受稍重钓组，Shaky Head、Free Rig、Neko Rig 适合开阔结构和深一点的标点，仍以控线为先。</v>
       </c>
       <c r="AI142" t="str" s="2">
-        <v/>
+        <v>Shaky Head / Free Rig / Neko Rig / Small Swimbait / Swim Jig</v>
       </c>
       <c r="AJ142" t="str" s="2">
         <v/>
@@ -21235,21 +21658,24 @@
         <v/>
       </c>
       <c r="AL142" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM142" t="str" s="2">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开阔结构与稍重精细 / 7'直柄强精细</v>
       </c>
       <c r="AN142" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 7' MH Shaky Head / Free Rig 直柄</v>
       </c>
       <c r="AO142" t="str" s="2">
+        <v>进阶泛用直柄 7' MH Fast，8-14 lb线组配置下，Shaky Head、Free Rig、Neko Rig 优先，适合比常规精细更重的钓组；保留直柄控线优势，同时有更好的刺鱼余量。</v>
+      </c>
+      <c r="AP142" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods features a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP142" t="str" s="2">
+      <c r="AQ142" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ142" t="str" s="2">
+      <c r="AR142" t="str" s="2">
         <v>UPC: 036282075818; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -21354,10 +21780,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH143" t="str" s="2">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用直柄 7'4" M Fast，偏直柄精细泛用，Neko Rig、Wacky Rig、Down Shot 适合岸边轻量软饵；小 Minnow 只是补充搜索路线。</v>
       </c>
       <c r="AI143" t="str" s="2">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ143" t="str" s="2">
         <v/>
@@ -21366,21 +21792,24 @@
         <v/>
       </c>
       <c r="AL143" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM143" t="str" s="2">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'4"直柄泛用</v>
       </c>
       <c r="AN143" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 7'4" M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO143" t="str" s="2">
+        <v>进阶泛用直柄 7'4" M Fast，8-14 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP143" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods features a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP143" t="str" s="2">
+      <c r="AQ143" t="str" s="2">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ143" t="str" s="2">
+      <c r="AR143" t="str" s="2">
         <v>UPC: 036282075825; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -21485,10 +21914,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH144" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量直柄 6'10" ML Fast，用于清水或轻压场更自然，Down Shot、Neko Rig、Wacky Rig 动作要小，补刺靠节奏和线张力。</v>
       </c>
       <c r="AI144" t="str" s="1">
-        <v/>
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
       </c>
       <c r="AJ144" t="str" s="1">
         <v/>
@@ -21497,21 +21926,24 @@
         <v/>
       </c>
       <c r="AL144" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM144" t="str" s="1">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线和轻压场 / 6'10"直柄精细</v>
       </c>
       <c r="AN144" t="str" s="1">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>高阶轻量 / 6'10" ML Down Shot / Neko 精细</v>
       </c>
       <c r="AO144" t="str" s="1">
+        <v>高阶轻量直柄 6'10" ML Fast，6-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，适合细线慢拖、轻抖和看线；微弱咬口反馈比强力控鱼更重要。</v>
+      </c>
+      <c r="AP144" t="str" s="1">
         <v>Introducing the next generation of sleek design and high performance rods with the Fantasista X. Featuring premium carbon blanks and our proprietary Powerlux® 500 resin system, Fantasista X rods deliver sensitive, yet powerful ultra-light blanks with improved impact and fracture resistance. Fuji® reel seats coupled with EVA and carbon rear split grip design allow for reduced weight and increased sensitivity , which makes the Fantasista X one of our most extremely sensitive and lightweight-performing rods.</v>
       </c>
-      <c r="AP144" t="str" s="1">
+      <c r="AQ144" t="str" s="1">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ144" t="str" s="1">
+      <c r="AR144" t="str" s="1">
         <v>UPC: 036282078123</v>
       </c>
     </row>
@@ -21616,10 +22048,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH145" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量直柄 7' M Fast，用于 Neko / Wacky 更自然，Neko Rig、Wacky Rig、Down Shot 可覆盖轻量打点和慢节奏搜索，别用太重的饵压竿。</v>
       </c>
       <c r="AI145" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ145" t="str" s="1">
         <v/>
@@ -21628,21 +22060,24 @@
         <v/>
       </c>
       <c r="AL145" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM145" t="str" s="1">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'直柄泛用</v>
       </c>
       <c r="AN145" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>高阶轻量 / 7' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO145" t="str" s="1">
+        <v>高阶轻量直柄 7' M Fast，8-14 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP145" t="str" s="1">
         <v>Introducing the next generation of sleek design and high performance rods with the Fantasista X. Featuring premium carbon blanks and our proprietary Powerlux® 500 resin system, Fantasista X rods deliver sensitive, yet powerful ultra-light blanks with improved impact and fracture resistance. Fuji® reel seats coupled with EVA and carbon rear split grip design allow for reduced weight and increased sensitivity , which makes the Fantasista X one of our most extremely sensitive and lightweight-performing rods.</v>
       </c>
-      <c r="AP145" t="str" s="1">
+      <c r="AQ145" t="str" s="1">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ145" t="str" s="1">
+      <c r="AR145" t="str" s="1">
         <v>UPC: 036282078130</v>
       </c>
     </row>
@@ -21747,10 +22182,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH146" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量直柄 7' MH Fast，比常规精细竿更能承受稍重钓组，Shaky Head、Free Rig、Neko Rig 适合开阔结构和深一点的标点，仍以控线为先。</v>
       </c>
       <c r="AI146" t="str" s="1">
-        <v/>
+        <v>Shaky Head / Free Rig / Neko Rig / Small Swimbait / Swim Jig</v>
       </c>
       <c r="AJ146" t="str" s="1">
         <v/>
@@ -21759,21 +22194,24 @@
         <v/>
       </c>
       <c r="AL146" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM146" t="str" s="1">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开阔结构与稍重精细 / 7'直柄强精细</v>
       </c>
       <c r="AN146" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>高阶轻量 / 7' MH Shaky Head / Free Rig 直柄</v>
       </c>
       <c r="AO146" t="str" s="1">
+        <v>高阶轻量直柄 7' MH Fast，10-17 lb线组配置下，Shaky Head、Free Rig、Neko Rig 优先，适合比常规精细更重的钓组；保留直柄控线优势，同时有更好的刺鱼余量。</v>
+      </c>
+      <c r="AP146" t="str" s="1">
         <v>Introducing the next generation of sleek design and high performance rods with the Fantasista X. Featuring premium carbon blanks and our proprietary Powerlux® 500 resin system, Fantasista X rods deliver sensitive, yet powerful ultra-light blanks with improved impact and fracture resistance. Fuji® reel seats coupled with EVA and carbon rear split grip design allow for reduced weight and increased sensitivity , which makes the Fantasista X one of our most extremely sensitive and lightweight-performing rods.</v>
       </c>
-      <c r="AP146" t="str" s="1">
+      <c r="AQ146" t="str" s="1">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ146" t="str" s="1">
+      <c r="AR146" t="str" s="1">
         <v>UPC: 036282078147</v>
       </c>
     </row>
@@ -21878,10 +22316,10 @@
         <v>Stainless steel guide train</v>
       </c>
       <c r="AH147" t="str" s="2">
-        <v>耐用泛用，维护成本低</v>
+        <v>冰钓短竿直柄 27" M Moderate，适合冰洞边垂直控饵；Ice Jig、Jigging Spoon、Jigging Minnow 用轻抽、停顿和小幅抬落更自然，重点看轻口反馈。</v>
       </c>
       <c r="AI147" t="str" s="2">
-        <v/>
+        <v>Ice Jig / Jigging Spoon / Jigging Minnow / Small Minnow</v>
       </c>
       <c r="AJ147" t="str" s="2">
         <v/>
@@ -21890,21 +22328,24 @@
         <v/>
       </c>
       <c r="AL147" t="str" s="2">
-        <v>冰钓</v>
+        <v/>
       </c>
       <c r="AM147" t="str" s="2">
-        <v>短竿专项</v>
+        <v>冰钓 / 冰洞垂直轻抽 / 27"近距离控饵</v>
       </c>
       <c r="AN147" t="str" s="2">
-        <v>短竿冰钓设计 / 近距离控饵直接 / 手感反馈优先</v>
+        <v>冰钓短竿 / 27" M Ice Jig 垂直操作</v>
       </c>
       <c r="AO147" t="str" s="2">
+        <v>冰钓短竿直柄 27" M Moderate配置下，Ice Jig、Jigging Spoon、Jigging Minnow 是主轴，短竿在冰洞边控线更直接；轻抽、停顿和读轻口比远投覆盖更重要。</v>
+      </c>
+      <c r="AP147" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta® Ice rod features solid carbon blanks for durable sensitivity and high density EVA handles for comfort on the ice.</v>
       </c>
-      <c r="AP147" t="str" s="2">
+      <c r="AQ147" t="str" s="2">
         <v>Feature: Solid carbon blanks for increased sensitivity and durability</v>
       </c>
-      <c r="AQ147" t="str" s="2">
+      <c r="AR147" t="str" s="2">
         <v>UPC: 036282076846</v>
       </c>
     </row>
@@ -22009,10 +22450,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH148" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量直柄 6'10" ML Extra Fast，用于清水或轻压场更自然，Down Shot、Neko Rig、Wacky Rig 动作要小，补刺靠节奏和线张力。</v>
       </c>
       <c r="AI148" t="str" s="1">
-        <v/>
+        <v>Down Shot / Neko Rig / Wacky Rig / No Sinker / Small Jighead</v>
       </c>
       <c r="AJ148" t="str" s="1">
         <v/>
@@ -22021,21 +22462,24 @@
         <v/>
       </c>
       <c r="AL148" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM148" t="str" s="1">
-        <v>直柄精细轻饵</v>
+        <v>淡水 Bass / 清水细线和轻压场 / 6'10"直柄精细</v>
       </c>
       <c r="AN148" t="str" s="1">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>高阶轻量 / 6'10" ML Down Shot / Neko 精细</v>
       </c>
       <c r="AO148" t="str" s="1">
+        <v>高阶轻量直柄 6'10" ML Extra Fast，4-10 lb线组配置下，Down Shot、Neko Rig、Wacky Rig 优先，适合细线慢拖、轻抖和看线；微弱咬口反馈比强力控鱼更重要。</v>
+      </c>
+      <c r="AP148" t="str" s="1">
         <v>Introducing Abu Garcia’s lightest rod series with the Abu Garcia® Zenon™ rods. Featuring premium carbon blanks and our exclusive Powerlux® 1000 resin system, these rods deliver powerful ultra-light sensitive blanks with higher break strengths and improved impact and fracture resistance without increasing overall weight or blank diameters. Fuji® reel seat improves comfort for all-day fishing. Coupled with titanium alloy guides with super thin zirconia inserts and a carbon handle split grip design, the Abu Garcia Zenon rods are optimized for performance.</v>
       </c>
-      <c r="AP148" t="str" s="1">
+      <c r="AQ148" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ148" t="str" s="1">
+      <c r="AR148" t="str" s="1">
         <v>UPC: 036282144293</v>
       </c>
     </row>
@@ -22140,10 +22584,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH149" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量直柄 7' M Fast，偏直柄精细泛用，Neko Rig、Wacky Rig、Down Shot 适合岸边轻量软饵；小 Minnow 只是补充搜索路线。</v>
       </c>
       <c r="AI149" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Wacky Rig / Down Shot / No Sinker / Small Minnow</v>
       </c>
       <c r="AJ149" t="str" s="1">
         <v/>
@@ -22152,21 +22596,24 @@
         <v/>
       </c>
       <c r="AL149" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM149" t="str" s="1">
-        <v>直柄泛用</v>
+        <v>淡水 Bass / 岸边轻量软饵和小硬饵 / 7'直柄泛用</v>
       </c>
       <c r="AN149" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>高阶轻量 / 7' M Neko / Wacky 精细泛用</v>
       </c>
       <c r="AO149" t="str" s="1">
+        <v>高阶轻量直柄 7' M Fast，6-12 lb线组配置下，Neko Rig、Wacky Rig、Down Shot 优先，适合细线控松线和轻量抛投；小 Minnow 作为搜索补充路线。</v>
+      </c>
+      <c r="AP149" t="str" s="1">
         <v>Introducing Abu Garcia’s lightest rod series with the Abu Garcia® Zenon™ rods. Featuring premium carbon blanks and our exclusive Powerlux® 1000 resin system, these rods deliver powerful ultra-light sensitive blanks with higher break strengths and improved impact and fracture resistance without increasing overall weight or blank diameters. Fuji® reel seat improves comfort for all-day fishing. Coupled with titanium alloy guides with super thin zirconia inserts and a carbon handle split grip design, the Abu Garcia Zenon rods are optimized for performance.</v>
       </c>
-      <c r="AP149" t="str" s="1">
+      <c r="AQ149" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ149" t="str" s="1">
+      <c r="AR149" t="str" s="1">
         <v>UPC: 036282144309</v>
       </c>
     </row>
@@ -22271,10 +22718,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH150" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量直柄 7' MH Fast，比常规精细竿更能承受稍重钓组，Shaky Head、Free Rig、Neko Rig 适合开阔结构和深一点的标点，仍以控线为先。</v>
       </c>
       <c r="AI150" t="str" s="1">
-        <v/>
+        <v>Shaky Head / Free Rig / Neko Rig / Small Swimbait / Swim Jig</v>
       </c>
       <c r="AJ150" t="str" s="1">
         <v/>
@@ -22283,21 +22730,24 @@
         <v/>
       </c>
       <c r="AL150" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM150" t="str" s="1">
-        <v>直柄强力泛用</v>
+        <v>淡水 Bass / 开阔结构与稍重精细 / 7'直柄强精细</v>
       </c>
       <c r="AN150" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>高阶轻量 / 7' MH Shaky Head / Free Rig 直柄</v>
       </c>
       <c r="AO150" t="str" s="1">
+        <v>高阶轻量直柄 7' MH Fast，8-15 lb线组配置下，Shaky Head、Free Rig、Neko Rig 优先，适合比常规精细更重的钓组；保留直柄控线优势，同时有更好的刺鱼余量。</v>
+      </c>
+      <c r="AP150" t="str" s="1">
         <v>Introducing Abu Garcia’s lightest rod series with the Abu Garcia® Zenon™ rods. Featuring premium carbon blanks and our exclusive Powerlux® 1000 resin system, these rods deliver powerful ultra-light sensitive blanks with higher break strengths and improved impact and fracture resistance without increasing overall weight or blank diameters. Fuji® reel seat improves comfort for all-day fishing. Coupled with titanium alloy guides with super thin zirconia inserts and a carbon handle split grip design, the Abu Garcia Zenon rods are optimized for performance.</v>
       </c>
-      <c r="AP150" t="str" s="1">
+      <c r="AQ150" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ150" t="str" s="1">
+      <c r="AR150" t="str" s="1">
         <v>UPC: 036282144316</v>
       </c>
     </row>
@@ -22402,10 +22852,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH151" t="str" s="2">
-        <v>maximized casting distance with lighter lures / finesse / lightweight lure use</v>
+        <v>高阶轻量枪柄 7'1" ML Moderate Fast，适合细线小卷阻饵，Small Crankbait、Shad Crank、Small Minnow 可低弹道进入窄标点；鱼口变轻时再切 No Sinker / Neko。</v>
       </c>
       <c r="AI151" t="str" s="2">
-        <v/>
+        <v>Small Crankbait / Shad Crank / Small Minnow / No Sinker / Neko Rig</v>
       </c>
       <c r="AJ151" t="str" s="2">
         <v/>
@@ -22414,21 +22864,24 @@
         <v/>
       </c>
       <c r="AL151" t="str" s="2">
-        <v>淡水 / bass / BFS</v>
+        <v/>
       </c>
       <c r="AM151" t="str" s="2">
-        <v>BFS 卷阻饵 / 精细搜索</v>
+        <v>淡水 Bass / 小河道与近岸浅中层 / 7'1"BFS 卷阻搜索</v>
       </c>
       <c r="AN151" t="str" s="2">
-        <v>轻饵抛投和卷阻饵节奏兼顾 / 适合小型 moving bait、搜索和精细控线</v>
+        <v>高阶轻量 / 7'1" ML BFS 小 crank / 小 minnow</v>
       </c>
       <c r="AO151" t="str" s="2">
+        <v>高阶轻量枪柄 7'1" ML Moderate Fast，6-12 lb线组配置下，Small Crankbait、Shad Crank、Small Minnow 优先，轻量卷阻饵可以低弹道抛进窄标点；细线下还能切回 Neko / No Sinker。</v>
+      </c>
+      <c r="AP151" t="str" s="2">
         <v>Introducing Abu Garcia’s lightest rod series with the Abu Garcia® Zenon™ rods. The NEW Bait Finesse models feature the perfect power and action to throw lightweight baits. Featuring premium carbon blanks and our exclusive Powerlux® 1000 resin system, these rods deliver powerful ultra-light sensitive blanks with higher break strengths and improved impact and fracture resistance without increasing overall weight or blank diameters. Fuji® reel seat improves comfort for all-day fishing. Coupled with titanium alloy guides with nitride silicon inserts and a carbon handle split grip design, the Abu Garcia Zenon rods are optimized for performance.</v>
       </c>
-      <c r="AP151" t="str" s="2">
+      <c r="AQ151" t="str" s="2">
         <v>Feature: Powerlux® 1000 delivers Abu Garcia’s lightest and most sensitive rod ever</v>
       </c>
-      <c r="AQ151" t="str" s="2">
+      <c r="AR151" t="str" s="2">
         <v>UPC: 036282118058</v>
       </c>
     </row>
@@ -22533,10 +22986,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH152" t="str" s="1">
-        <v>maximized casting distance with lighter lures / finesse / lightweight lure use</v>
+        <v>高阶轻量枪柄 7'1" M Fast，核心是轻饵启动和控线，Small Minnow、Shad、Small Crankbait 适合小标点低弹道抛投，软硬饵切换要控制饵重上限。</v>
       </c>
       <c r="AI152" t="str" s="1">
-        <v/>
+        <v>Small Minnow / Shad / Small Crankbait / Neko Rig / No Sinker</v>
       </c>
       <c r="AJ152" t="str" s="1">
         <v/>
@@ -22545,21 +22998,24 @@
         <v/>
       </c>
       <c r="AL152" t="str" s="1">
-        <v>淡水 / bass / BFS</v>
+        <v/>
       </c>
       <c r="AM152" t="str" s="1">
-        <v>精细轻饵</v>
+        <v>淡水 Bass / 小场地细线轻饵 / 7'1"枪柄 BFS</v>
       </c>
       <c r="AN152" t="str" s="1">
-        <v>小饵抛投更轻松 / 精细操控直接 / 适合轻量硬饵和小型钓组</v>
+        <v>高阶轻量 / 7'1" M BFS 精细轻饵</v>
       </c>
       <c r="AO152" t="str" s="1">
+        <v>高阶轻量枪柄 7'1" M Fast，8-15 lb线组配置下，Small Minnow、Shad、Small Crankbait 优先，低弹道轻抛和细线控线是核心；鱼口变轻时可在小硬饵与软饵间切换。</v>
+      </c>
+      <c r="AP152" t="str" s="1">
         <v>Introducing Abu Garcia’s lightest rod series with the Abu Garcia® Zenon™ rods. The NEW Bait Finesse models feature the perfect power and action to throw lightweight baits. Featuring premium carbon blanks and our exclusive Powerlux® 1000 resin system, these rods deliver powerful ultra-light sensitive blanks with higher break strengths and improved impact and fracture resistance without increasing overall weight or blank diameters. Fuji® reel seat improves comfort for all-day fishing. Coupled with titanium alloy guides with nitride silicon inserts and a carbon handle split grip design, the Abu Garcia Zenon rods are optimized for performance.</v>
       </c>
-      <c r="AP152" t="str" s="1">
+      <c r="AQ152" t="str" s="1">
         <v>Feature: Powerlux® 1000 delivers Abu Garcia’s lightest and most sensitive rod ever</v>
       </c>
-      <c r="AQ152" t="str" s="1">
+      <c r="AR152" t="str" s="1">
         <v>UPC: 036282118065</v>
       </c>
     </row>
@@ -22664,33 +23120,36 @@
         <v>Stainless steel / aluminum oxide guide train</v>
       </c>
       <c r="AH153" t="str" s="2">
-        <v>耐用泛用，适合日常淡水路亚</v>
+        <v>入门耐用枪柄 6'6" MH Fast，更适合 Texas / Jig 路线，Texas Rig、Rubber Jig、Free Rig 先保证落点和读底，鱼活性高时可切移动饵提高覆盖。</v>
       </c>
       <c r="AI153" t="str" s="2">
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
+      </c>
+      <c r="AJ153" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ153" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK153" t="str" s="2">
         <v/>
       </c>
       <c r="AL153" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM153" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 6'6"中重型底操</v>
       </c>
       <c r="AN153" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>入门耐用 / 6'6" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO153" t="str" s="2">
+        <v>入门耐用枪柄 6'6" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP153" t="str" s="2">
         <v>The updated Vengeance series of fishing rods delivers on-the-water performance and style in a balanced, lightweight design. Construction starts with a 24-ton intermediate modulus graphite blank that is paired with stainless steel guides. Split grip EVA handles ensure comfort and durability for the long haul. The Vengeance series of casting rods delivers excellent performance at a great value.</v>
       </c>
-      <c r="AP153" t="str" s="2">
+      <c r="AQ153" t="str" s="2">
         <v>Guide Type: Stainless Steel/Aluminum Oxide</v>
       </c>
-      <c r="AQ153" t="str" s="2">
+      <c r="AR153" t="str" s="2">
         <v>UPC: 036282117679; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -22795,33 +23254,36 @@
         <v>Stainless steel / aluminum oxide guide train</v>
       </c>
       <c r="AH154" t="str" s="2">
-        <v>耐用泛用，适合日常淡水路亚</v>
+        <v>入门耐用枪柄 6'9" MH Fast，用于 cover 外缘和硬结构慢拖，Texas Rig、Rubber Jig、Free Rig 的优势在刺鱼余量和软硬饵切换宽容。</v>
       </c>
       <c r="AI154" t="str" s="2">
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
+      </c>
+      <c r="AJ154" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ154" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK154" t="str" s="2">
         <v/>
       </c>
       <c r="AL154" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM154" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 6'9"中重型底操</v>
       </c>
       <c r="AN154" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>入门耐用 / 6'9" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO154" t="str" s="2">
+        <v>入门耐用枪柄 6'9" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP154" t="str" s="2">
         <v>The updated Vengeance series of fishing rods delivers on-the-water performance and style in a balanced, lightweight design. Construction starts with a 24-ton intermediate modulus graphite blank that is paired with stainless steel guides. Split grip EVA handles ensure comfort and durability for the long haul. The Vengeance series of casting rods delivers excellent performance at a great value.</v>
       </c>
-      <c r="AP154" t="str" s="2">
+      <c r="AQ154" t="str" s="2">
         <v>Guide Type: Stainless Steel/Aluminum Oxide</v>
       </c>
-      <c r="AQ154" t="str" s="2">
+      <c r="AR154" t="str" s="2">
         <v>UPC: 036282117686; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -22926,33 +23388,36 @@
         <v>Stainless steel / aluminum oxide guide train</v>
       </c>
       <c r="AH155" t="str" s="2">
-        <v>耐用泛用，适合日常淡水路亚</v>
+        <v>入门耐用枪柄 7' M Extra Fast，抛投负担较轻，Texas Rig、Free Rig、Rubber Jig 适合短中距离打点；需要搜索时再切 Spinnerbait / Chatterbait。</v>
       </c>
       <c r="AI155" t="str" s="2">
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
+      </c>
+      <c r="AJ155" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ155" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK155" t="str" s="2">
         <v/>
       </c>
       <c r="AL155" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM155" t="str" s="2">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 7'轻中量底操</v>
       </c>
       <c r="AN155" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>入门耐用 / 7' M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO155" t="str" s="2">
+        <v>入门耐用枪柄 7' M Extra Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP155" t="str" s="2">
         <v>The updated Vengeance series of fishing rods delivers on-the-water performance and style in a balanced, lightweight design. Construction starts with a 24-ton intermediate modulus graphite blank that is paired with stainless steel guides. Split grip EVA handles ensure comfort and durability for the long haul. The Vengeance series of casting rods delivers excellent performance at a great value.</v>
       </c>
-      <c r="AP155" t="str" s="2">
+      <c r="AQ155" t="str" s="2">
         <v>Guide Type: Stainless Steel/Aluminum Oxide</v>
       </c>
-      <c r="AQ155" t="str" s="2">
+      <c r="AR155" t="str" s="2">
         <v>UPC: 036282117693; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -23057,33 +23522,36 @@
         <v>Stainless steel / aluminum oxide guide train</v>
       </c>
       <c r="AH156" t="str" s="2">
-        <v>耐用泛用，适合日常淡水路亚</v>
+        <v>入门耐用枪柄 7' M Moderate Fast，以稳定卷收为核心，Crankbait、Shad Crank、Squarebill 适合沿草边、石滩和浅中层水线搜索，短咬时不宜立刻大幅扬竿。</v>
       </c>
       <c r="AI156" t="str" s="2">
+        <v>Crankbait / Shad Crank / Squarebill / Lipless Crankbait / Chatterbait</v>
+      </c>
+      <c r="AJ156" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ156" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK156" t="str" s="2">
         <v/>
       </c>
       <c r="AL156" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM156" t="str" s="2">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 开阔水域卷阻搜索 / 7'Crankbait</v>
       </c>
       <c r="AN156" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>入门耐用 / 7' M crankbait / shad 专项</v>
       </c>
       <c r="AO156" t="str" s="2">
+        <v>入门耐用枪柄 7' M Moderate Fast，8-17 lb线组配置下，Crankbait、Shad Crank、Squarebill 优先，稳定卷收和挂鱼缓冲比快速刺鱼更关键；适合沿草边、石滩和浅中层水线搜索。</v>
+      </c>
+      <c r="AP156" t="str" s="2">
         <v>The updated Vengeance series of fishing rods delivers on-the-water performance and style in a balanced, lightweight design. Construction starts with a 24-ton intermediate modulus graphite blank that is paired with stainless steel guides. Split grip EVA handles ensure comfort and durability for the long haul. The Vengeance series of casting rods delivers excellent performance at a great value.</v>
       </c>
-      <c r="AP156" t="str" s="2">
+      <c r="AQ156" t="str" s="2">
         <v>Guide Type: Stainless Steel/Aluminum Oxide</v>
       </c>
-      <c r="AQ156" t="str" s="2">
+      <c r="AR156" t="str" s="2">
         <v>UPC: 036282117709; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -23188,33 +23656,36 @@
         <v>Stainless steel / aluminum oxide guide train</v>
       </c>
       <c r="AH157" t="str" s="2">
-        <v>耐用泛用，适合日常淡水路亚</v>
+        <v>入门耐用枪柄 7' MH Fast，用于 cover 外缘和硬结构慢拖，Texas Rig、Rubber Jig、Free Rig 的优势在刺鱼余量和软硬饵切换宽容。</v>
       </c>
       <c r="AI157" t="str" s="2">
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
+      </c>
+      <c r="AJ157" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ157" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK157" t="str" s="2">
         <v/>
       </c>
       <c r="AL157" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM157" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'中重型底操</v>
       </c>
       <c r="AN157" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>入门耐用 / 7' MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO157" t="str" s="2">
+        <v>入门耐用枪柄 7' MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP157" t="str" s="2">
         <v>The updated Vengeance series of fishing rods delivers on-the-water performance and style in a balanced, lightweight design. Construction starts with a 24-ton intermediate modulus graphite blank that is paired with stainless steel guides. Split grip EVA handles ensure comfort and durability for the long haul. The Vengeance series of casting rods delivers excellent performance at a great value.</v>
       </c>
-      <c r="AP157" t="str" s="2">
+      <c r="AQ157" t="str" s="2">
         <v>Guide Type: Stainless Steel/Aluminum Oxide</v>
       </c>
-      <c r="AQ157" t="str" s="2">
+      <c r="AR157" t="str" s="2">
         <v>UPC: 036282117716; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -23319,33 +23790,36 @@
         <v>Stainless steel / aluminum oxide guide train</v>
       </c>
       <c r="AH158" t="str" s="2">
-        <v>耐用泛用，适合日常淡水路亚</v>
+        <v>入门耐用枪柄 7'3" MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI158" t="str" s="2">
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
+      </c>
+      <c r="AJ158" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ158" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK158" t="str" s="2">
         <v/>
       </c>
       <c r="AL158" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM158" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'3"中重型底操</v>
       </c>
       <c r="AN158" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>入门耐用 / 7'3" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO158" t="str" s="2">
+        <v>入门耐用枪柄 7'3" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP158" t="str" s="2">
         <v>The updated Vengeance series of fishing rods delivers on-the-water performance and style in a balanced, lightweight design. Construction starts with a 24-ton intermediate modulus graphite blank that is paired with stainless steel guides. Split grip EVA handles ensure comfort and durability for the long haul. The Vengeance series of casting rods delivers excellent performance at a great value.</v>
       </c>
-      <c r="AP158" t="str" s="2">
+      <c r="AQ158" t="str" s="2">
         <v>Guide Type: Stainless Steel/Aluminum Oxide</v>
       </c>
-      <c r="AQ158" t="str" s="2">
+      <c r="AR158" t="str" s="2">
         <v>UPC: 036282117723; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -23450,33 +23924,36 @@
         <v>Stainless steel / aluminum oxide guide train</v>
       </c>
       <c r="AH159" t="str" s="2">
-        <v>耐用泛用，适合日常淡水路亚</v>
+        <v>入门耐用枪柄 7'3" H Fast，适合草面搜索和重 cover 控鱼，Frog、Punching、Heavy Texas 的重点是抛准、等口和出障速度。</v>
       </c>
       <c r="AI159" t="str" s="2">
+        <v>Frog / Punching / Heavy Texas / Swim Jig / Heavy Cover Jig</v>
+      </c>
+      <c r="AJ159" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ159" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK159" t="str" s="2">
         <v/>
       </c>
       <c r="AL159" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM159" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 浮草草垫与浅水 cover / 7'3"Frog</v>
       </c>
       <c r="AN159" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>入门耐用 / 7'3" H Frog / cover 强控鱼</v>
       </c>
       <c r="AO159" t="str" s="2">
+        <v>入门耐用枪柄 7'3" H Fast，12-25 lb线组配置下，Frog、Punching、Heavy Texas 优先，草面开口后需要快速收线和压住鱼；兼顾 Punching 时更看重腰力和容错。</v>
+      </c>
+      <c r="AP159" t="str" s="2">
         <v>The updated Vengeance series of fishing rods delivers on-the-water performance and style in a balanced, lightweight design. Construction starts with a 24-ton intermediate modulus graphite blank that is paired with stainless steel guides. Split grip EVA handles ensure comfort and durability for the long haul. The Vengeance series of casting rods delivers excellent performance at a great value.</v>
       </c>
-      <c r="AP159" t="str" s="2">
+      <c r="AQ159" t="str" s="2">
         <v>Guide Type: Stainless Steel/Aluminum Oxide</v>
       </c>
-      <c r="AQ159" t="str" s="2">
+      <c r="AR159" t="str" s="2">
         <v>UPC: 036282117730; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -23581,33 +24058,36 @@
         <v>Stainless steel / aluminum oxide guide train</v>
       </c>
       <c r="AH160" t="str" s="2">
-        <v>耐用泛用，适合日常淡水路亚</v>
+        <v>入门耐用枪柄 7'6" H Fast，偏重线底操，Heavy Texas、Rubber Jig、Football Jig 适合木桩、石堆和厚草边慢拖，重点是读底后稳定刺鱼。</v>
       </c>
       <c r="AI160" t="str" s="2">
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
+      </c>
+      <c r="AJ160" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ160" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK160" t="str" s="2">
         <v/>
       </c>
       <c r="AL160" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM160" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'6"强力底操</v>
       </c>
       <c r="AN160" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>入门耐用 / 7'6" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO160" t="str" s="2">
+        <v>入门耐用枪柄 7'6" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP160" t="str" s="2">
         <v>The updated Vengeance series of fishing rods delivers on-the-water performance and style in a balanced, lightweight design. Construction starts with a 24-ton intermediate modulus graphite blank that is paired with stainless steel guides. Split grip EVA handles ensure comfort and durability for the long haul. The Vengeance series of casting rods delivers excellent performance at a great value.</v>
       </c>
-      <c r="AP160" t="str" s="2">
+      <c r="AQ160" t="str" s="2">
         <v>Guide Type: Stainless Steel/Aluminum Oxide</v>
       </c>
-      <c r="AQ160" t="str" s="2">
+      <c r="AR160" t="str" s="2">
         <v>UPC: 036282117747; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -23712,33 +24192,36 @@
         <v>Stainless steel / aluminum oxide guide train</v>
       </c>
       <c r="AH161" t="str" s="2">
-        <v>耐用泛用，适合日常淡水路亚</v>
+        <v>入门耐用枪柄 6'6" M Fast，抛投负担较轻，Texas Rig、Free Rig、Rubber Jig 适合短中距离打点；需要搜索时再切 Spinnerbait / Chatterbait。</v>
       </c>
       <c r="AI161" t="str" s="2">
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
+      </c>
+      <c r="AJ161" t="str" s="2">
         <v>1</v>
       </c>
-      <c r="AJ161" t="str" s="2">
-        <v/>
-      </c>
       <c r="AK161" t="str" s="2">
         <v/>
       </c>
       <c r="AL161" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM161" t="str" s="2">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 6'6"轻中量底操</v>
       </c>
       <c r="AN161" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>入门耐用 / 6'6" M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO161" t="str" s="2">
+        <v>入门耐用枪柄 6'6" M Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP161" t="str" s="2">
         <v>The updated Vengeance series of fishing rods delivers on-the-water performance and style in a balanced, lightweight design. Construction starts with a 24-ton intermediate modulus graphite blank that is paired with stainless steel guides. Split grip EVA handles ensure comfort and durability for the long haul. The Vengeance series of casting rods delivers excellent performance at a great value.</v>
       </c>
-      <c r="AP161" t="str" s="2">
+      <c r="AQ161" t="str" s="2">
         <v>Guide Type: Stainless Steel/Aluminum Oxide</v>
       </c>
-      <c r="AQ161" t="str" s="2">
+      <c r="AR161" t="str" s="2">
         <v>UPC: 036282117662; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -23843,10 +24326,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH162" t="str" s="1">
-        <v>maximized casting distance with lighter lures / technique-specific actions</v>
+        <v>Flipping 枪柄 7'6" MH Fast，更适合近距离 pitching / flipping，Flipping Jig、Punching、Heavy Texas 以落点和入障角度为先，回线不能拖泥带水。</v>
       </c>
       <c r="AI162" t="str" s="1">
-        <v/>
+        <v>Flipping Jig / Punching / Heavy Texas / Creature Bait / Heavy Cover Jig</v>
       </c>
       <c r="AJ162" t="str" s="1">
         <v/>
@@ -23855,21 +24338,24 @@
         <v/>
       </c>
       <c r="AL162" t="str" s="1">
-        <v>淡水 / bass / 重障碍</v>
+        <v/>
       </c>
       <c r="AM162" t="str" s="1">
-        <v>Flipping / cover 打点</v>
+        <v>淡水 Bass / 草洞木桩与密集 cover / 7'6"重障碍打点</v>
       </c>
       <c r="AN162" t="str" s="1">
-        <v>适合重障碍打点 / 近距离投放更稳 / 强控鱼能力更突出</v>
+        <v>Flipping / 7'6" MH Flipping / Punching 打点</v>
       </c>
       <c r="AO162" t="str" s="1">
+        <v>Flipping 枪柄 7'6" MH Fast，12-25 lb线组配置下，Flipping Jig、Punching、Heavy Texas 优先，适合近距离低弹道入障；12-25 lb 线组下刺鱼和把鱼拉离 cover 是主要价值。</v>
+      </c>
+      <c r="AP162" t="str" s="1">
         <v>"Whether you are flipping or pitching big lures into dense cover or targeting shallow cover, my extra heavy and medium heavy flipping rods are designed to get the job done. These powerful, yet lightweight flipping rods have both the backbone and parabolic action needed to maximize your hook penetration on hook sets. Developed with sensitivity and power in mind, these are the ultimate flipping sticks!" - Hunter Shryock</v>
       </c>
-      <c r="AP162" t="str" s="1">
+      <c r="AQ162" t="str" s="1">
         <v>Feature: 36-Ton graphite with Powerlux™ 200 resin</v>
       </c>
-      <c r="AQ162" t="str" s="1">
+      <c r="AR162" t="str" s="1">
         <v>UPC: 036282103344; Reel Seat: Abu Garcia custom ergonomic reel seat</v>
       </c>
     </row>
@@ -23974,10 +24460,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH163" t="str" s="2">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>卷阻专用枪柄 7'5" MH Fast，以稳定卷收为核心，Deep Crankbait、Crankbait、Lipless Crankbait 适合沿草边、石滩和浅中层水线搜索，短咬时不宜立刻大幅扬竿。</v>
       </c>
       <c r="AI163" t="str" s="2">
-        <v/>
+        <v>Deep Crankbait / Crankbait / Lipless Crankbait / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ163" t="str" s="2">
         <v/>
@@ -23986,21 +24472,24 @@
         <v/>
       </c>
       <c r="AL163" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM163" t="str" s="2">
-        <v>卷阻饵 / 搜索</v>
+        <v>淡水 Bass / 开阔水域卷阻搜索 / 7'5"Crankbait</v>
       </c>
       <c r="AN163" t="str" s="2">
-        <v>适合 crankbait 和 moving bait / 卷收节奏稳定 / 搜索型作钓更顺手</v>
+        <v>卷阻专用 / 7'5" MH crankbait / shad 专项</v>
       </c>
       <c r="AO163" t="str" s="2">
+        <v>卷阻专用枪柄 7'5" MH Fast，12-20 lb线组配置下，Deep Crankbait、Crankbait、Lipless Crankbait 优先，稳定卷收和挂鱼缓冲比快速刺鱼更关键；适合沿草边、石滩和浅中层水线搜索。</v>
+      </c>
+      <c r="AP163" t="str" s="2">
         <v>Optimized for performance, the Abu Garcia® Winch series of rods are designed specifically for anglers using crankbait techniques. Featuring cork and high density EVA grips and ergonomic Fuji® reel seats, the Winch series is built with a custom composite construction for a more moderate action, making it perfect for fishing crankbaits.</v>
       </c>
-      <c r="AP163" t="str" s="2">
+      <c r="AQ163" t="str" s="2">
         <v>Feature: Composite blend construction</v>
       </c>
-      <c r="AQ163" t="str" s="2">
+      <c r="AR163" t="str" s="2">
         <v>UPC: 036282982420; Reel Seat: Fuji reel seat</v>
       </c>
     </row>
@@ -24105,10 +24594,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH164" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 6'10" ML Fast，适合细线轻饵打点，Neko Rig、Down Shot、No Sinker 要控制落点和松线；小 crank 可做短距离搜索补充。</v>
       </c>
       <c r="AI164" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Small Crankbait</v>
       </c>
       <c r="AJ164" t="str" s="1">
         <v/>
@@ -24117,21 +24606,24 @@
         <v/>
       </c>
       <c r="AL164" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM164" t="str" s="1">
-        <v>枪柄精细轻饵</v>
+        <v>淡水 Bass / 小场地轻线打点 / 6'10"枪柄精细轻饵</v>
       </c>
       <c r="AN164" t="str" s="1">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>轻量高感 / 6'10" ML Neko / No Sinker 轻量打点</v>
       </c>
       <c r="AO164" t="str" s="1">
+        <v>轻量高感枪柄 6'10" ML Fast，6-12 lb线组配置下，Neko Rig、Down Shot、No Sinker 优先，适合小标点低弹道抛投；小 crank 只作为补充搜索路线。</v>
+      </c>
+      <c r="AP164" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and Winn® advanced polymer Dri-Tac grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP164" t="str" s="1">
+      <c r="AQ164" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ164" t="str" s="1">
+      <c r="AR164" t="str" s="1">
         <v>UPC: 036282031906; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -24236,10 +24728,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH165" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7' M Fast，适合轻中量底操，Texas Rig、Free Rig、Rubber Jig 可以打岸边硬物和稀疏 cover；移动饵只是活性高时的补充。</v>
       </c>
       <c r="AI165" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ165" t="str" s="1">
         <v/>
@@ -24248,21 +24740,24 @@
         <v/>
       </c>
       <c r="AL165" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM165" t="str" s="1">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 7'轻中量底操</v>
       </c>
       <c r="AN165" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>轻量高感 / 7' M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO165" t="str" s="1">
+        <v>轻量高感枪柄 7' M Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP165" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and Winn® advanced polymer Dri-Tac grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP165" t="str" s="1">
+      <c r="AQ165" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ165" t="str" s="1">
+      <c r="AR165" t="str" s="1">
         <v>UPC: 036282031913; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -24367,10 +24862,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH166" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7' MH Extra Fast，用于 cover 外缘和硬结构慢拖，Texas Rig、Rubber Jig、Free Rig 的优势在刺鱼余量和软硬饵切换宽容。</v>
       </c>
       <c r="AI166" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ166" t="str" s="1">
         <v/>
@@ -24379,21 +24874,24 @@
         <v/>
       </c>
       <c r="AL166" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM166" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'中重型底操</v>
       </c>
       <c r="AN166" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 7' MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO166" t="str" s="1">
+        <v>轻量高感枪柄 7' MH Extra Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP166" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and Winn® advanced polymer Dri-Tac grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP166" t="str" s="1">
+      <c r="AQ166" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ166" t="str" s="1">
+      <c r="AR166" t="str" s="1">
         <v>UPC: 036282031920; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -24498,10 +24996,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH167" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7'3" MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI167" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ167" t="str" s="1">
         <v/>
@@ -24510,21 +25008,24 @@
         <v/>
       </c>
       <c r="AL167" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM167" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'3"中重型底操</v>
       </c>
       <c r="AN167" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 7'3" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO167" t="str" s="1">
+        <v>轻量高感枪柄 7'3" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP167" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and Winn® advanced polymer Dri-Tac grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP167" t="str" s="1">
+      <c r="AQ167" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ167" t="str" s="1">
+      <c r="AR167" t="str" s="1">
         <v>UPC: 036282031937; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -24629,10 +25130,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH168" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7'4" MH Fast，更适合 Texas / Jig 路线，Texas Rig、Rubber Jig、Free Rig 先保证落点和读底，鱼活性高时可切移动饵提高覆盖。</v>
       </c>
       <c r="AI168" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ168" t="str" s="1">
         <v/>
@@ -24641,21 +25142,24 @@
         <v/>
       </c>
       <c r="AL168" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM168" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'4"中重型底操</v>
       </c>
       <c r="AN168" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 7'4" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO168" t="str" s="1">
+        <v>轻量高感枪柄 7'4" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP168" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and Winn® advanced polymer Dri-Tac grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP168" t="str" s="1">
+      <c r="AQ168" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ168" t="str" s="1">
+      <c r="AR168" t="str" s="1">
         <v>UPC: 036282031944; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -24760,10 +25264,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH169" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7'6" H Fast，偏重线底操，Heavy Texas、Rubber Jig、Football Jig 适合木桩、石堆和厚草边慢拖，重点是读底后稳定刺鱼。</v>
       </c>
       <c r="AI169" t="str" s="1">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ169" t="str" s="1">
         <v/>
@@ -24772,21 +25276,24 @@
         <v/>
       </c>
       <c r="AL169" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM169" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'6"强力底操</v>
       </c>
       <c r="AN169" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 7'6" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO169" t="str" s="1">
+        <v>轻量高感枪柄 7'6" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP169" t="str" s="1">
         <v>Introducing the next generation of Veritas rods. The introduction of Powerlux® 100 increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and Winn® advanced polymer Dri-Tac grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP169" t="str" s="1">
+      <c r="AQ169" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ169" t="str" s="1">
+      <c r="AR169" t="str" s="1">
         <v>UPC: 036282031951; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -24891,10 +25398,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH170" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7' H Extra Fast，用于强结构打点时，Heavy Texas、Rubber Jig、Football Jig 要让饵贴底通过障碍；中鱼后用竿腰把鱼带出标点。</v>
       </c>
       <c r="AI170" t="str" s="2">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ170" t="str" s="2">
         <v/>
@@ -24903,21 +25410,24 @@
         <v/>
       </c>
       <c r="AL170" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM170" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'强力底操</v>
       </c>
       <c r="AN170" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 7' H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO170" t="str" s="2">
+        <v>轻量高感枪柄 7' H Extra Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP170" t="str" s="2">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP170" t="str" s="2">
+      <c r="AQ170" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ170" t="str" s="2">
+      <c r="AR170" t="str" s="2">
         <v>UPC: 036282981836; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -25022,10 +25532,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH171" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>轻量高感枪柄 7'3" H Fast，偏重线底操，Heavy Texas、Rubber Jig、Football Jig 适合木桩、石堆和厚草边慢拖，重点是读底后稳定刺鱼。</v>
       </c>
       <c r="AI171" t="str" s="2">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ171" t="str" s="2">
         <v/>
@@ -25034,21 +25544,24 @@
         <v/>
       </c>
       <c r="AL171" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM171" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'3"强力底操</v>
       </c>
       <c r="AN171" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>轻量高感 / 7'3" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO171" t="str" s="2">
+        <v>轻量高感枪柄 7'3" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP171" t="str" s="2">
         <v>Introducing the next generation of Veritas rods with Powerlux® 100, which increases the rod’s strength by 15 percent while also reducing the rod’s overall weight by 5 percent. The new Veritas rod family gives anglers the performance, sensitivity, and durability they need to win, whether they’re fishing for fun or for a paycheck. The Powerlux 100 resin system evenly distributes nano particles between each carbon fiber to enhance the rod’s performance and strength by preventing cracks in the blank material. The Powerlux technology helps produce rods with higher break strengths and improved impact and fracture resistance. The Abu Garcia custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and closed cell EVA split grips, the Abu Garcia Veritas pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP171" t="str" s="2">
+      <c r="AQ171" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ171" t="str" s="2">
+      <c r="AR171" t="str" s="2">
         <v>UPC: 036282981850; Reel Seat: Ergonomic Abu designed reel seat</v>
       </c>
     </row>
@@ -25153,10 +25666,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH172" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7' MH Fast，用于 cover 外缘和硬结构慢拖，Texas Rig、Rubber Jig、Free Rig 的优势在刺鱼余量和软硬饵切换宽容。</v>
       </c>
       <c r="AI172" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ172" t="str" s="1">
         <v/>
@@ -25165,21 +25678,24 @@
         <v/>
       </c>
       <c r="AL172" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM172" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'中重型底操</v>
       </c>
       <c r="AN172" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7' MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO172" t="str" s="1">
+        <v>竞赛轻量枪柄 7' MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP172" t="str" s="1">
         <v>Offering serious anglers with a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The Abu Garcia® custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and a carbon handle split grip design, the new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP172" t="str" s="1">
+      <c r="AQ172" t="str" s="1">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ172" t="str" s="1">
+      <c r="AR172" t="str" s="1">
         <v>UPC: 036282077928</v>
       </c>
     </row>
@@ -25284,10 +25800,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH173" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7' M Fast，抛投负担较轻，Texas Rig、Free Rig、Rubber Jig 适合短中距离打点；需要搜索时再切 Spinnerbait / Chatterbait。</v>
       </c>
       <c r="AI173" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ173" t="str" s="1">
         <v/>
@@ -25296,21 +25812,24 @@
         <v/>
       </c>
       <c r="AL173" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM173" t="str" s="1">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 7'轻中量底操</v>
       </c>
       <c r="AN173" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>竞赛轻量 / 7' M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO173" t="str" s="1">
+        <v>竞赛轻量枪柄 7' M Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP173" t="str" s="1">
         <v>Offering serious anglers with a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The Abu Garcia® custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and a carbon handle split grip design, the new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP173" t="str" s="1">
+      <c r="AQ173" t="str" s="1">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ173" t="str" s="1">
+      <c r="AR173" t="str" s="1">
         <v>UPC: 036282077911</v>
       </c>
     </row>
@@ -25415,10 +25934,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH174" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7'3" MH Fast，更适合 Texas / Jig 路线，Texas Rig、Rubber Jig、Free Rig 先保证落点和读底，鱼活性高时可切移动饵提高覆盖。</v>
       </c>
       <c r="AI174" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ174" t="str" s="1">
         <v/>
@@ -25427,21 +25946,24 @@
         <v/>
       </c>
       <c r="AL174" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM174" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'3"中重型底操</v>
       </c>
       <c r="AN174" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7'3" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO174" t="str" s="1">
+        <v>竞赛轻量枪柄 7'3" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP174" t="str" s="1">
         <v>Offering serious anglers with a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The Abu Garcia® custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and a carbon handle split grip design, the new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP174" t="str" s="1">
+      <c r="AQ174" t="str" s="1">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ174" t="str" s="1">
+      <c r="AR174" t="str" s="1">
         <v>UPC: 036282077942</v>
       </c>
     </row>
@@ -25546,10 +26068,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH175" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7'3" H Fast，用于强结构打点时，Heavy Texas、Rubber Jig、Football Jig 要让饵贴底通过障碍；中鱼后用竿腰把鱼带出标点。</v>
       </c>
       <c r="AI175" t="str" s="1">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ175" t="str" s="1">
         <v/>
@@ -25558,21 +26080,24 @@
         <v/>
       </c>
       <c r="AL175" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM175" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'3"强力底操</v>
       </c>
       <c r="AN175" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7'3" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO175" t="str" s="1">
+        <v>竞赛轻量枪柄 7'3" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP175" t="str" s="1">
         <v>Offering serious anglers with a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The Abu Garcia® custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and a carbon handle split grip design, the new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP175" t="str" s="1">
+      <c r="AQ175" t="str" s="1">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ175" t="str" s="1">
+      <c r="AR175" t="str" s="1">
         <v>UPC: 036282077959</v>
       </c>
     </row>
@@ -25677,10 +26202,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH176" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7'6" MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI176" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ176" t="str" s="1">
         <v/>
@@ -25689,21 +26214,24 @@
         <v/>
       </c>
       <c r="AL176" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM176" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'6"中重型底操</v>
       </c>
       <c r="AN176" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7'6" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO176" t="str" s="1">
+        <v>竞赛轻量枪柄 7'6" MH Fast，12-25 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP176" t="str" s="1">
         <v>Offering serious anglers with a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The Abu Garcia® custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and a carbon handle split grip design, the new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP176" t="str" s="1">
+      <c r="AQ176" t="str" s="1">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ176" t="str" s="1">
+      <c r="AR176" t="str" s="1">
         <v>UPC: 036282077966</v>
       </c>
     </row>
@@ -25808,10 +26336,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH177" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>竞赛轻量枪柄 7'6" H Fast，用于强结构打点时，Heavy Texas、Rubber Jig、Football Jig 要让饵贴底通过障碍；中鱼后用竿腰把鱼带出标点。</v>
       </c>
       <c r="AI177" t="str" s="1">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ177" t="str" s="1">
         <v/>
@@ -25820,21 +26348,24 @@
         <v/>
       </c>
       <c r="AL177" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM177" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'6"强力底操</v>
       </c>
       <c r="AN177" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>竞赛轻量 / 7'6" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO177" t="str" s="1">
+        <v>竞赛轻量枪柄 7'6" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP177" t="str" s="1">
         <v>Offering serious anglers with a rod with increased strength and improved weight and sensitivity. Designed with Powerlux® 200 blanks. Our proprietary resin technology has proven to increase rod break strength without adding materials or weight, allowing us to build a much stronger rod without affecting the balance or overall feel of the rod. The Abu Garcia® custom designed reel seat delivers hypersensitivity around the exposed blank sections and improves comfort for all-day fishing. Coupled with titanium alloy guides with zirconium inserts and a carbon handle split grip design, the new Abu Garcia® Veritas® tournament rod series pushes the limits of high-performance fishing rods.</v>
       </c>
-      <c r="AP177" t="str" s="1">
+      <c r="AQ177" t="str" s="1">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ177" t="str" s="1">
+      <c r="AR177" t="str" s="1">
         <v>UPC: 036282077973</v>
       </c>
     </row>
@@ -25939,10 +26470,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH178" t="str" s="2">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用枪柄 6'6" MH Fast，用于 cover 外缘和硬结构慢拖，Texas Rig、Rubber Jig、Free Rig 的优势在刺鱼余量和软硬饵切换宽容。</v>
       </c>
       <c r="AI178" t="str" s="2">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ178" t="str" s="2">
         <v/>
@@ -25951,21 +26482,24 @@
         <v/>
       </c>
       <c r="AL178" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM178" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 6'6"中重型底操</v>
       </c>
       <c r="AN178" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 6'6" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO178" t="str" s="2">
+        <v>进阶泛用枪柄 6'6" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP178" t="str" s="2">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods feature a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP178" t="str" s="2">
+      <c r="AQ178" t="str" s="2">
         <v>Feature: 30-Ton graphite for a lightweight balanced design</v>
       </c>
-      <c r="AQ178" t="str" s="2">
+      <c r="AR178" t="str" s="2">
         <v>UPC: 036282075863; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -26070,10 +26604,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH179" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用枪柄 6'3" M Fast，抛投负担较轻，Texas Rig、Free Rig、Rubber Jig 适合短中距离打点；需要搜索时再切 Spinnerbait / Chatterbait。</v>
       </c>
       <c r="AI179" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ179" t="str" s="1">
         <v/>
@@ -26082,21 +26616,24 @@
         <v/>
       </c>
       <c r="AL179" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM179" t="str" s="1">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 6'3"轻中量底操</v>
       </c>
       <c r="AN179" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 6'3" M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO179" t="str" s="1">
+        <v>进阶泛用枪柄 6'3" M Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP179" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods feature a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP179" t="str" s="1">
+      <c r="AQ179" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ179" t="str" s="1">
+      <c r="AR179" t="str" s="1">
         <v>UPC: 036282075832; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -26201,10 +26738,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH180" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用枪柄 6'6" M Fast，适合轻中量底操，Texas Rig、Free Rig、Rubber Jig 可以打岸边硬物和稀疏 cover；移动饵只是活性高时的补充。</v>
       </c>
       <c r="AI180" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ180" t="str" s="1">
         <v/>
@@ -26213,21 +26750,24 @@
         <v/>
       </c>
       <c r="AL180" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM180" t="str" s="1">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 6'6"轻中量底操</v>
       </c>
       <c r="AN180" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 6'6" M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO180" t="str" s="1">
+        <v>进阶泛用枪柄 6'6" M Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP180" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods feature a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP180" t="str" s="1">
+      <c r="AQ180" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ180" t="str" s="1">
+      <c r="AR180" t="str" s="1">
         <v>UPC: 036282075849; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -26332,10 +26872,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH181" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用枪柄 6'6" MH Fast，用于 cover 外缘和硬结构慢拖，Texas Rig、Rubber Jig、Free Rig 的优势在刺鱼余量和软硬饵切换宽容。</v>
       </c>
       <c r="AI181" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ181" t="str" s="1">
         <v/>
@@ -26344,21 +26884,24 @@
         <v/>
       </c>
       <c r="AL181" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM181" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 6'6"中重型底操</v>
       </c>
       <c r="AN181" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 6'6" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO181" t="str" s="1">
+        <v>进阶泛用枪柄 6'6" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP181" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods feature a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP181" t="str" s="1">
+      <c r="AQ181" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ181" t="str" s="1">
+      <c r="AR181" t="str" s="1">
         <v>UPC: 036282075856; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -26463,10 +27006,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH182" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用枪柄 6'9" MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI182" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ182" t="str" s="1">
         <v/>
@@ -26475,21 +27018,24 @@
         <v/>
       </c>
       <c r="AL182" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM182" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 6'9"中重型底操</v>
       </c>
       <c r="AN182" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 6'9" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO182" t="str" s="1">
+        <v>进阶泛用枪柄 6'9" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP182" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods feature a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP182" t="str" s="1">
+      <c r="AQ182" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ182" t="str" s="1">
+      <c r="AR182" t="str" s="1">
         <v>UPC: 036282075870; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -26594,10 +27140,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH183" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用枪柄 7' M Fast，适合轻中量底操，Texas Rig、Free Rig、Rubber Jig 可以打岸边硬物和稀疏 cover；移动饵只是活性高时的补充。</v>
       </c>
       <c r="AI183" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ183" t="str" s="1">
         <v/>
@@ -26606,21 +27152,24 @@
         <v/>
       </c>
       <c r="AL183" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM183" t="str" s="1">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 7'轻中量底操</v>
       </c>
       <c r="AN183" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 7' M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO183" t="str" s="1">
+        <v>进阶泛用枪柄 7' M Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP183" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods feature a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP183" t="str" s="1">
+      <c r="AQ183" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ183" t="str" s="1">
+      <c r="AR183" t="str" s="1">
         <v>UPC: 036282075894; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -26725,10 +27274,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH184" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用枪柄 7' MH Fast，用于 cover 外缘和硬结构慢拖，Texas Rig、Rubber Jig、Free Rig 的优势在刺鱼余量和软硬饵切换宽容。</v>
       </c>
       <c r="AI184" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ184" t="str" s="1">
         <v/>
@@ -26737,21 +27286,24 @@
         <v/>
       </c>
       <c r="AL184" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM184" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'中重型底操</v>
       </c>
       <c r="AN184" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 7' MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO184" t="str" s="1">
+        <v>进阶泛用枪柄 7' MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP184" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods feature a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP184" t="str" s="1">
+      <c r="AQ184" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ184" t="str" s="1">
+      <c r="AR184" t="str" s="1">
         <v>UPC: 036282075900; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -26856,10 +27408,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH185" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用枪柄 7' H Fast，偏重线底操，Heavy Texas、Rubber Jig、Football Jig 适合木桩、石堆和厚草边慢拖，重点是读底后稳定刺鱼。</v>
       </c>
       <c r="AI185" t="str" s="1">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ185" t="str" s="1">
         <v/>
@@ -26868,21 +27420,24 @@
         <v/>
       </c>
       <c r="AL185" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM185" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'强力底操</v>
       </c>
       <c r="AN185" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 7' H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO185" t="str" s="1">
+        <v>进阶泛用枪柄 7' H Fast，14-30 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP185" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods feature a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP185" t="str" s="1">
+      <c r="AQ185" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ185" t="str" s="1">
+      <c r="AR185" t="str" s="1">
         <v>UPC: 036282075917; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -26987,10 +27542,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH186" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用枪柄 7'3" MH Fast，更适合 Texas / Jig 路线，Texas Rig、Rubber Jig、Free Rig 先保证落点和读底，鱼活性高时可切移动饵提高覆盖。</v>
       </c>
       <c r="AI186" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ186" t="str" s="1">
         <v/>
@@ -26999,21 +27554,24 @@
         <v/>
       </c>
       <c r="AL186" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM186" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'3"中重型底操</v>
       </c>
       <c r="AN186" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 7'3" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO186" t="str" s="1">
+        <v>进阶泛用枪柄 7'3" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP186" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods feature a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP186" t="str" s="1">
+      <c r="AQ186" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ186" t="str" s="1">
+      <c r="AR186" t="str" s="1">
         <v>UPC: 036282075924; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -27118,10 +27676,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH187" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用枪柄 7'3" H Fast，偏重线底操，Heavy Texas、Rubber Jig、Football Jig 适合木桩、石堆和厚草边慢拖，重点是读底后稳定刺鱼。</v>
       </c>
       <c r="AI187" t="str" s="1">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ187" t="str" s="1">
         <v/>
@@ -27130,21 +27688,24 @@
         <v/>
       </c>
       <c r="AL187" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM187" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'3"强力底操</v>
       </c>
       <c r="AN187" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 7'3" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO187" t="str" s="1">
+        <v>进阶泛用枪柄 7'3" H Fast，14-30 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP187" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods feature a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP187" t="str" s="1">
+      <c r="AQ187" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ187" t="str" s="1">
+      <c r="AR187" t="str" s="1">
         <v>UPC: 036282075931; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -27249,10 +27810,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH188" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用枪柄 7'6" MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI188" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ188" t="str" s="1">
         <v/>
@@ -27261,21 +27822,24 @@
         <v/>
       </c>
       <c r="AL188" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM188" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'6"中重型底操</v>
       </c>
       <c r="AN188" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 7'6" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO188" t="str" s="1">
+        <v>进阶泛用枪柄 7'6" MH Fast，12-25 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP188" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods feature a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP188" t="str" s="1">
+      <c r="AQ188" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ188" t="str" s="1">
+      <c r="AR188" t="str" s="1">
         <v>UPC: 036282075948; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -27380,10 +27944,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH189" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用枪柄 7'6" H Fast，偏重线底操，Heavy Texas、Rubber Jig、Football Jig 适合木桩、石堆和厚草边慢拖，重点是读底后稳定刺鱼。</v>
       </c>
       <c r="AI189" t="str" s="1">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ189" t="str" s="1">
         <v/>
@@ -27392,21 +27956,24 @@
         <v/>
       </c>
       <c r="AL189" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM189" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'6"强力底操</v>
       </c>
       <c r="AN189" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>进阶泛用 / 7'6" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO189" t="str" s="1">
+        <v>进阶泛用枪柄 7'6" H Fast，14-30 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP189" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods feature a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP189" t="str" s="1">
+      <c r="AQ189" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ189" t="str" s="1">
+      <c r="AR189" t="str" s="1">
         <v>UPC: 036282075955; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -27511,10 +28078,10 @@
         <v>Stainless steel / Zirconium guide train</v>
       </c>
       <c r="AH190" t="str" s="1">
-        <v>导环内衬更适合高频抛投和细线使用</v>
+        <v>进阶泛用枪柄 7' M Moderate，偏 crankbait 节奏，Crankbait、Shad Crank、Squarebill 要保持泳层和回收速度；挂底或碰障后用竿身缓冲带过。</v>
       </c>
       <c r="AI190" t="str" s="1">
-        <v/>
+        <v>Crankbait / Shad Crank / Squarebill / Lipless Crankbait / Chatterbait</v>
       </c>
       <c r="AJ190" t="str" s="1">
         <v/>
@@ -27523,21 +28090,24 @@
         <v/>
       </c>
       <c r="AL190" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM190" t="str" s="1">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 开阔水域卷阻搜索 / 7'Crankbait</v>
       </c>
       <c r="AN190" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>进阶泛用 / 7' M crankbait / shad 专项</v>
       </c>
       <c r="AO190" t="str" s="1">
+        <v>进阶泛用枪柄 7' M Moderate，8-17 lb线组配置下，Crankbait、Shad Crank、Squarebill 优先，稳定卷收和挂鱼缓冲比快速刺鱼更关键；适合沿草边、石滩和浅中层水线搜索。</v>
+      </c>
+      <c r="AP190" t="str" s="1">
         <v>With a continued tradition of advanced design and precision performance, the Vendetta rod series features a construction that delivers on the water every time. 30-ton graphite paired with Intracarbon™ multidirectional carbon fibers allow for a lightweight blank with the ability to stand up to intense loads. Rods feature a new ergonomic molded carbon fiber reel seat which is interconnected, lighter, and sleeker looking.</v>
       </c>
-      <c r="AP190" t="str" s="1">
+      <c r="AQ190" t="str" s="1">
         <v>Guide Type: Stainless Steel</v>
       </c>
-      <c r="AQ190" t="str" s="1">
+      <c r="AR190" t="str" s="1">
         <v>UPC: 036282075962; Reel Seat: CCRS carbon constructed reel seat</v>
       </c>
     </row>
@@ -27642,10 +28212,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH191" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 6'10" ML Fast，适合细线轻饵打点，Neko Rig、Down Shot、No Sinker 要控制落点和松线；小 crank 可做短距离搜索补充。</v>
       </c>
       <c r="AI191" t="str" s="2">
-        <v/>
+        <v>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Small Crankbait</v>
       </c>
       <c r="AJ191" t="str" s="2">
         <v/>
@@ -27654,21 +28224,24 @@
         <v/>
       </c>
       <c r="AL191" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM191" t="str" s="2">
-        <v>枪柄精细轻饵</v>
+        <v>淡水 Bass / 小场地轻线打点 / 6'10"枪柄精细轻饵</v>
       </c>
       <c r="AN191" t="str" s="2">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>高阶轻量 / 6'10" ML Neko / No Sinker 轻量打点</v>
       </c>
       <c r="AO191" t="str" s="2">
+        <v>高阶轻量枪柄 6'10" ML Fast，6-12 lb线组配置下，Neko Rig、Down Shot、No Sinker 优先，适合小标点低弹道抛投；小 crank 只作为补充搜索路线。</v>
+      </c>
+      <c r="AP191" t="str" s="2">
         <v>Introducing the next generation of sleek design and high performance rods with the Fantasista X. Featuring premium carbon blanks and our proprietary Powerlux® 500 resin system, Fantasista X rods deliver sensitive, yet powerful ultra-light blanks with improved impact and fracture resistance. Fuji® reel seats coupled with EVA and carbon rear split grip design allow for reduced weight and increased sensitivity , which makes the Fantasista X one of our most extremely sensitive and lightweight-performing rods.</v>
       </c>
-      <c r="AP191" t="str" s="2">
+      <c r="AQ191" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ191" t="str" s="2">
+      <c r="AR191" t="str" s="2">
         <v>UPC: 036282078031</v>
       </c>
     </row>
@@ -27773,10 +28346,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH192" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 6'10" MH Fast，更适合 Texas / Jig 路线，Texas Rig、Rubber Jig、Free Rig 先保证落点和读底，鱼活性高时可切移动饵提高覆盖。</v>
       </c>
       <c r="AI192" t="str" s="2">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ192" t="str" s="2">
         <v/>
@@ -27785,21 +28358,24 @@
         <v/>
       </c>
       <c r="AL192" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM192" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 6'10"中重型底操</v>
       </c>
       <c r="AN192" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>高阶轻量 / 6'10" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO192" t="str" s="2">
+        <v>高阶轻量枪柄 6'10" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP192" t="str" s="2">
         <v>Introducing the next generation of sleek design and high performance rods with the Fantasista X. Featuring premium carbon blanks and our proprietary Powerlux® 500 resin system, Fantasista X rods deliver sensitive, yet powerful ultra-light blanks with improved impact and fracture resistance. Fuji® reel seats coupled with EVA and carbon rear split grip design allow for reduced weight and increased sensitivity , which makes the Fantasista X one of our most extremely sensitive and lightweight-performing rods.</v>
       </c>
-      <c r="AP192" t="str" s="2">
+      <c r="AQ192" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ192" t="str" s="2">
+      <c r="AR192" t="str" s="2">
         <v>UPC: 036282078048</v>
       </c>
     </row>
@@ -27904,10 +28480,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH193" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 7' M Fast，抛投负担较轻，Texas Rig、Free Rig、Rubber Jig 适合短中距离打点；需要搜索时再切 Spinnerbait / Chatterbait。</v>
       </c>
       <c r="AI193" t="str" s="2">
-        <v/>
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ193" t="str" s="2">
         <v/>
@@ -27916,21 +28492,24 @@
         <v/>
       </c>
       <c r="AL193" t="str" s="2">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM193" t="str" s="2">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 7'轻中量底操</v>
       </c>
       <c r="AN193" t="str" s="2">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>高阶轻量 / 7' M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO193" t="str" s="2">
+        <v>高阶轻量枪柄 7' M Fast，8-17 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP193" t="str" s="2">
         <v>Introducing the next generation of sleek design and high performance rods with the Fantasista X. Featuring premium carbon blanks and our proprietary Powerlux® 500 resin system, Fantasista X rods deliver sensitive, yet powerful ultra-light blanks with improved impact and fracture resistance. Fuji® reel seats coupled with EVA and carbon rear split grip design allow for reduced weight and increased sensitivity , which makes the Fantasista X one of our most extremely sensitive and lightweight-performing rods.</v>
       </c>
-      <c r="AP193" t="str" s="2">
+      <c r="AQ193" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ193" t="str" s="2">
+      <c r="AR193" t="str" s="2">
         <v>UPC: 036282078055</v>
       </c>
     </row>
@@ -28035,10 +28614,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH194" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 7' MH Extra Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI194" t="str" s="2">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ194" t="str" s="2">
         <v/>
@@ -28047,21 +28626,24 @@
         <v/>
       </c>
       <c r="AL194" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM194" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'中重型底操</v>
       </c>
       <c r="AN194" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>高阶轻量 / 7' MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO194" t="str" s="2">
+        <v>高阶轻量枪柄 7' MH Extra Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP194" t="str" s="2">
         <v>Introducing the next generation of sleek design and high performance rods with the Fantasista X. Featuring premium carbon blanks and our proprietary Powerlux® 500 resin system, Fantasista X rods deliver sensitive, yet powerful ultra-light blanks with improved impact and fracture resistance. Fuji® reel seats coupled with EVA and carbon rear split grip design allow for reduced weight and increased sensitivity , which makes the Fantasista X one of our most extremely sensitive and lightweight-performing rods.</v>
       </c>
-      <c r="AP194" t="str" s="2">
+      <c r="AQ194" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ194" t="str" s="2">
+      <c r="AR194" t="str" s="2">
         <v>UPC: 036282078062</v>
       </c>
     </row>
@@ -28166,10 +28748,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH195" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 7'3" MH Fast，更适合 Texas / Jig 路线，Texas Rig、Rubber Jig、Free Rig 先保证落点和读底，鱼活性高时可切移动饵提高覆盖。</v>
       </c>
       <c r="AI195" t="str" s="2">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ195" t="str" s="2">
         <v/>
@@ -28178,21 +28760,24 @@
         <v/>
       </c>
       <c r="AL195" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM195" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'3"中重型底操</v>
       </c>
       <c r="AN195" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>高阶轻量 / 7'3" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO195" t="str" s="2">
+        <v>高阶轻量枪柄 7'3" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP195" t="str" s="2">
         <v>Introducing the next generation of sleek design and high performance rods with the Fantasista X. Featuring premium carbon blanks and our proprietary Powerlux® 500 resin system, Fantasista X rods deliver sensitive, yet powerful ultra-light blanks with improved impact and fracture resistance. Fuji® reel seats coupled with EVA and carbon rear split grip design allow for reduced weight and increased sensitivity , which makes the Fantasista X one of our most extremely sensitive and lightweight-performing rods.</v>
       </c>
-      <c r="AP195" t="str" s="2">
+      <c r="AQ195" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ195" t="str" s="2">
+      <c r="AR195" t="str" s="2">
         <v>UPC: 036282078079</v>
       </c>
     </row>
@@ -28297,10 +28882,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH196" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 7'3" H Fast，偏重线底操，Heavy Texas、Rubber Jig、Football Jig 适合木桩、石堆和厚草边慢拖，重点是读底后稳定刺鱼。</v>
       </c>
       <c r="AI196" t="str" s="2">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ196" t="str" s="2">
         <v/>
@@ -28309,21 +28894,24 @@
         <v/>
       </c>
       <c r="AL196" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM196" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'3"强力底操</v>
       </c>
       <c r="AN196" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>高阶轻量 / 7'3" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO196" t="str" s="2">
+        <v>高阶轻量枪柄 7'3" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP196" t="str" s="2">
         <v>Introducing the next generation of sleek design and high performance rods with the Fantasista X. Featuring premium carbon blanks and our proprietary Powerlux® 500 resin system, Fantasista X rods deliver sensitive, yet powerful ultra-light blanks with improved impact and fracture resistance. Fuji® reel seats coupled with EVA and carbon rear split grip design allow for reduced weight and increased sensitivity , which makes the Fantasista X one of our most extremely sensitive and lightweight-performing rods.</v>
       </c>
-      <c r="AP196" t="str" s="2">
+      <c r="AQ196" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ196" t="str" s="2">
+      <c r="AR196" t="str" s="2">
         <v>UPC: 036282078086</v>
       </c>
     </row>
@@ -28428,10 +29016,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH197" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 7'6" MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI197" t="str" s="2">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ197" t="str" s="2">
         <v/>
@@ -28440,21 +29028,24 @@
         <v/>
       </c>
       <c r="AL197" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM197" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'6"中重型底操</v>
       </c>
       <c r="AN197" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>高阶轻量 / 7'6" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO197" t="str" s="2">
+        <v>高阶轻量枪柄 7'6" MH Fast，12-20 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP197" t="str" s="2">
         <v>Introducing the next generation of sleek design and high performance rods with the Fantasista X. Featuring premium carbon blanks and our proprietary Powerlux® 500 resin system, Fantasista X rods deliver sensitive, yet powerful ultra-light blanks with improved impact and fracture resistance. Fuji® reel seats coupled with EVA and carbon rear split grip design allow for reduced weight and increased sensitivity , which makes the Fantasista X one of our most extremely sensitive and lightweight-performing rods.</v>
       </c>
-      <c r="AP197" t="str" s="2">
+      <c r="AQ197" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ197" t="str" s="2">
+      <c r="AR197" t="str" s="2">
         <v>UPC: 036282078093</v>
       </c>
     </row>
@@ -28559,10 +29150,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH198" t="str" s="2">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 7'6" H Fast，偏重线底操，Heavy Texas、Rubber Jig、Football Jig 适合木桩、石堆和厚草边慢拖，重点是读底后稳定刺鱼。</v>
       </c>
       <c r="AI198" t="str" s="2">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ198" t="str" s="2">
         <v/>
@@ -28571,21 +29162,24 @@
         <v/>
       </c>
       <c r="AL198" t="str" s="2">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM198" t="str" s="2">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'6"强力底操</v>
       </c>
       <c r="AN198" t="str" s="2">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>高阶轻量 / 7'6" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO198" t="str" s="2">
+        <v>高阶轻量枪柄 7'6" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP198" t="str" s="2">
         <v>Introducing the next generation of sleek design and high performance rods with the Fantasista X. Featuring premium carbon blanks and our proprietary Powerlux® 500 resin system, Fantasista X rods deliver sensitive, yet powerful ultra-light blanks with improved impact and fracture resistance. Fuji® reel seats coupled with EVA and carbon rear split grip design allow for reduced weight and increased sensitivity , which makes the Fantasista X one of our most extremely sensitive and lightweight-performing rods.</v>
       </c>
-      <c r="AP198" t="str" s="2">
+      <c r="AQ198" t="str" s="2">
         <v>Guide Type: Titanium</v>
       </c>
-      <c r="AQ198" t="str" s="2">
+      <c r="AR198" t="str" s="2">
         <v>UPC: 036282078109</v>
       </c>
     </row>
@@ -28690,10 +29284,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH199" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 6'9" ML Fast，适合细线轻饵打点，Neko Rig、Down Shot、No Sinker 要控制落点和松线；小 crank 可做短距离搜索补充。</v>
       </c>
       <c r="AI199" t="str" s="1">
-        <v/>
+        <v>Neko Rig / Down Shot / No Sinker / Small Rubber Jig / Small Crankbait</v>
       </c>
       <c r="AJ199" t="str" s="1">
         <v/>
@@ -28702,21 +29296,24 @@
         <v/>
       </c>
       <c r="AL199" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM199" t="str" s="1">
-        <v>枪柄精细轻饵</v>
+        <v>淡水 Bass / 小场地轻线打点 / 6'9"枪柄精细轻饵</v>
       </c>
       <c r="AN199" t="str" s="1">
-        <v>轻饵与精细钓组更顺手 / 小型软饵和轻量硬饵操作更直接</v>
+        <v>高阶轻量 / 6'9" ML Neko / No Sinker 轻量打点</v>
       </c>
       <c r="AO199" t="str" s="1">
+        <v>高阶轻量枪柄 6'9" ML Fast，4-10 lb线组配置下，Neko Rig、Down Shot、No Sinker 优先，适合小标点低弹道抛投；小 crank 只作为补充搜索路线。</v>
+      </c>
+      <c r="AP199" t="str" s="1">
         <v>Introducing Abu Garcia’s lightest rod series with the Abu Garcia® Zenon™ rods. Featuring premium carbon blanks and our exclusive Powerlux® 1000 resin system, these rods deliver powerful ultra-light sensitive blanks with higher break strengths and improved impact and fracture resistance without increasing overall weight or blank diameters. Fuji® reel seat improves comfort for all-day fishing. Coupled with titanium alloy guides with nitride silicon inserts and a carbon handle split grip design, the Abu Garcia Zenon rods are optimized for performance.</v>
       </c>
-      <c r="AP199" t="str" s="1">
+      <c r="AQ199" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ199" t="str" s="1">
+      <c r="AR199" t="str" s="1">
         <v>UPC: 036282144255</v>
       </c>
     </row>
@@ -28821,10 +29418,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH200" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 7' M Fast，适合轻中量底操，Texas Rig、Free Rig、Rubber Jig 可以打岸边硬物和稀疏 cover；移动饵只是活性高时的补充。</v>
       </c>
       <c r="AI200" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Free Rig / Rubber Jig / Spinnerbait / Chatterbait</v>
       </c>
       <c r="AJ200" t="str" s="1">
         <v/>
@@ -28833,21 +29430,24 @@
         <v/>
       </c>
       <c r="AL200" t="str" s="1">
-        <v>淡水 / bass</v>
+        <v/>
       </c>
       <c r="AM200" t="str" s="1">
-        <v>枪柄泛用</v>
+        <v>淡水 Bass / 岸边硬物与轻 cover / 7'轻中量底操</v>
       </c>
       <c r="AN200" t="str" s="1">
-        <v>淡水泛用路亚场景适配 / 常规软硬饵和搜索覆盖较广</v>
+        <v>高阶轻量 / 7' M Texas / Free Rig 轻中量泛用</v>
       </c>
       <c r="AO200" t="str" s="1">
+        <v>高阶轻量枪柄 7' M Fast，8-15 lb线组配置下，Texas Rig、Free Rig、Rubber Jig 优先，抛投负担较轻，适合岸边结构慢拖；鱼活性高时可换 Spinnerbait 搜索。</v>
+      </c>
+      <c r="AP200" t="str" s="1">
         <v>Introducing Abu Garcia’s lightest rod series with the Abu Garcia® Zenon™ rods. Featuring premium carbon blanks and our exclusive Powerlux® 1000 resin system, these rods deliver powerful ultra-light sensitive blanks with higher break strengths and improved impact and fracture resistance without increasing overall weight or blank diameters. Fuji® reel seat improves comfort for all-day fishing. Coupled with titanium alloy guides with nitride silicon inserts and a carbon handle split grip design, the Abu Garcia Zenon rods are optimized for performance.</v>
       </c>
-      <c r="AP200" t="str" s="1">
+      <c r="AQ200" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ200" t="str" s="1">
+      <c r="AR200" t="str" s="1">
         <v>UPC: 036282144262</v>
       </c>
     </row>
@@ -28952,10 +29552,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH201" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 7' MH Fast，更适合 Texas / Jig 路线，Texas Rig、Rubber Jig、Free Rig 先保证落点和读底，鱼活性高时可切移动饵提高覆盖。</v>
       </c>
       <c r="AI201" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ201" t="str" s="1">
         <v/>
@@ -28964,21 +29564,24 @@
         <v/>
       </c>
       <c r="AL201" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM201" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'中重型底操</v>
       </c>
       <c r="AN201" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>高阶轻量 / 7' MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO201" t="str" s="1">
+        <v>高阶轻量枪柄 7' MH Fast，10-17 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP201" t="str" s="1">
         <v>Introducing Abu Garcia’s lightest rod series with the Abu Garcia® Zenon™ rods. Featuring premium carbon blanks and our exclusive Powerlux® 1000 resin system, these rods deliver powerful ultra-light sensitive blanks with higher break strengths and improved impact and fracture resistance without increasing overall weight or blank diameters. Fuji® reel seat improves comfort for all-day fishing. Coupled with titanium alloy guides with nitride silicon inserts and a carbon handle split grip design, the Abu Garcia Zenon rods are optimized for performance.</v>
       </c>
-      <c r="AP201" t="str" s="1">
+      <c r="AQ201" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ201" t="str" s="1">
+      <c r="AR201" t="str" s="1">
         <v>UPC: 036282144279</v>
       </c>
     </row>
@@ -29083,10 +29686,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH202" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 7'2" H Fast，偏重线底操，Heavy Texas、Rubber Jig、Football Jig 适合木桩、石堆和厚草边慢拖，重点是读底后稳定刺鱼。</v>
       </c>
       <c r="AI202" t="str" s="1">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ202" t="str" s="1">
         <v/>
@@ -29095,21 +29698,24 @@
         <v/>
       </c>
       <c r="AL202" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM202" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'2"强力底操</v>
       </c>
       <c r="AN202" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>高阶轻量 / 7'2" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO202" t="str" s="1">
+        <v>高阶轻量枪柄 7'2" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP202" t="str" s="1">
         <v>Introducing Abu Garcia’s lightest rod series with the Abu Garcia® Zenon™ rods. Featuring premium carbon blanks and our exclusive Powerlux® 1000 resin system, these rods deliver powerful ultra-light sensitive blanks with higher break strengths and improved impact and fracture resistance without increasing overall weight or blank diameters. Fuji® reel seat improves comfort for all-day fishing. Coupled with titanium alloy guides with nitride silicon inserts and a carbon handle split grip design, the Abu Garcia Zenon rods are optimized for performance.</v>
       </c>
-      <c r="AP202" t="str" s="1">
+      <c r="AQ202" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ202" t="str" s="1">
+      <c r="AR202" t="str" s="1">
         <v>UPC: 036282144286</v>
       </c>
     </row>
@@ -29214,10 +29820,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH203" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 7'3" MH Fast，是中重型底操主力，Texas Rig、Rubber Jig、Free Rig 适合岸边结构、草边和硬物点；搜索时再换 Chatterbait / Spinnerbait。</v>
       </c>
       <c r="AI203" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ203" t="str" s="1">
         <v/>
@@ -29226,21 +29832,24 @@
         <v/>
       </c>
       <c r="AL203" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM203" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'3"中重型底操</v>
       </c>
       <c r="AN203" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>高阶轻量 / 7'3" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO203" t="str" s="1">
+        <v>高阶轻量枪柄 7'3" MH Fast，10-17 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP203" t="str" s="1">
         <v>Introducing Abu Garcia’s lightest rod series with the Abu Garcia® Zenon™ rods. Featuring premium carbon blanks and our exclusive Powerlux® 1000 resin system, these rods deliver powerful ultra-light sensitive blanks with higher break strengths and improved impact and fracture resistance without increasing overall weight or blank diameters. Fuji® reel seat improves comfort for all-day fishing. Coupled with titanium alloy guides with nitride silicon inserts and a carbon handle split grip design, the Abu Garcia Zenon rods are optimized for performance.</v>
       </c>
-      <c r="AP203" t="str" s="1">
+      <c r="AQ203" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ203" t="str" s="1">
+      <c r="AR203" t="str" s="1">
         <v>UPC: 036282118010</v>
       </c>
     </row>
@@ -29345,10 +29954,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH204" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 7'3" H Fast，偏重线底操，Heavy Texas、Rubber Jig、Football Jig 适合木桩、石堆和厚草边慢拖，重点是读底后稳定刺鱼。</v>
       </c>
       <c r="AI204" t="str" s="1">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ204" t="str" s="1">
         <v/>
@@ -29357,21 +29966,24 @@
         <v/>
       </c>
       <c r="AL204" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM204" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'3"强力底操</v>
       </c>
       <c r="AN204" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>高阶轻量 / 7'3" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO204" t="str" s="1">
+        <v>高阶轻量枪柄 7'3" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP204" t="str" s="1">
         <v>Introducing Abu Garcia’s lightest rod series with the Abu Garcia® Zenon™ rods. Featuring premium carbon blanks and our exclusive Powerlux® 1000 resin system, these rods deliver powerful ultra-light sensitive blanks with higher break strengths and improved impact and fracture resistance without increasing overall weight or blank diameters. Fuji® reel seat improves comfort for all-day fishing. Coupled with titanium alloy guides with nitride silicon inserts and a carbon handle split grip design, the Abu Garcia Zenon rods are optimized for performance.</v>
       </c>
-      <c r="AP204" t="str" s="1">
+      <c r="AQ204" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ204" t="str" s="1">
+      <c r="AR204" t="str" s="1">
         <v>UPC: 036282118027</v>
       </c>
     </row>
@@ -29476,10 +30088,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH205" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 7'4" MH Fast，用于 cover 外缘和硬结构慢拖，Texas Rig、Rubber Jig、Free Rig 的优势在刺鱼余量和软硬饵切换宽容。</v>
       </c>
       <c r="AI205" t="str" s="1">
-        <v/>
+        <v>Texas Rig / Rubber Jig / Free Rig / Chatterbait / Spinnerbait</v>
       </c>
       <c r="AJ205" t="str" s="1">
         <v/>
@@ -29488,21 +30100,24 @@
         <v/>
       </c>
       <c r="AL205" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM205" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 岸边结构与草边 / 7'4"中重型底操</v>
       </c>
       <c r="AN205" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>高阶轻量 / 7'4" MH Texas / Rubber Jig 泛用底操</v>
       </c>
       <c r="AO205" t="str" s="1">
+        <v>高阶轻量枪柄 7'4" MH Fast，10-17 lb线组配置下，Texas Rig、Rubber Jig、Free Rig 优先，适合落点打准后读底和碰障；需要搜索时可切 Chatterbait / Spinnerbait。</v>
+      </c>
+      <c r="AP205" t="str" s="1">
         <v>Introducing Abu Garcia’s lightest rod series with the Abu Garcia® Zenon™ rods. Featuring premium carbon blanks and our exclusive Powerlux® 1000 resin system, these rods deliver powerful ultra-light sensitive blanks with higher break strengths and improved impact and fracture resistance without increasing overall weight or blank diameters. Fuji® reel seat improves comfort for all-day fishing. Coupled with titanium alloy guides with nitride silicon inserts and a carbon handle split grip design, the Abu Garcia Zenon rods are optimized for performance.</v>
       </c>
-      <c r="AP205" t="str" s="1">
+      <c r="AQ205" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ205" t="str" s="1">
+      <c r="AR205" t="str" s="1">
         <v>UPC: 036282118034</v>
       </c>
     </row>
@@ -29607,10 +30222,10 @@
         <v>ROCS guide train</v>
       </c>
       <c r="AH206" t="str" s="1">
-        <v>maximized casting distance with lighter lures</v>
+        <v>高阶轻量枪柄 7'6" H Fast，偏重线底操，Heavy Texas、Rubber Jig、Football Jig 适合木桩、石堆和厚草边慢拖，重点是读底后稳定刺鱼。</v>
       </c>
       <c r="AI206" t="str" s="1">
-        <v/>
+        <v>Heavy Texas / Rubber Jig / Football Jig / Swim Jig / Carolina Rig</v>
       </c>
       <c r="AJ206" t="str" s="1">
         <v/>
@@ -29619,27 +30234,30 @@
         <v/>
       </c>
       <c r="AL206" t="str" s="1">
-        <v>淡水 / bass / 强力泛用</v>
+        <v/>
       </c>
       <c r="AM206" t="str" s="1">
-        <v>枪柄强力泛用</v>
+        <v>淡水 Bass / 重线 cover 与硬结构 / 7'6"强力底操</v>
       </c>
       <c r="AN206" t="str" s="1">
-        <v>适合中重型路亚和强控鱼场景 / 腰力和余量更强 / 比轻量泛用竿更适合覆盖障碍和大个体</v>
+        <v>高阶轻量 / 7'6" H Heavy Texas / Jig 底操</v>
       </c>
       <c r="AO206" t="str" s="1">
+        <v>高阶轻量枪柄 7'6" H Fast，12-25 lb线组配置下，Heavy Texas、Rubber Jig、Football Jig 优先，适合木桩、石堆、草边等需要贴底慢拖的点；重点是重线底操和贴障控鱼。</v>
+      </c>
+      <c r="AP206" t="str" s="1">
         <v>Introducing Abu Garcia’s lightest rod series with the Abu Garcia® Zenon™ rods. Featuring premium carbon blanks and our exclusive Powerlux® 1000 resin system, these rods deliver powerful ultra-light sensitive blanks with higher break strengths and improved impact and fracture resistance without increasing overall weight or blank diameters. Fuji® reel seat improves comfort for all-day fishing. Coupled with titanium alloy guides with nitride silicon inserts and a carbon handle split grip design, the Abu Garcia Zenon rods are optimized for performance.</v>
       </c>
-      <c r="AP206" t="str" s="1">
+      <c r="AQ206" t="str" s="1">
         <v>Guide Type: Titanium Zirconium</v>
       </c>
-      <c r="AQ206" t="str" s="1">
+      <c r="AR206" t="str" s="1">
         <v>UPC: 036282118041</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AQ206"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AR206"/>
   </ignoredErrors>
 </worksheet>
 </file>